--- a/Project Zero Dashboard 1 - Copy.xlsx
+++ b/Project Zero Dashboard 1 - Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMT NUC 3\Desktop\Solar Dashboard Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733EC174-2FF6-4A89-B2EC-047F238F5B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F30B43-584F-4A96-A8C9-63A5C8A6E518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{850AF22D-85D1-4C73-981E-24580D680358}"/>
   </bookViews>
@@ -21474,13 +21474,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>28</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>24</c:v>
@@ -21586,13 +21586,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>79</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>78</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>84</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>82</c:v>
@@ -21697,13 +21697,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>51</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>58</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>58</c:v>
@@ -26981,14 +26981,14 @@
         <v>82</v>
       </c>
       <c r="AF6" s="52">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AG6" s="40">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="AH6" s="40">
         <f>IF(AF6&gt;AG6,0,AG6-AF6)</f>
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="AI6" s="22"/>
       <c r="AJ6">
@@ -27062,11 +27062,11 @@
         <v>27</v>
       </c>
       <c r="AG7" s="40">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="AH7" s="40">
         <f t="shared" ref="AH7:AH17" si="5">IF(AF7&gt;AG7,0,AG7-AF7)</f>
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="AI7" s="22"/>
       <c r="AJ7">
@@ -27137,14 +27137,14 @@
         <v>84</v>
       </c>
       <c r="AF8" s="40">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG8" s="40">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="AH8" s="40">
         <f t="shared" si="5"/>
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="AI8" s="22"/>
       <c r="AJ8">

--- a/Project Zero Dashboard 1 - Copy.xlsx
+++ b/Project Zero Dashboard 1 - Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMT NUC 3\Desktop\Solar Dashboard Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F30B43-584F-4A96-A8C9-63A5C8A6E518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D5502A-2042-4CBD-88BA-72A7314AC4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{850AF22D-85D1-4C73-981E-24580D680358}"/>
   </bookViews>
@@ -560,7 +560,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -601,27 +601,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5793,7 +5784,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -6021,7 +6012,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.00">
-                  <c:v>174.69849771143146</c:v>
+                  <c:v>175.45132063535101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11016,7 +11007,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0</c:v>
@@ -11094,7 +11085,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>125.30150228856854</c:v>
+                  <c:v>124.548679364649</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16166,7 +16157,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.00">
-                  <c:v>174.69849771143146</c:v>
+                  <c:v>174.82613529007804</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21243,7 +21234,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>125.30150228856854</c:v>
+                  <c:v>125.17386470992196</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21477,16 +21468,19 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>29</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.66610000000000003</c:v>
+                <c:pt idx="5">
+                  <c:v>1.327</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21589,16 +21583,19 @@
                   <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>63</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>65</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>82</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.6326499999999999</c:v>
+                <c:pt idx="5">
+                  <c:v>5.2713400000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21700,16 +21697,37 @@
                   <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>58</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.9665499999999998</c:v>
+                <c:pt idx="5">
+                  <c:v>3.9443400000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25900,7 +25918,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>666,10</a:t>
+            <a:t>651,90</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="3600">
             <a:solidFill>
@@ -25975,7 +25993,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>666,10</a:t>
+            <a:t>1327,00</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -26254,7 +26272,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>1966,55</a:t>
+            <a:t>2003,64</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -26329,7 +26347,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>1966,55</a:t>
+            <a:t>3944,34</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="6600">
             <a:solidFill>
@@ -26822,21 +26840,21 @@
       <c r="O4" s="4"/>
       <c r="P4" s="19">
         <f>AVERAGE(Y6:Y68)</f>
-        <v>12.567924528301887</v>
+        <v>12.300000000000002</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="V4" s="37"/>
+      <c r="V4" s="36"/>
       <c r="W4" s="6"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
+      <c r="X4" s="37"/>
+      <c r="Y4" s="37"/>
+      <c r="Z4" s="37"/>
+      <c r="AA4" s="37"/>
       <c r="AB4" s="6"/>
-      <c r="AC4" s="38"/>
+      <c r="AC4" s="37"/>
       <c r="AD4" s="16"/>
-      <c r="AE4" s="37"/>
+      <c r="AE4" s="36"/>
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
       <c r="AH4" s="6"/>
@@ -26875,38 +26893,35 @@
       <c r="O5" s="4"/>
       <c r="P5" s="20">
         <f>AVERAGE(AA6:AA68)</f>
-        <v>48.75277777777778</v>
+        <v>49.176666666666669</v>
       </c>
       <c r="Q5" s="18" t="s">
         <v>77</v>
       </c>
       <c r="V5" s="7"/>
-      <c r="W5" s="39" t="s">
+      <c r="W5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="41" t="s">
+      <c r="Y5" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="41" t="s">
+      <c r="AA5" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="AB5" s="42"/>
-      <c r="AC5" s="43" t="s">
+      <c r="AC5" s="21" t="s">
         <v>66</v>
       </c>
       <c r="AD5" s="22"/>
-      <c r="AE5" s="51" t="s">
+      <c r="AE5" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="AF5" s="39" t="s">
+      <c r="AF5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AG5" s="39" t="s">
+      <c r="AG5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="AH5" s="39" t="s">
+      <c r="AH5" s="5" t="s">
         <v>96</v>
       </c>
       <c r="AI5" s="22"/>
@@ -26954,25 +26969,22 @@
       <c r="O6" s="4"/>
       <c r="P6" s="20">
         <f>IF(P4&gt;P5,0,P5-P4)</f>
-        <v>36.184853249475893</v>
+        <v>36.876666666666665</v>
       </c>
       <c r="Q6" s="18" t="s">
         <v>77</v>
       </c>
       <c r="V6" s="7"/>
-      <c r="W6" s="42" t="s">
+      <c r="W6" t="s">
         <v>9</v>
       </c>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="40"/>
-      <c r="AA6" s="44">
+      <c r="Y6" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="14">
         <v>66</v>
       </c>
-      <c r="AB6" s="42"/>
-      <c r="AC6" s="40">
+      <c r="AC6" s="13">
         <f>IF(Y6&gt;AA6,0,AA6-Y6)</f>
         <v>66</v>
       </c>
@@ -26980,13 +26992,13 @@
       <c r="AE6" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="AF6" s="52">
+      <c r="AF6" s="13">
         <v>34</v>
       </c>
-      <c r="AG6" s="40">
+      <c r="AG6" s="13">
         <v>64</v>
       </c>
-      <c r="AH6" s="40">
+      <c r="AH6" s="13">
         <f>IF(AF6&gt;AG6,0,AG6-AF6)</f>
         <v>30</v>
       </c>
@@ -27032,25 +27044,22 @@
       </c>
       <c r="P7" s="21">
         <f>SUM(Y6:Y59)</f>
-        <v>666.1</v>
+        <v>651.90000000000009</v>
       </c>
       <c r="Q7" s="18" t="s">
         <v>77</v>
       </c>
       <c r="V7" s="7"/>
-      <c r="W7" s="42" t="s">
+      <c r="W7" t="s">
         <v>11</v>
       </c>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="40"/>
-      <c r="AA7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="42"/>
-      <c r="AC7" s="40">
+      <c r="Y7" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="13">
         <f t="shared" ref="AC7:AC59" si="4">IF(Y7&gt;AA7,0,AA7-Y7)</f>
         <v>0</v>
       </c>
@@ -27058,15 +27067,15 @@
       <c r="AE7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="AF7" s="40">
-        <v>27</v>
-      </c>
-      <c r="AG7" s="40">
-        <v>63</v>
-      </c>
-      <c r="AH7" s="40">
+      <c r="AF7" s="13">
+        <v>34</v>
+      </c>
+      <c r="AG7" s="13">
+        <v>64</v>
+      </c>
+      <c r="AH7" s="13">
         <f t="shared" ref="AH7:AH17" si="5">IF(AF7&gt;AG7,0,AG7-AF7)</f>
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI7" s="22"/>
       <c r="AJ7">
@@ -27110,25 +27119,22 @@
       </c>
       <c r="P8" s="5">
         <f>SUM(AA6:AA68)</f>
-        <v>2632.65</v>
+        <v>2655.54</v>
       </c>
       <c r="Q8" s="18" t="s">
         <v>77</v>
       </c>
       <c r="V8" s="7"/>
-      <c r="W8" s="42" t="s">
+      <c r="W8" t="s">
         <v>13</v>
       </c>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="40"/>
-      <c r="AA8" s="44">
+      <c r="Y8" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="14">
         <v>30</v>
       </c>
-      <c r="AB8" s="42"/>
-      <c r="AC8" s="40">
+      <c r="AC8" s="13">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
@@ -27136,13 +27142,13 @@
       <c r="AE8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="AF8" s="40">
-        <v>29</v>
-      </c>
-      <c r="AG8" s="40">
-        <v>65</v>
-      </c>
-      <c r="AH8" s="40">
+      <c r="AF8" s="13">
+        <v>27</v>
+      </c>
+      <c r="AG8" s="13">
+        <v>63</v>
+      </c>
+      <c r="AH8" s="13">
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
@@ -27189,25 +27195,22 @@
       <c r="O9" s="4"/>
       <c r="P9" s="20">
         <f>IF(P7&gt;P8,0,P8-P7)</f>
-        <v>1966.5500000000002</v>
+        <v>2003.6399999999999</v>
       </c>
       <c r="Q9" s="18" t="s">
         <v>77</v>
       </c>
       <c r="V9" s="7"/>
-      <c r="W9" s="42" t="s">
+      <c r="W9" t="s">
         <v>14</v>
       </c>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="40"/>
-      <c r="AA9" s="44">
+      <c r="Y9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="14">
         <v>68</v>
       </c>
-      <c r="AB9" s="42"/>
-      <c r="AC9" s="40">
+      <c r="AC9" s="13">
         <f t="shared" si="4"/>
         <v>68</v>
       </c>
@@ -27215,15 +27218,15 @@
       <c r="AE9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AF9" s="40">
-        <v>24</v>
-      </c>
-      <c r="AG9" s="40">
-        <v>82</v>
-      </c>
-      <c r="AH9" s="40">
+      <c r="AF9" s="13">
+        <v>29</v>
+      </c>
+      <c r="AG9" s="13">
+        <v>65</v>
+      </c>
+      <c r="AH9" s="13">
         <f t="shared" si="5"/>
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="AI9" s="22"/>
       <c r="AJ9">
@@ -27265,19 +27268,16 @@
       <c r="N10" s="7"/>
       <c r="Q10" s="22"/>
       <c r="V10" s="7"/>
-      <c r="W10" s="42" t="s">
+      <c r="W10" t="s">
         <v>16</v>
       </c>
-      <c r="X10" s="40"/>
-      <c r="Y10" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="40"/>
-      <c r="AA10" s="44">
+      <c r="Y10" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="14">
         <v>61</v>
       </c>
-      <c r="AB10" s="42"/>
-      <c r="AC10" s="40">
+      <c r="AC10" s="13">
         <f t="shared" si="4"/>
         <v>61</v>
       </c>
@@ -27285,15 +27285,15 @@
       <c r="AE10" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AF10" s="40">
-        <v>0.66610000000000003</v>
-      </c>
-      <c r="AG10" s="40">
-        <v>2.6326499999999999</v>
-      </c>
-      <c r="AH10" s="40">
+      <c r="AF10" s="13">
+        <v>24</v>
+      </c>
+      <c r="AG10" s="13">
+        <v>82</v>
+      </c>
+      <c r="AH10" s="13">
         <f t="shared" si="5"/>
-        <v>1.9665499999999998</v>
+        <v>58</v>
       </c>
       <c r="AI10" s="22"/>
       <c r="AJ10">
@@ -27339,22 +27339,19 @@
       <c r="P11" s="20"/>
       <c r="Q11" s="23">
         <f>Q15</f>
-        <v>0.2530150228856855</v>
+        <v>0.24548679364649001</v>
       </c>
       <c r="V11" s="7"/>
-      <c r="W11" s="42" t="s">
+      <c r="W11" t="s">
         <v>17</v>
       </c>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="40"/>
-      <c r="AA11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="42"/>
-      <c r="AC11" s="40">
+      <c r="Y11" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -27362,9 +27359,16 @@
       <c r="AE11" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AF11" s="40"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="40"/>
+      <c r="AF11" s="13">
+        <v>1.327</v>
+      </c>
+      <c r="AG11" s="13">
+        <v>5.2713400000000004</v>
+      </c>
+      <c r="AH11" s="13">
+        <f t="shared" si="5"/>
+        <v>3.9443400000000004</v>
+      </c>
       <c r="AI11" s="22"/>
       <c r="AJ11">
         <f t="shared" si="6"/>
@@ -27410,24 +27414,23 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="18"/>
       <c r="V12" s="7"/>
-      <c r="W12" s="42" t="s">
+      <c r="W12" t="s">
         <v>19</v>
       </c>
-      <c r="X12" s="42">
+      <c r="X12">
         <v>10</v>
       </c>
-      <c r="Y12" s="40">
+      <c r="Y12" s="13">
         <f>X12+Z12</f>
         <v>50</v>
       </c>
-      <c r="Z12" s="42">
+      <c r="Z12">
         <v>40</v>
       </c>
-      <c r="AA12" s="42">
+      <c r="AA12">
         <v>38</v>
       </c>
-      <c r="AB12" s="42"/>
-      <c r="AC12" s="40">
+      <c r="AC12" s="13">
         <f>IF(Y12&gt;AA12,0,AA12-Y12)</f>
         <v>0</v>
       </c>
@@ -27435,9 +27438,12 @@
       <c r="AE12" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="AF12" s="40"/>
-      <c r="AG12" s="40"/>
-      <c r="AH12" s="40"/>
+      <c r="AF12" s="13"/>
+      <c r="AG12" s="13"/>
+      <c r="AH12" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI12" s="22"/>
       <c r="AJ12">
         <f t="shared" si="6"/>
@@ -27482,22 +27488,19 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="23">
         <f>Q17</f>
-        <v>0.74698497711431455</v>
+        <v>0.75451320635350994</v>
       </c>
       <c r="V13" s="7"/>
-      <c r="W13" s="42" t="s">
+      <c r="W13" t="s">
         <v>20</v>
       </c>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="40"/>
-      <c r="AA13" s="44">
+      <c r="Y13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="14">
         <v>46</v>
       </c>
-      <c r="AB13" s="42"/>
-      <c r="AC13" s="40">
+      <c r="AC13" s="13">
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
@@ -27505,9 +27508,12 @@
       <c r="AE13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AF13" s="40"/>
-      <c r="AG13" s="40"/>
-      <c r="AH13" s="40"/>
+      <c r="AF13" s="13"/>
+      <c r="AG13" s="13"/>
+      <c r="AH13" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI13" s="22"/>
       <c r="AJ13">
         <f t="shared" si="6"/>
@@ -27550,19 +27556,16 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="18"/>
       <c r="V14" s="7"/>
-      <c r="W14" s="42" t="s">
+      <c r="W14" t="s">
         <v>21</v>
       </c>
-      <c r="X14" s="40"/>
-      <c r="Y14" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="40"/>
-      <c r="AA14" s="44">
+      <c r="Y14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="14">
         <v>147</v>
       </c>
-      <c r="AB14" s="42"/>
-      <c r="AC14" s="40">
+      <c r="AC14" s="13">
         <f t="shared" si="4"/>
         <v>147</v>
       </c>
@@ -27570,9 +27573,12 @@
       <c r="AE14" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AF14" s="40"/>
-      <c r="AG14" s="40"/>
-      <c r="AH14" s="40"/>
+      <c r="AF14" s="13"/>
+      <c r="AG14" s="13"/>
+      <c r="AH14" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI14" s="22"/>
       <c r="AJ14">
         <f t="shared" si="6"/>
@@ -27617,22 +27623,19 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="25">
         <f>P7/P8</f>
-        <v>0.2530150228856855</v>
+        <v>0.24548679364649001</v>
       </c>
       <c r="V15" s="7"/>
-      <c r="W15" s="42" t="s">
+      <c r="W15" t="s">
         <v>22</v>
       </c>
-      <c r="X15" s="40"/>
-      <c r="Y15" s="42">
+      <c r="Y15">
         <v>80</v>
       </c>
-      <c r="Z15" s="40"/>
-      <c r="AA15" s="44">
+      <c r="AA15" s="14">
         <v>30</v>
       </c>
-      <c r="AB15" s="42"/>
-      <c r="AC15" s="40">
+      <c r="AC15" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -27640,9 +27643,12 @@
       <c r="AE15" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AF15" s="40"/>
-      <c r="AG15" s="40"/>
-      <c r="AH15" s="40"/>
+      <c r="AF15" s="13"/>
+      <c r="AG15" s="13"/>
+      <c r="AH15" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI15" s="22"/>
       <c r="AJ15">
         <f t="shared" si="6"/>
@@ -27685,19 +27691,16 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="26"/>
       <c r="V16" s="7"/>
-      <c r="W16" s="42" t="s">
+      <c r="W16" t="s">
         <v>23</v>
       </c>
-      <c r="X16" s="40"/>
-      <c r="Y16" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="40"/>
-      <c r="AA16" s="44">
+      <c r="Y16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="14">
         <v>102</v>
       </c>
-      <c r="AB16" s="42"/>
-      <c r="AC16" s="40">
+      <c r="AC16" s="13">
         <f t="shared" si="4"/>
         <v>102</v>
       </c>
@@ -27705,9 +27708,12 @@
       <c r="AE16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="AF16" s="40"/>
-      <c r="AG16" s="40"/>
-      <c r="AH16" s="40"/>
+      <c r="AF16" s="13"/>
+      <c r="AG16" s="13"/>
+      <c r="AH16" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI16" s="22"/>
       <c r="AJ16">
         <f t="shared" si="6"/>
@@ -27758,22 +27764,19 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="25">
         <f>P9/P8</f>
-        <v>0.74698497711431455</v>
+        <v>0.75451320635350994</v>
       </c>
       <c r="V17" s="7"/>
-      <c r="W17" s="42" t="s">
+      <c r="W17" t="s">
         <v>24</v>
       </c>
-      <c r="X17" s="40"/>
-      <c r="Y17" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="40"/>
-      <c r="AA17" s="44">
+      <c r="Y17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="14">
         <v>54</v>
       </c>
-      <c r="AB17" s="42"/>
-      <c r="AC17" s="40">
+      <c r="AC17" s="13">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
@@ -27781,9 +27784,12 @@
       <c r="AE17" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="AF17" s="40"/>
-      <c r="AG17" s="40"/>
-      <c r="AH17" s="40"/>
+      <c r="AF17" s="13"/>
+      <c r="AG17" s="13"/>
+      <c r="AH17" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AI17" s="22"/>
       <c r="AJ17">
         <f t="shared" si="6"/>
@@ -27830,19 +27836,16 @@
       <c r="O18" s="3"/>
       <c r="Q18" s="27"/>
       <c r="V18" s="7"/>
-      <c r="W18" s="42" t="s">
+      <c r="W18" t="s">
         <v>25</v>
       </c>
-      <c r="X18" s="40"/>
-      <c r="Y18" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="40"/>
-      <c r="AA18" s="44">
+      <c r="Y18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="14">
         <v>172</v>
       </c>
-      <c r="AB18" s="42"/>
-      <c r="AC18" s="40">
+      <c r="AC18" s="13">
         <f t="shared" si="4"/>
         <v>172</v>
       </c>
@@ -27901,19 +27904,16 @@
       <c r="V19" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="W19" s="42" t="s">
+      <c r="W19" t="s">
         <v>26</v>
       </c>
-      <c r="X19" s="40"/>
-      <c r="Y19" s="40">
+      <c r="Y19" s="13">
         <v>10</v>
       </c>
-      <c r="Z19" s="40"/>
-      <c r="AA19" s="44">
+      <c r="AA19" s="14">
         <v>50</v>
       </c>
-      <c r="AB19" s="42"/>
-      <c r="AC19" s="40">
+      <c r="AC19" s="13">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
@@ -27962,19 +27962,16 @@
       <c r="P20" s="3"/>
       <c r="R20" s="3"/>
       <c r="V20" s="7"/>
-      <c r="W20" s="42" t="s">
+      <c r="W20" t="s">
         <v>27</v>
       </c>
-      <c r="X20" s="40"/>
-      <c r="Y20" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="40"/>
-      <c r="AA20" s="42">
+      <c r="Y20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA20">
         <v>58</v>
       </c>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="40">
+      <c r="AC20" s="13">
         <f t="shared" si="4"/>
         <v>58</v>
       </c>
@@ -28032,19 +28029,16 @@
       <c r="Q21" s="16"/>
       <c r="R21" s="3"/>
       <c r="V21" s="7"/>
-      <c r="W21" s="42" t="s">
+      <c r="W21" t="s">
         <v>28</v>
       </c>
-      <c r="X21" s="40"/>
-      <c r="Y21" s="36">
-        <v>121.1</v>
-      </c>
-      <c r="Z21" s="40"/>
-      <c r="AA21" s="42">
+      <c r="Y21" s="43">
+        <v>108.6</v>
+      </c>
+      <c r="AA21">
         <v>104</v>
       </c>
-      <c r="AB21" s="42"/>
-      <c r="AC21" s="40">
+      <c r="AC21" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -28090,19 +28084,16 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="18"/>
       <c r="V22" s="7"/>
-      <c r="W22" s="42" t="s">
+      <c r="W22" t="s">
         <v>29</v>
       </c>
-      <c r="X22" s="40"/>
-      <c r="Y22" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="40"/>
-      <c r="AA22" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="42"/>
-      <c r="AC22" s="40">
+      <c r="Y22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -28148,25 +28139,22 @@
       </c>
       <c r="P23" s="21">
         <f>'Production By Date'!B59</f>
-        <v>666.1</v>
+        <v>1327</v>
       </c>
       <c r="Q23" s="22" t="s">
         <v>77</v>
       </c>
       <c r="V23" s="7"/>
-      <c r="W23" s="42" t="s">
+      <c r="W23" t="s">
         <v>30</v>
       </c>
-      <c r="X23" s="40"/>
-      <c r="Y23" s="42">
+      <c r="Y23">
         <v>34</v>
       </c>
-      <c r="Z23" s="40"/>
-      <c r="AA23" s="44">
+      <c r="AA23" s="14">
         <v>51</v>
       </c>
-      <c r="AB23" s="42"/>
-      <c r="AC23" s="40">
+      <c r="AC23" s="13">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
@@ -28212,25 +28200,22 @@
       <c r="O24" s="4"/>
       <c r="P24" s="20">
         <f>P23/1000</f>
-        <v>0.66610000000000003</v>
+        <v>1.327</v>
       </c>
       <c r="Q24" s="18" t="s">
         <v>79</v>
       </c>
       <c r="V24" s="7"/>
-      <c r="W24" s="42" t="s">
+      <c r="W24" t="s">
         <v>31</v>
       </c>
-      <c r="X24" s="40"/>
-      <c r="Y24" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="40"/>
-      <c r="AA24" s="44">
+      <c r="Y24" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="14">
         <v>45</v>
       </c>
-      <c r="AB24" s="42"/>
-      <c r="AC24" s="40">
+      <c r="AC24" s="13">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
@@ -28277,25 +28262,22 @@
       </c>
       <c r="P25" s="5">
         <f>'Consumption By Date'!B59</f>
-        <v>2632.65</v>
+        <v>5271.34</v>
       </c>
       <c r="Q25" s="22" t="s">
         <v>77</v>
       </c>
       <c r="V25" s="7"/>
-      <c r="W25" s="42" t="s">
+      <c r="W25" t="s">
         <v>32</v>
       </c>
-      <c r="X25" s="40"/>
-      <c r="Y25" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="40"/>
-      <c r="AA25" s="44">
+      <c r="Y25" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="14">
         <v>55</v>
       </c>
-      <c r="AB25" s="42"/>
-      <c r="AC25" s="40">
+      <c r="AC25" s="13">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
@@ -28340,25 +28322,22 @@
       <c r="N26" s="7"/>
       <c r="P26" s="20">
         <f>P25/1000</f>
-        <v>2.6326499999999999</v>
+        <v>5.2713400000000004</v>
       </c>
       <c r="Q26" s="22" t="s">
         <v>79</v>
       </c>
       <c r="V26" s="7"/>
-      <c r="W26" s="42" t="s">
+      <c r="W26" t="s">
         <v>33</v>
       </c>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="42">
+      <c r="Y26" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA26">
         <v>95</v>
       </c>
-      <c r="AB26" s="42"/>
-      <c r="AC26" s="40">
+      <c r="AC26" s="13">
         <f t="shared" si="4"/>
         <v>95</v>
       </c>
@@ -28406,25 +28385,22 @@
       <c r="O27" s="4"/>
       <c r="P27" s="20">
         <f>IF(P23&gt;P25,0,P25-P23)</f>
-        <v>1966.5500000000002</v>
+        <v>3944.34</v>
       </c>
       <c r="Q27" s="22" t="s">
         <v>77</v>
       </c>
       <c r="V27" s="7"/>
-      <c r="W27" s="42" t="s">
+      <c r="W27" t="s">
         <v>34</v>
       </c>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="40"/>
-      <c r="AA27" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="42"/>
-      <c r="AC27" s="40">
+      <c r="Y27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -28469,27 +28445,24 @@
       <c r="N28" s="7"/>
       <c r="P28" s="20">
         <f>P27/1000</f>
-        <v>1.9665500000000002</v>
+        <v>3.94434</v>
       </c>
       <c r="Q28" s="22" t="s">
         <v>79</v>
       </c>
       <c r="V28" s="7"/>
-      <c r="W28" s="42" t="s">
+      <c r="W28" t="s">
         <v>35</v>
       </c>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="36">
-        <v>46.2</v>
-      </c>
-      <c r="Z28" s="40"/>
-      <c r="AA28" s="42">
+      <c r="Y28" s="43">
+        <v>42.5</v>
+      </c>
+      <c r="AA28">
         <v>56</v>
       </c>
-      <c r="AB28" s="42"/>
-      <c r="AC28" s="40">
+      <c r="AC28" s="13">
         <f t="shared" si="4"/>
-        <v>9.7999999999999972</v>
+        <v>13.5</v>
       </c>
       <c r="AD28" s="22"/>
       <c r="AJ28">
@@ -28532,19 +28505,16 @@
       <c r="N29" s="7"/>
       <c r="Q29" s="22"/>
       <c r="V29" s="7"/>
-      <c r="W29" s="42" t="s">
+      <c r="W29" t="s">
         <v>36</v>
       </c>
-      <c r="X29" s="40"/>
-      <c r="Y29" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="40"/>
-      <c r="AA29" s="44">
+      <c r="Y29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="14">
         <v>50</v>
       </c>
-      <c r="AB29" s="42"/>
-      <c r="AC29" s="40">
+      <c r="AC29" s="13">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
@@ -28575,7 +28545,7 @@
       </c>
       <c r="AQ29">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR29">
         <f t="shared" si="1"/>
@@ -28593,24 +28563,21 @@
       <c r="P30" s="20"/>
       <c r="Q30" s="23">
         <f>Q34</f>
-        <v>0.2530150228856855</v>
+        <v>0.25173864709921956</v>
       </c>
       <c r="V30" s="7"/>
-      <c r="W30" s="42" t="s">
+      <c r="W30" t="s">
         <v>37</v>
       </c>
-      <c r="X30" s="40"/>
-      <c r="Y30" s="36">
-        <v>60.8</v>
-      </c>
-      <c r="Z30" s="40"/>
-      <c r="AA30" s="45">
-        <v>63.05</v>
-      </c>
-      <c r="AB30" s="42"/>
-      <c r="AC30" s="40">
+      <c r="Y30" s="43">
+        <v>90.8</v>
+      </c>
+      <c r="AA30" s="34">
+        <v>59.12</v>
+      </c>
+      <c r="AC30" s="13">
         <f t="shared" si="4"/>
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" s="22"/>
       <c r="AJ30">
@@ -28656,21 +28623,18 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="18"/>
       <c r="V31" s="7"/>
-      <c r="W31" s="42" t="s">
+      <c r="W31" t="s">
         <v>38</v>
       </c>
-      <c r="X31" s="40"/>
-      <c r="Y31" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="40"/>
-      <c r="AA31" s="45">
-        <v>107.96</v>
-      </c>
-      <c r="AB31" s="42"/>
-      <c r="AC31" s="40">
+      <c r="Y31" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="34">
+        <v>122.93</v>
+      </c>
+      <c r="AC31" s="13">
         <f t="shared" si="4"/>
-        <v>107.96</v>
+        <v>122.93</v>
       </c>
       <c r="AD31" s="22"/>
       <c r="AJ31">
@@ -28717,22 +28681,19 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="23">
         <f>Q36</f>
-        <v>0.74698497711431455</v>
+        <v>0.74826135290078044</v>
       </c>
       <c r="V32" s="7"/>
-      <c r="W32" s="42" t="s">
+      <c r="W32" t="s">
         <v>39</v>
       </c>
-      <c r="X32" s="40"/>
-      <c r="Y32" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="40"/>
-      <c r="AA32" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="42"/>
-      <c r="AC32" s="40">
+      <c r="Y32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -28780,21 +28741,18 @@
       <c r="Q33" s="18"/>
       <c r="R33" s="3"/>
       <c r="V33" s="7"/>
-      <c r="W33" s="42" t="s">
+      <c r="W33" t="s">
         <v>40</v>
       </c>
-      <c r="X33" s="40"/>
-      <c r="Y33" s="46">
+      <c r="Y33" s="31">
         <v>10</v>
       </c>
-      <c r="Z33" s="40"/>
-      <c r="AA33" s="45">
-        <v>48.91</v>
-      </c>
-      <c r="AB33" s="42"/>
-      <c r="AC33" s="40">
+      <c r="AA33" s="34">
+        <v>58.51</v>
+      </c>
+      <c r="AC33" s="13">
         <f t="shared" si="4"/>
-        <v>38.909999999999997</v>
+        <v>48.51</v>
       </c>
       <c r="AD33" s="22"/>
       <c r="AJ33">
@@ -28841,25 +28799,22 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="25">
         <f>P23/P25</f>
-        <v>0.2530150228856855</v>
+        <v>0.25173864709921956</v>
       </c>
       <c r="R34" s="3"/>
       <c r="V34" s="7"/>
-      <c r="W34" s="42" t="s">
+      <c r="W34" t="s">
         <v>41</v>
       </c>
-      <c r="X34" s="40"/>
-      <c r="Y34" s="47">
-        <v>48</v>
-      </c>
-      <c r="Z34" s="40"/>
-      <c r="AA34" s="44">
+      <c r="Y34" s="33">
+        <v>28</v>
+      </c>
+      <c r="AA34" s="14">
         <v>29</v>
       </c>
-      <c r="AB34" s="42"/>
-      <c r="AC34" s="40">
+      <c r="AC34" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD34" s="22"/>
       <c r="AJ34">
@@ -28905,21 +28860,18 @@
       <c r="Q35" s="26"/>
       <c r="R35" s="3"/>
       <c r="V35" s="7"/>
-      <c r="W35" s="42" t="s">
+      <c r="W35" t="s">
         <v>42</v>
       </c>
-      <c r="X35" s="40"/>
-      <c r="Y35" s="40">
-        <v>42</v>
-      </c>
-      <c r="Z35" s="40"/>
-      <c r="AA35" s="44">
+      <c r="Y35" s="13">
+        <v>34</v>
+      </c>
+      <c r="AA35" s="14">
         <v>92</v>
       </c>
-      <c r="AB35" s="42"/>
-      <c r="AC35" s="40">
+      <c r="AC35" s="13">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="AD35" s="22"/>
       <c r="AJ35">
@@ -28966,23 +28918,20 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="25">
         <f>P27/P25</f>
-        <v>0.74698497711431455</v>
+        <v>0.74826135290078044</v>
       </c>
       <c r="R36" s="3"/>
       <c r="V36" s="7"/>
-      <c r="W36" s="42" t="s">
+      <c r="W36" t="s">
         <v>43</v>
       </c>
-      <c r="X36" s="40"/>
-      <c r="Y36" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="40"/>
-      <c r="AA36" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="42"/>
-      <c r="AC36" s="40">
+      <c r="Y36" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29029,19 +28978,16 @@
       <c r="Q37" s="27"/>
       <c r="R37" s="3"/>
       <c r="V37" s="7"/>
-      <c r="W37" s="42" t="s">
+      <c r="W37" t="s">
         <v>44</v>
       </c>
-      <c r="X37" s="40"/>
-      <c r="Y37" s="40">
+      <c r="Y37" s="13">
         <v>30</v>
       </c>
-      <c r="Z37" s="40"/>
-      <c r="AA37" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="42"/>
-      <c r="AC37" s="40">
+      <c r="AA37" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29089,21 +29035,19 @@
       <c r="Q38" s="29"/>
       <c r="R38" s="3"/>
       <c r="V38" s="7"/>
-      <c r="W38" s="42" t="s">
+      <c r="W38" t="s">
         <v>45</v>
       </c>
-      <c r="X38" s="40"/>
-      <c r="Y38" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="40"/>
-      <c r="AA38" s="45">
-        <v>89.19</v>
-      </c>
-      <c r="AB38" s="48"/>
-      <c r="AC38" s="40">
+      <c r="Y38" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="34">
+        <v>86.85</v>
+      </c>
+      <c r="AB38" s="39"/>
+      <c r="AC38" s="13">
         <f t="shared" si="4"/>
-        <v>89.19</v>
+        <v>86.85</v>
       </c>
       <c r="AD38" s="22"/>
       <c r="AJ38">
@@ -29146,21 +29090,19 @@
       <c r="P39" s="3"/>
       <c r="R39" s="3"/>
       <c r="V39" s="7"/>
-      <c r="W39" s="42" t="s">
+      <c r="W39" t="s">
         <v>46</v>
       </c>
-      <c r="X39" s="40"/>
-      <c r="Y39" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="40"/>
-      <c r="AA39" s="45">
-        <v>35.54</v>
-      </c>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="40">
+      <c r="Y39" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="34">
+        <v>40.130000000000003</v>
+      </c>
+      <c r="AB39" s="40"/>
+      <c r="AC39" s="13">
         <f t="shared" si="4"/>
-        <v>35.54</v>
+        <v>40.130000000000003</v>
       </c>
       <c r="AD39" s="22"/>
       <c r="AJ39">
@@ -29202,19 +29144,16 @@
       <c r="E40" s="9"/>
       <c r="P40" s="3"/>
       <c r="V40" s="7"/>
-      <c r="W40" s="42" t="s">
+      <c r="W40" t="s">
         <v>47</v>
       </c>
-      <c r="X40" s="40"/>
-      <c r="Y40" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="40"/>
-      <c r="AA40" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="42"/>
-      <c r="AC40" s="40">
+      <c r="Y40" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29257,19 +29196,16 @@
       <c r="C41" s="8"/>
       <c r="E41" s="9"/>
       <c r="V41" s="7"/>
-      <c r="W41" s="42" t="s">
+      <c r="W41" t="s">
         <v>48</v>
       </c>
-      <c r="X41" s="40"/>
-      <c r="Y41" s="40">
+      <c r="Y41" s="13">
         <v>2</v>
       </c>
-      <c r="Z41" s="40"/>
-      <c r="AA41" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="42"/>
-      <c r="AC41" s="40">
+      <c r="AA41" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29312,19 +29248,16 @@
       <c r="C42" s="8"/>
       <c r="E42" s="9"/>
       <c r="V42" s="7"/>
-      <c r="W42" s="42" t="s">
+      <c r="W42" t="s">
         <v>49</v>
       </c>
-      <c r="X42" s="40"/>
-      <c r="Y42" s="42">
+      <c r="Y42">
         <v>32</v>
       </c>
-      <c r="Z42" s="40"/>
-      <c r="AA42" s="42">
+      <c r="AA42">
         <v>60</v>
       </c>
-      <c r="AB42" s="42"/>
-      <c r="AC42" s="40">
+      <c r="AC42" s="13">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
@@ -29363,27 +29296,19 @@
       </c>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A43" s="42"/>
-      <c r="B43" s="42"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="42"/>
       <c r="E43" s="9"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
       <c r="V43" s="7"/>
-      <c r="W43" s="42" t="s">
+      <c r="W43" t="s">
         <v>50</v>
       </c>
-      <c r="X43" s="40"/>
-      <c r="Y43" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="40"/>
-      <c r="AA43" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="42"/>
-      <c r="AC43" s="40">
+      <c r="Y43" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29422,27 +29347,19 @@
       </c>
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A44" s="42"/>
-      <c r="B44" s="42"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="42"/>
       <c r="E44" s="9"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="42"/>
       <c r="V44" s="7"/>
-      <c r="W44" s="42" t="s">
+      <c r="W44" t="s">
         <v>51</v>
       </c>
-      <c r="X44" s="40"/>
-      <c r="Y44" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="40"/>
-      <c r="AA44" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="42"/>
-      <c r="AC44" s="40">
+      <c r="Y44" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29481,27 +29398,19 @@
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A45" s="42"/>
-      <c r="B45" s="42"/>
       <c r="C45" s="8"/>
-      <c r="D45" s="42"/>
       <c r="E45" s="9"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
       <c r="V45" s="7"/>
-      <c r="W45" s="42" t="s">
+      <c r="W45" t="s">
         <v>52</v>
       </c>
-      <c r="X45" s="40"/>
-      <c r="Y45" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="40"/>
-      <c r="AA45" s="44">
+      <c r="Y45" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="14">
         <v>40</v>
       </c>
-      <c r="AB45" s="42"/>
-      <c r="AC45" s="40">
+      <c r="AC45" s="13">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
@@ -29540,27 +29449,19 @@
       </c>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A46" s="42"/>
-      <c r="B46" s="42"/>
       <c r="C46" s="8"/>
-      <c r="D46" s="42"/>
       <c r="E46" s="9"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
       <c r="V46" s="7"/>
-      <c r="W46" s="42" t="s">
+      <c r="W46" t="s">
         <v>53</v>
       </c>
-      <c r="X46" s="40"/>
-      <c r="Y46" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="40"/>
-      <c r="AA46" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="42"/>
-      <c r="AC46" s="40">
+      <c r="Y46" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29599,25 +29500,16 @@
       </c>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A47" s="42"/>
-      <c r="B47" s="42"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="42"/>
       <c r="E47" s="9"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
       <c r="V47" s="7"/>
-      <c r="W47" s="42" t="s">
+      <c r="W47" t="s">
         <v>54</v>
       </c>
-      <c r="X47" s="40"/>
-      <c r="Y47" s="40"/>
-      <c r="Z47" s="40"/>
-      <c r="AA47" s="44">
+      <c r="AA47" s="14">
         <v>70</v>
       </c>
-      <c r="AB47" s="42"/>
-      <c r="AC47" s="40">
+      <c r="AC47" s="13">
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
@@ -29657,19 +29549,16 @@
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.25">
       <c r="V48" s="7"/>
-      <c r="W48" s="42" t="s">
+      <c r="W48" t="s">
         <v>55</v>
       </c>
-      <c r="X48" s="40"/>
-      <c r="Y48" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="40"/>
-      <c r="AA48" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="40">
+      <c r="Y48" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29709,19 +29598,16 @@
     </row>
     <row r="49" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V49" s="7"/>
-      <c r="W49" s="42" t="s">
+      <c r="W49" t="s">
         <v>56</v>
       </c>
-      <c r="X49" s="40"/>
-      <c r="Y49" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="40"/>
-      <c r="AA49" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="42"/>
-      <c r="AC49" s="40">
+      <c r="Y49" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29761,19 +29647,16 @@
     </row>
     <row r="50" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V50" s="7"/>
-      <c r="W50" s="42" t="s">
+      <c r="W50" t="s">
         <v>57</v>
       </c>
-      <c r="X50" s="40"/>
-      <c r="Y50" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="40"/>
-      <c r="AA50" s="44">
+      <c r="Y50" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="14">
         <v>80</v>
       </c>
-      <c r="AB50" s="42"/>
-      <c r="AC50" s="40">
+      <c r="AC50" s="13">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
@@ -29813,19 +29696,16 @@
     </row>
     <row r="51" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V51" s="7"/>
-      <c r="W51" s="42" t="s">
+      <c r="W51" t="s">
         <v>58</v>
       </c>
-      <c r="X51" s="40"/>
-      <c r="Y51" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="40"/>
-      <c r="AA51" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="42"/>
-      <c r="AC51" s="40">
+      <c r="Y51" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -29865,19 +29745,16 @@
     </row>
     <row r="52" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V52" s="7"/>
-      <c r="W52" s="42" t="s">
+      <c r="W52" t="s">
         <v>59</v>
       </c>
-      <c r="X52" s="40"/>
-      <c r="Y52" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="40"/>
-      <c r="AA52" s="44">
+      <c r="Y52" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="14">
         <v>170</v>
       </c>
-      <c r="AB52" s="42"/>
-      <c r="AC52" s="40">
+      <c r="AC52" s="13">
         <f t="shared" si="4"/>
         <v>170</v>
       </c>
@@ -29917,19 +29794,16 @@
     </row>
     <row r="53" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V53" s="7"/>
-      <c r="W53" s="42" t="s">
+      <c r="W53" t="s">
         <v>60</v>
       </c>
-      <c r="X53" s="40"/>
-      <c r="Y53" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="40"/>
-      <c r="AA53" s="44">
+      <c r="Y53" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="14">
         <v>30</v>
       </c>
-      <c r="AB53" s="42"/>
-      <c r="AC53" s="40">
+      <c r="AC53" s="13">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
@@ -29969,19 +29843,16 @@
     </row>
     <row r="54" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V54" s="7"/>
-      <c r="W54" s="42" t="s">
+      <c r="W54" t="s">
         <v>61</v>
       </c>
-      <c r="X54" s="40"/>
-      <c r="Y54" s="42">
+      <c r="Y54">
         <v>41</v>
       </c>
-      <c r="Z54" s="40"/>
-      <c r="AA54" s="42">
+      <c r="AA54">
         <v>225</v>
       </c>
-      <c r="AB54" s="42"/>
-      <c r="AC54" s="40">
+      <c r="AC54" s="13">
         <f t="shared" si="4"/>
         <v>184</v>
       </c>
@@ -30021,19 +29892,16 @@
     </row>
     <row r="55" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V55" s="7"/>
-      <c r="W55" s="42" t="s">
+      <c r="W55" t="s">
         <v>62</v>
       </c>
-      <c r="X55" s="40"/>
-      <c r="Y55" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="40"/>
-      <c r="AA55" s="44">
+      <c r="Y55" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="14">
         <v>53</v>
       </c>
-      <c r="AB55" s="42"/>
-      <c r="AC55" s="40">
+      <c r="AC55" s="13">
         <f t="shared" si="4"/>
         <v>53</v>
       </c>
@@ -30073,19 +29941,16 @@
     </row>
     <row r="56" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V56" s="7"/>
-      <c r="W56" s="42" t="s">
+      <c r="W56" t="s">
         <v>63</v>
       </c>
-      <c r="X56" s="40"/>
-      <c r="Y56" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="40"/>
-      <c r="AA56" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB56" s="42"/>
-      <c r="AC56" s="40">
+      <c r="Y56" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -30125,19 +29990,16 @@
     </row>
     <row r="57" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V57" s="7"/>
-      <c r="W57" s="42" t="s">
+      <c r="W57" t="s">
         <v>64</v>
       </c>
-      <c r="X57" s="40"/>
-      <c r="Y57" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="40"/>
-      <c r="AA57" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="42"/>
-      <c r="AC57" s="40">
+      <c r="Y57" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -30177,19 +30039,16 @@
     </row>
     <row r="58" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V58" s="7"/>
-      <c r="W58" s="42" t="s">
+      <c r="W58" t="s">
         <v>65</v>
       </c>
-      <c r="X58" s="40"/>
-      <c r="Y58" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="40"/>
-      <c r="AA58" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="42"/>
-      <c r="AC58" s="40">
+      <c r="Y58" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -30229,19 +30088,16 @@
     </row>
     <row r="59" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V59" s="7"/>
-      <c r="W59" s="42" t="s">
+      <c r="W59" t="s">
         <v>71</v>
       </c>
-      <c r="X59" s="40"/>
-      <c r="Y59" s="42">
+      <c r="Y59">
         <v>59</v>
       </c>
-      <c r="Z59" s="40"/>
-      <c r="AA59" s="42">
+      <c r="AA59">
         <v>61</v>
       </c>
-      <c r="AB59" s="42"/>
-      <c r="AC59" s="40">
+      <c r="AC59" s="13">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -30282,12 +30138,12 @@
     <row r="60" spans="22:44" x14ac:dyDescent="0.25">
       <c r="V60" s="10"/>
       <c r="W60" s="11"/>
-      <c r="X60" s="50"/>
-      <c r="Y60" s="50"/>
-      <c r="Z60" s="50"/>
-      <c r="AA60" s="50"/>
+      <c r="X60" s="41"/>
+      <c r="Y60" s="41"/>
+      <c r="Z60" s="41"/>
+      <c r="AA60" s="41"/>
       <c r="AB60" s="11"/>
-      <c r="AC60" s="50"/>
+      <c r="AC60" s="41"/>
       <c r="AD60" s="29"/>
       <c r="AJ60">
         <f t="shared" si="6"/>
@@ -30965,7 +30821,7 @@
       </c>
       <c r="AR79">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="36:44" x14ac:dyDescent="0.25">
@@ -31828,11 +31684,11 @@
       </c>
       <c r="AL105" s="13">
         <f>200-Q30*100</f>
-        <v>174.69849771143146</v>
+        <v>174.82613529007804</v>
       </c>
       <c r="AM105">
         <f>200-Q32*100</f>
-        <v>125.30150228856854</v>
+        <v>125.17386470992196</v>
       </c>
       <c r="AO105">
         <f t="shared" si="15"/>
@@ -31843,11 +31699,11 @@
       </c>
       <c r="AQ105" s="13">
         <f>200-Q11*100</f>
-        <v>174.69849771143146</v>
+        <v>175.45132063535101</v>
       </c>
       <c r="AR105">
         <f>200-Q13*100</f>
-        <v>125.30150228856854</v>
+        <v>124.548679364649</v>
       </c>
     </row>
   </sheetData>
@@ -31974,7 +31830,9 @@
       <c r="B2" s="14">
         <v>0</v>
       </c>
-      <c r="C2" s="14"/>
+      <c r="C2" s="14">
+        <v>0</v>
+      </c>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
@@ -32009,7 +31867,9 @@
       <c r="B3" s="14">
         <v>0</v>
       </c>
-      <c r="C3" s="14"/>
+      <c r="C3" s="14">
+        <v>0</v>
+      </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
@@ -32046,7 +31906,9 @@
       <c r="B4" s="14">
         <v>0</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="14">
+        <v>0</v>
+      </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
@@ -32081,7 +31943,9 @@
       <c r="B5" s="14">
         <v>0</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
@@ -32116,7 +31980,9 @@
       <c r="B6" s="14">
         <v>0</v>
       </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="14">
+        <v>0</v>
+      </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
@@ -32151,7 +32017,9 @@
       <c r="B7" s="14">
         <v>0</v>
       </c>
-      <c r="C7" s="14"/>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
@@ -32186,6 +32054,9 @@
       <c r="B8" s="13">
         <v>50</v>
       </c>
+      <c r="C8" s="13">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
@@ -32194,6 +32065,9 @@
       <c r="B9" s="13">
         <v>0</v>
       </c>
+      <c r="C9" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
@@ -32202,6 +32076,9 @@
       <c r="B10" s="13">
         <v>0</v>
       </c>
+      <c r="C10" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
@@ -32210,6 +32087,9 @@
       <c r="B11" s="13">
         <v>80</v>
       </c>
+      <c r="C11" s="13">
+        <v>80</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
@@ -32218,6 +32098,9 @@
       <c r="B12" s="13">
         <v>0</v>
       </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
@@ -32226,6 +32109,9 @@
       <c r="B13" s="13">
         <v>0</v>
       </c>
+      <c r="C13" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
@@ -32234,6 +32120,9 @@
       <c r="B14" s="13">
         <v>0</v>
       </c>
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
@@ -32242,6 +32131,9 @@
       <c r="B15" s="13">
         <v>10</v>
       </c>
+      <c r="C15" s="13">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -32250,6 +32142,9 @@
       <c r="B16" s="13">
         <v>0</v>
       </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
@@ -32258,7 +32153,9 @@
       <c r="B17" s="32">
         <v>121.1</v>
       </c>
-      <c r="C17" s="32"/>
+      <c r="C17" s="32">
+        <v>108.6</v>
+      </c>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -32293,6 +32190,9 @@
       <c r="B18" s="13">
         <v>0</v>
       </c>
+      <c r="C18" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
@@ -32301,6 +32201,9 @@
       <c r="B19" s="13">
         <v>34</v>
       </c>
+      <c r="C19" s="13">
+        <v>34</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
@@ -32309,6 +32212,9 @@
       <c r="B20" s="13">
         <v>0</v>
       </c>
+      <c r="C20" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
@@ -32317,6 +32223,9 @@
       <c r="B21" s="13">
         <v>0</v>
       </c>
+      <c r="C21" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
@@ -32325,6 +32234,9 @@
       <c r="B22" s="13">
         <v>0</v>
       </c>
+      <c r="C22" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
@@ -32333,6 +32245,9 @@
       <c r="B23" s="13">
         <v>0</v>
       </c>
+      <c r="C23" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
@@ -32341,7 +32256,9 @@
       <c r="B24" s="32">
         <v>46.2</v>
       </c>
-      <c r="C24" s="32"/>
+      <c r="C24" s="32">
+        <v>42.5</v>
+      </c>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -32376,6 +32293,9 @@
       <c r="B25" s="13">
         <v>0</v>
       </c>
+      <c r="C25" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
@@ -32384,7 +32304,9 @@
       <c r="B26" s="32">
         <v>60.8</v>
       </c>
-      <c r="C26" s="32"/>
+      <c r="C26" s="32">
+        <v>90.8</v>
+      </c>
       <c r="D26" s="32"/>
       <c r="E26" s="32"/>
       <c r="F26" s="32"/>
@@ -32419,6 +32341,9 @@
       <c r="B27" s="13">
         <v>0</v>
       </c>
+      <c r="C27" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
@@ -32427,6 +32352,9 @@
       <c r="B28" s="13">
         <v>0</v>
       </c>
+      <c r="C28" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
@@ -32435,7 +32363,9 @@
       <c r="B29" s="31">
         <v>10</v>
       </c>
-      <c r="C29" s="31"/>
+      <c r="C29" s="31">
+        <v>10</v>
+      </c>
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
@@ -32470,7 +32400,9 @@
       <c r="B30" s="33">
         <v>48</v>
       </c>
-      <c r="C30" s="33"/>
+      <c r="C30" s="33">
+        <v>36</v>
+      </c>
       <c r="D30" s="33"/>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
@@ -32505,6 +32437,9 @@
       <c r="B31" s="13">
         <v>42</v>
       </c>
+      <c r="C31" s="13">
+        <v>35</v>
+      </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
@@ -32513,129 +32448,177 @@
       <c r="B32" s="13">
         <v>0</v>
       </c>
+      <c r="C32" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>44</v>
       </c>
       <c r="B33" s="13">
         <v>30</v>
       </c>
+      <c r="C33" s="13">
+        <v>30</v>
+      </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
         <v>45</v>
       </c>
       <c r="B34" s="13">
         <v>0</v>
       </c>
+      <c r="C34" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>46</v>
       </c>
       <c r="B35" s="13">
         <v>0</v>
       </c>
+      <c r="C35" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
       <c r="B36" s="13">
         <v>0</v>
       </c>
+      <c r="C36" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>48</v>
       </c>
       <c r="B37" s="13">
         <v>2</v>
       </c>
+      <c r="C37" s="13">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>49</v>
       </c>
       <c r="B38" s="13">
         <v>32</v>
       </c>
+      <c r="C38" s="13">
+        <v>32</v>
+      </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>50</v>
       </c>
       <c r="B39" s="13">
         <v>0</v>
       </c>
+      <c r="C39" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="13">
         <v>0</v>
       </c>
+      <c r="C40" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>52</v>
       </c>
       <c r="B41" s="13">
         <v>0</v>
       </c>
+      <c r="C41" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
         <v>53</v>
       </c>
       <c r="B42" s="13">
         <v>0</v>
       </c>
+      <c r="C42" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>55</v>
       </c>
       <c r="B44" s="13">
         <v>0</v>
       </c>
+      <c r="C44" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>56</v>
       </c>
       <c r="B45" s="13">
         <v>0</v>
       </c>
+      <c r="C45" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="13">
         <v>0</v>
       </c>
+      <c r="C46" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>58</v>
       </c>
       <c r="B47" s="13">
         <v>0</v>
       </c>
+      <c r="C47" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
         <v>59</v>
       </c>
       <c r="B48" s="13">
+        <v>0</v>
+      </c>
+      <c r="C48" s="13">
         <v>0</v>
       </c>
     </row>
@@ -32646,6 +32629,9 @@
       <c r="B49" s="13">
         <v>0</v>
       </c>
+      <c r="C49" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
@@ -32654,6 +32640,9 @@
       <c r="B50" s="13">
         <v>41</v>
       </c>
+      <c r="C50" s="13">
+        <v>41</v>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
@@ -32662,6 +32651,9 @@
       <c r="B51" s="13">
         <v>0</v>
       </c>
+      <c r="C51" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
@@ -32670,6 +32662,9 @@
       <c r="B52" s="13">
         <v>0</v>
       </c>
+      <c r="C52" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
@@ -32678,6 +32673,9 @@
       <c r="B53" s="13">
         <v>0</v>
       </c>
+      <c r="C53" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
@@ -32686,6 +32684,9 @@
       <c r="B54" s="13">
         <v>0</v>
       </c>
+      <c r="C54" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
@@ -32694,6 +32695,9 @@
       <c r="B55" s="13">
         <v>59</v>
       </c>
+      <c r="C55" s="13">
+        <v>59</v>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
@@ -32705,7 +32709,7 @@
       </c>
       <c r="C57" s="13">
         <f t="shared" ref="C57:AF57" si="0">SUM(C2:C55)</f>
-        <v>0</v>
+        <v>660.90000000000009</v>
       </c>
       <c r="D57" s="13">
         <f t="shared" si="0"/>
@@ -32830,7 +32834,7 @@
       </c>
       <c r="B59" s="13">
         <f>SUM(A57:AF57)</f>
-        <v>666.1</v>
+        <v>1327</v>
       </c>
     </row>
   </sheetData>
@@ -32951,7 +32955,9 @@
       <c r="B2" s="14">
         <v>66</v>
       </c>
-      <c r="C2" s="14"/>
+      <c r="C2" s="14">
+        <v>66</v>
+      </c>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
@@ -32989,7 +32995,9 @@
       <c r="B3" s="14">
         <v>0</v>
       </c>
-      <c r="C3" s="14"/>
+      <c r="C3" s="14">
+        <v>0</v>
+      </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
@@ -33049,7 +33057,9 @@
       <c r="B4" s="14">
         <v>30</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="14">
+        <v>30</v>
+      </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
@@ -33087,7 +33097,9 @@
       <c r="B5" s="14">
         <v>68</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="14">
+        <v>68</v>
+      </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
@@ -33125,7 +33137,9 @@
       <c r="B6" s="14">
         <v>61</v>
       </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="14">
+        <v>61</v>
+      </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
@@ -33163,7 +33177,9 @@
       <c r="B7" s="14">
         <v>0</v>
       </c>
-      <c r="C7" s="14"/>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
@@ -33201,6 +33217,9 @@
       <c r="B8">
         <v>38</v>
       </c>
+      <c r="C8">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -33209,7 +33228,9 @@
       <c r="B9" s="14">
         <v>46</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="14">
+        <v>46</v>
+      </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
@@ -33247,7 +33268,9 @@
       <c r="B10" s="14">
         <v>147</v>
       </c>
-      <c r="C10" s="14"/>
+      <c r="C10" s="14">
+        <v>147</v>
+      </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
@@ -33285,7 +33308,9 @@
       <c r="B11" s="14">
         <v>30</v>
       </c>
-      <c r="C11" s="14"/>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
@@ -33323,7 +33348,9 @@
       <c r="B12" s="14">
         <v>102</v>
       </c>
-      <c r="C12" s="14"/>
+      <c r="C12" s="14">
+        <v>102</v>
+      </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
@@ -33361,7 +33388,9 @@
       <c r="B13" s="14">
         <v>54</v>
       </c>
-      <c r="C13" s="14"/>
+      <c r="C13" s="14">
+        <v>54</v>
+      </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
@@ -33399,7 +33428,9 @@
       <c r="B14" s="14">
         <v>172</v>
       </c>
-      <c r="C14" s="14"/>
+      <c r="C14" s="14">
+        <v>172</v>
+      </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
@@ -33437,7 +33468,9 @@
       <c r="B15" s="14">
         <v>50</v>
       </c>
-      <c r="C15" s="14"/>
+      <c r="C15" s="14">
+        <v>50</v>
+      </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
@@ -33475,6 +33508,9 @@
       <c r="B16">
         <v>58</v>
       </c>
+      <c r="C16">
+        <v>58</v>
+      </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -33483,6 +33519,9 @@
       <c r="B17">
         <v>104</v>
       </c>
+      <c r="C17">
+        <v>104</v>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -33491,7 +33530,9 @@
       <c r="B18" s="14">
         <v>0</v>
       </c>
-      <c r="C18" s="14"/>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
@@ -33529,7 +33570,9 @@
       <c r="B19" s="14">
         <v>51</v>
       </c>
-      <c r="C19" s="14"/>
+      <c r="C19" s="14">
+        <v>51</v>
+      </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
@@ -33567,7 +33610,9 @@
       <c r="B20" s="14">
         <v>45</v>
       </c>
-      <c r="C20" s="14"/>
+      <c r="C20" s="14">
+        <v>45</v>
+      </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
@@ -33605,7 +33650,9 @@
       <c r="B21" s="14">
         <v>55</v>
       </c>
-      <c r="C21" s="14"/>
+      <c r="C21" s="14">
+        <v>55</v>
+      </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
@@ -33643,6 +33690,9 @@
       <c r="B22">
         <v>95</v>
       </c>
+      <c r="C22">
+        <v>95</v>
+      </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -33651,7 +33701,9 @@
       <c r="B23" s="14">
         <v>0</v>
       </c>
-      <c r="C23" s="14"/>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
@@ -33689,6 +33741,9 @@
       <c r="B24">
         <v>56</v>
       </c>
+      <c r="C24">
+        <v>56</v>
+      </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -33697,7 +33752,9 @@
       <c r="B25" s="14">
         <v>50</v>
       </c>
-      <c r="C25" s="14"/>
+      <c r="C25" s="14">
+        <v>50</v>
+      </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="14"/>
@@ -33735,7 +33792,9 @@
       <c r="B26" s="34">
         <v>63.05</v>
       </c>
-      <c r="C26" s="34"/>
+      <c r="C26" s="34">
+        <v>63.05</v>
+      </c>
       <c r="D26" s="34"/>
       <c r="E26" s="34"/>
       <c r="F26" s="34"/>
@@ -33773,7 +33832,9 @@
       <c r="B27" s="34">
         <v>107.96</v>
       </c>
-      <c r="C27" s="34"/>
+      <c r="C27" s="34">
+        <v>114</v>
+      </c>
       <c r="D27" s="34"/>
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
@@ -33811,7 +33872,9 @@
       <c r="B28" s="14">
         <v>0</v>
       </c>
-      <c r="C28" s="14"/>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
@@ -33849,7 +33912,9 @@
       <c r="B29" s="34">
         <v>48.91</v>
       </c>
-      <c r="C29" s="34"/>
+      <c r="C29" s="34">
+        <v>48.91</v>
+      </c>
       <c r="D29" s="34"/>
       <c r="E29" s="34"/>
       <c r="F29" s="34"/>
@@ -33887,7 +33952,9 @@
       <c r="B30" s="14">
         <v>29</v>
       </c>
-      <c r="C30" s="14"/>
+      <c r="C30" s="14">
+        <v>29</v>
+      </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
@@ -33925,7 +33992,9 @@
       <c r="B31" s="14">
         <v>92</v>
       </c>
-      <c r="C31" s="14"/>
+      <c r="C31" s="14">
+        <v>92</v>
+      </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
@@ -33963,7 +34032,9 @@
       <c r="B32" s="14">
         <v>0</v>
       </c>
-      <c r="C32" s="14"/>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
@@ -34001,7 +34072,9 @@
       <c r="B33" s="14">
         <v>0</v>
       </c>
-      <c r="C33" s="14"/>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
@@ -34039,7 +34112,9 @@
       <c r="B34" s="34">
         <v>89.19</v>
       </c>
-      <c r="C34" s="34"/>
+      <c r="C34" s="34">
+        <v>89.19</v>
+      </c>
       <c r="D34" s="34"/>
       <c r="E34" s="34"/>
       <c r="F34" s="34"/>
@@ -34077,7 +34152,9 @@
       <c r="B35" s="34">
         <v>35.54</v>
       </c>
-      <c r="C35" s="34"/>
+      <c r="C35" s="34">
+        <v>35.54</v>
+      </c>
       <c r="D35" s="34"/>
       <c r="E35" s="34"/>
       <c r="F35" s="34"/>
@@ -34115,7 +34192,9 @@
       <c r="B36" s="14">
         <v>0</v>
       </c>
-      <c r="C36" s="14"/>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
@@ -34153,7 +34232,9 @@
       <c r="B37" s="14">
         <v>0</v>
       </c>
-      <c r="C37" s="14"/>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14"/>
@@ -34191,6 +34272,9 @@
       <c r="B38">
         <v>60</v>
       </c>
+      <c r="C38">
+        <v>60</v>
+      </c>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -34199,7 +34283,9 @@
       <c r="B39" s="14">
         <v>0</v>
       </c>
-      <c r="C39" s="14"/>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14"/>
@@ -34237,7 +34323,9 @@
       <c r="B40" s="14">
         <v>0</v>
       </c>
-      <c r="C40" s="14"/>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
@@ -34275,7 +34363,9 @@
       <c r="B41" s="14">
         <v>40</v>
       </c>
-      <c r="C41" s="14"/>
+      <c r="C41" s="14">
+        <v>40</v>
+      </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14"/>
@@ -34313,7 +34403,9 @@
       <c r="B42" s="14">
         <v>0</v>
       </c>
-      <c r="C42" s="14"/>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
@@ -34351,7 +34443,9 @@
       <c r="B43" s="14">
         <v>70</v>
       </c>
-      <c r="C43" s="14"/>
+      <c r="C43" s="14">
+        <v>70</v>
+      </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
@@ -34389,7 +34483,9 @@
       <c r="B44" s="14">
         <v>0</v>
       </c>
-      <c r="C44" s="14"/>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
@@ -34427,7 +34523,9 @@
       <c r="B45" s="14">
         <v>0</v>
       </c>
-      <c r="C45" s="14"/>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
@@ -34465,7 +34563,9 @@
       <c r="B46" s="14">
         <v>80</v>
       </c>
-      <c r="C46" s="14"/>
+      <c r="C46" s="14">
+        <v>80</v>
+      </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -34503,7 +34603,9 @@
       <c r="B47" s="14">
         <v>0</v>
       </c>
-      <c r="C47" s="14"/>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
@@ -34541,7 +34643,9 @@
       <c r="B48" s="14">
         <v>170</v>
       </c>
-      <c r="C48" s="14"/>
+      <c r="C48" s="14">
+        <v>170</v>
+      </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
@@ -34579,7 +34683,9 @@
       <c r="B49" s="14">
         <v>30</v>
       </c>
-      <c r="C49" s="14"/>
+      <c r="C49" s="14">
+        <v>30</v>
+      </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
@@ -34617,6 +34723,9 @@
       <c r="B50">
         <v>225</v>
       </c>
+      <c r="C50">
+        <v>225</v>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
@@ -34625,7 +34734,9 @@
       <c r="B51" s="14">
         <v>53</v>
       </c>
-      <c r="C51" s="14"/>
+      <c r="C51" s="14">
+        <v>53</v>
+      </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
@@ -34663,7 +34774,9 @@
       <c r="B52" s="14">
         <v>0</v>
       </c>
-      <c r="C52" s="14"/>
+      <c r="C52" s="14">
+        <v>0</v>
+      </c>
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
@@ -34701,7 +34814,9 @@
       <c r="B53" s="14">
         <v>0</v>
       </c>
-      <c r="C53" s="14"/>
+      <c r="C53" s="14">
+        <v>0</v>
+      </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
@@ -34739,7 +34854,9 @@
       <c r="B54" s="14">
         <v>0</v>
       </c>
-      <c r="C54" s="14"/>
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -34777,6 +34894,9 @@
       <c r="B55">
         <v>61</v>
       </c>
+      <c r="C55">
+        <v>61</v>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
@@ -34788,7 +34908,7 @@
       </c>
       <c r="C57" s="13">
         <f t="shared" ref="C57:AF57" si="0">SUM(C2:C55)</f>
-        <v>0</v>
+        <v>2638.69</v>
       </c>
       <c r="D57" s="13">
         <f t="shared" si="0"/>
@@ -34913,7 +35033,7 @@
       </c>
       <c r="B59">
         <f>SUM(A57:AF57)</f>
-        <v>2632.65</v>
+        <v>5271.34</v>
       </c>
     </row>
   </sheetData>

--- a/Project Zero Dashboard 1 - Copy.xlsx
+++ b/Project Zero Dashboard 1 - Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMT NUC 3\Desktop\Solar Dashboard Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D5502A-2042-4CBD-88BA-72A7314AC4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0631805-E830-4FE0-970E-7C3A1944A491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{850AF22D-85D1-4C73-981E-24580D680358}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="100">
   <si>
     <t>Average Production</t>
   </si>
@@ -330,12 +330,21 @@
   <si>
     <t>Purchase (MWh)</t>
   </si>
+  <si>
+    <t>DELAY : 5</t>
+  </si>
+  <si>
+    <t>9.8</t>
+  </si>
+  <si>
+    <t>x12</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,6 +432,12 @@
       <sz val="11"/>
       <color rgb="FF212529"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF201E3B"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -560,7 +575,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -613,6 +628,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5712,76 +5728,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -6012,7 +6028,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.00">
-                  <c:v>175.45132063535101</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10785,229 +10801,229 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0</c:v>
@@ -11085,7 +11101,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>124.548679364649</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15929,7 +15945,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -16157,7 +16173,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.00">
-                  <c:v>174.82613529007804</c:v>
+                  <c:v>175.75763458668064</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21156,7 +21172,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0</c:v>
@@ -21234,7 +21250,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>125.17386470992196</c:v>
+                  <c:v>124.24236541331938</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25489,7 +25505,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>25%</a:t>
+            <a:t>#VALUE!</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -25617,7 +25633,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>75%</a:t>
+            <a:t>#VALUE!</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -25768,7 +25784,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>75%</a:t>
+            <a:t>76%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="8800">
             <a:solidFill>
@@ -25843,7 +25859,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>25%</a:t>
+            <a:t>24%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -25918,7 +25934,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>651,90</a:t>
+            <a:t>#VALUE!</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="3600">
             <a:solidFill>
@@ -25993,7 +26009,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>1327,00</a:t>
+            <a:t>3246,70</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -26272,7 +26288,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>2003,64</a:t>
+            <a:t>#VALUE!</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -26347,7 +26363,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>3944,34</a:t>
+            <a:t>10145,97</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="6600">
             <a:solidFill>
@@ -26838,9 +26854,9 @@
         <v>0</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="19">
+      <c r="P4" s="19" t="e">
         <f>AVERAGE(Y6:Y68)</f>
-        <v>12.300000000000002</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>77</v>
@@ -26893,7 +26909,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="20">
         <f>AVERAGE(AA6:AA68)</f>
-        <v>49.176666666666669</v>
+        <v>49.306666666666665</v>
       </c>
       <c r="Q5" s="18" t="s">
         <v>77</v>
@@ -26947,13 +26963,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ5">
+      <c r="AQ5" t="e">
         <f t="shared" ref="AQ5:AQ36" si="0">IF(AO5&lt;=($Q$11*100),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AR5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR5" t="e">
         <f t="shared" ref="AR5:AR36" si="1">IF(AO5&lt;=($Q$13*100),1,0)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -26967,9 +26983,9 @@
         <v>67</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="P6" s="20">
+      <c r="P6" s="20" t="e">
         <f>IF(P4&gt;P5,0,P5-P4)</f>
-        <v>36.876666666666665</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Q6" s="18" t="s">
         <v>77</v>
@@ -27027,13 +27043,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ6">
+      <c r="AQ6" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR6" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.25">
@@ -27042,9 +27058,9 @@
       <c r="N7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="P7" s="21">
+      <c r="P7" s="21" t="e">
         <f>SUM(Y6:Y59)</f>
-        <v>651.90000000000009</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Q7" s="18" t="s">
         <v>77</v>
@@ -27102,13 +27118,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ7">
+      <c r="AQ7" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR7" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.25">
@@ -27119,7 +27135,7 @@
       </c>
       <c r="P8" s="5">
         <f>SUM(AA6:AA68)</f>
-        <v>2655.54</v>
+        <v>2662.56</v>
       </c>
       <c r="Q8" s="18" t="s">
         <v>77</v>
@@ -27177,13 +27193,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ8">
+      <c r="AQ8" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR8" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.25">
@@ -27193,9 +27209,9 @@
         <v>68</v>
       </c>
       <c r="O9" s="4"/>
-      <c r="P9" s="20">
+      <c r="P9" s="20" t="e">
         <f>IF(P7&gt;P8,0,P8-P7)</f>
-        <v>2003.6399999999999</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Q9" s="18" t="s">
         <v>77</v>
@@ -27253,13 +27269,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ9">
+      <c r="AQ9" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR9" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -27320,13 +27336,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ10">
+      <c r="AQ10" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR10" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.25">
@@ -27337,9 +27353,9 @@
       </c>
       <c r="O11" s="20"/>
       <c r="P11" s="20"/>
-      <c r="Q11" s="23">
+      <c r="Q11" s="23" t="e">
         <f>Q15</f>
-        <v>0.24548679364649001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="V11" s="7"/>
       <c r="W11" t="s">
@@ -27394,13 +27410,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ11">
+      <c r="AQ11" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR11" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.25">
@@ -27417,12 +27433,12 @@
       <c r="W12" t="s">
         <v>19</v>
       </c>
-      <c r="X12">
-        <v>10</v>
-      </c>
-      <c r="Y12" s="13">
+      <c r="X12" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y12" s="13" t="e">
         <f>X12+Z12</f>
-        <v>50</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z12">
         <v>40</v>
@@ -27430,9 +27446,9 @@
       <c r="AA12">
         <v>38</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AC12" s="13" t="e">
         <f>IF(Y12&gt;AA12,0,AA12-Y12)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AD12" s="22"/>
       <c r="AE12" s="7" t="s">
@@ -27469,13 +27485,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ12">
+      <c r="AQ12" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR12" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.25">
@@ -27486,9 +27502,9 @@
       </c>
       <c r="O13" s="24"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="23">
+      <c r="Q13" s="23" t="e">
         <f>Q17</f>
-        <v>0.75451320635350994</v>
+        <v>#VALUE!</v>
       </c>
       <c r="V13" s="7"/>
       <c r="W13" t="s">
@@ -27539,13 +27555,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ13">
+      <c r="AQ13" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR13" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.25">
@@ -27604,13 +27620,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ14">
+      <c r="AQ14" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR14" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.25">
@@ -27621,9 +27637,9 @@
       </c>
       <c r="O15" s="24"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="25">
+      <c r="Q15" s="25" t="e">
         <f>P7/P8</f>
-        <v>0.24548679364649001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="V15" s="7"/>
       <c r="W15" t="s">
@@ -27674,13 +27690,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ15">
+      <c r="AQ15" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR15" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.25">
@@ -27739,13 +27755,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ16">
+      <c r="AQ16" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR16" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.25">
@@ -27762,9 +27778,9 @@
       </c>
       <c r="O17" s="24"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="25">
+      <c r="Q17" s="25" t="e">
         <f>P9/P8</f>
-        <v>0.75451320635350994</v>
+        <v>#VALUE!</v>
       </c>
       <c r="V17" s="7"/>
       <c r="W17" t="s">
@@ -27815,13 +27831,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ17">
+      <c r="AQ17" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR17" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.25">
@@ -27879,13 +27895,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ18">
+      <c r="AQ18" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR18" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.25">
@@ -27942,13 +27958,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ19">
+      <c r="AQ19" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR19" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.25">
@@ -28000,13 +28016,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ20">
+      <c r="AQ20" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR20" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:44" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -28067,13 +28083,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ21">
+      <c r="AQ21" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR21" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.25">
@@ -28122,13 +28138,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ22">
+      <c r="AQ22" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR22" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.25">
@@ -28139,7 +28155,7 @@
       </c>
       <c r="P23" s="21">
         <f>'Production By Date'!B59</f>
-        <v>1327</v>
+        <v>3246.7000000000003</v>
       </c>
       <c r="Q23" s="22" t="s">
         <v>77</v>
@@ -28183,13 +28199,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ23">
+      <c r="AQ23" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR23" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.25">
@@ -28200,7 +28216,7 @@
       <c r="O24" s="4"/>
       <c r="P24" s="20">
         <f>P23/1000</f>
-        <v>1.327</v>
+        <v>3.2467000000000001</v>
       </c>
       <c r="Q24" s="18" t="s">
         <v>79</v>
@@ -28244,13 +28260,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ24">
+      <c r="AQ24" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR24" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.25">
@@ -28262,7 +28278,7 @@
       </c>
       <c r="P25" s="5">
         <f>'Consumption By Date'!B59</f>
-        <v>5271.34</v>
+        <v>13392.670000000002</v>
       </c>
       <c r="Q25" s="22" t="s">
         <v>77</v>
@@ -28306,13 +28322,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ25">
+      <c r="AQ25" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR25" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.25">
@@ -28322,7 +28338,7 @@
       <c r="N26" s="7"/>
       <c r="P26" s="20">
         <f>P25/1000</f>
-        <v>5.2713400000000004</v>
+        <v>13.392670000000003</v>
       </c>
       <c r="Q26" s="22" t="s">
         <v>79</v>
@@ -28366,13 +28382,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ26">
+      <c r="AQ26" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR26" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.25">
@@ -28385,7 +28401,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="20">
         <f>IF(P23&gt;P25,0,P25-P23)</f>
-        <v>3944.34</v>
+        <v>10145.970000000001</v>
       </c>
       <c r="Q27" s="22" t="s">
         <v>77</v>
@@ -28429,13 +28445,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ27">
+      <c r="AQ27" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR27">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR27" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.25">
@@ -28445,7 +28461,7 @@
       <c r="N28" s="7"/>
       <c r="P28" s="20">
         <f>P27/1000</f>
-        <v>3.94434</v>
+        <v>10.145970000000002</v>
       </c>
       <c r="Q28" s="22" t="s">
         <v>79</v>
@@ -28489,13 +28505,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ28">
+      <c r="AQ28" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AR28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR28" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.25">
@@ -28529,7 +28545,7 @@
       </c>
       <c r="AL29">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM29">
         <f t="shared" si="3"/>
@@ -28543,13 +28559,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ29">
+      <c r="AQ29" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AR29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR29" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.25">
@@ -28563,7 +28579,7 @@
       <c r="P30" s="20"/>
       <c r="Q30" s="23">
         <f>Q34</f>
-        <v>0.25173864709921956</v>
+        <v>0.24242365413319375</v>
       </c>
       <c r="V30" s="7"/>
       <c r="W30" t="s">
@@ -28573,7 +28589,7 @@
         <v>90.8</v>
       </c>
       <c r="AA30" s="34">
-        <v>59.12</v>
+        <v>56.92</v>
       </c>
       <c r="AC30" s="13">
         <f t="shared" si="4"/>
@@ -28604,13 +28620,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ30">
+      <c r="AQ30" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AR30">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR30" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.25">
@@ -28630,11 +28646,11 @@
         <v>0</v>
       </c>
       <c r="AA31" s="34">
-        <v>122.93</v>
+        <v>126.05</v>
       </c>
       <c r="AC31" s="13">
         <f t="shared" si="4"/>
-        <v>122.93</v>
+        <v>126.05</v>
       </c>
       <c r="AD31" s="22"/>
       <c r="AJ31">
@@ -28661,13 +28677,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ31">
+      <c r="AQ31" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AR31">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR31" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.25">
@@ -28681,7 +28697,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="23">
         <f>Q36</f>
-        <v>0.74826135290078044</v>
+        <v>0.75757634586680622</v>
       </c>
       <c r="V32" s="7"/>
       <c r="W32" t="s">
@@ -28722,13 +28738,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ32">
+      <c r="AQ32" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AR32">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR32" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.25">
@@ -28748,11 +28764,11 @@
         <v>10</v>
       </c>
       <c r="AA33" s="34">
-        <v>58.51</v>
+        <v>51.44</v>
       </c>
       <c r="AC33" s="13">
         <f t="shared" si="4"/>
-        <v>48.51</v>
+        <v>41.44</v>
       </c>
       <c r="AD33" s="22"/>
       <c r="AJ33">
@@ -28779,16 +28795,16 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ33">
+      <c r="AQ33" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AR33">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR33" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:44" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:44" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A34" s="7"/>
       <c r="C34" s="8"/>
       <c r="E34" s="9"/>
@@ -28799,22 +28815,22 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="25">
         <f>P23/P25</f>
-        <v>0.25173864709921956</v>
+        <v>0.24242365413319375</v>
       </c>
       <c r="R34" s="3"/>
       <c r="V34" s="7"/>
       <c r="W34" t="s">
         <v>41</v>
       </c>
-      <c r="Y34" s="33">
-        <v>28</v>
+      <c r="Y34" s="44" t="s">
+        <v>98</v>
       </c>
       <c r="AA34" s="14">
         <v>29</v>
       </c>
       <c r="AC34" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD34" s="22"/>
       <c r="AJ34">
@@ -28841,13 +28857,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ34">
+      <c r="AQ34" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AR34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR34" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.25">
@@ -28863,15 +28879,15 @@
       <c r="W35" t="s">
         <v>42</v>
       </c>
-      <c r="Y35" s="13">
-        <v>34</v>
+      <c r="Y35" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="AA35" s="14">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="AC35" s="13">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="22"/>
       <c r="AJ35">
@@ -28898,13 +28914,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ35">
+      <c r="AQ35" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AR35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR35" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.25">
@@ -28918,7 +28934,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="25">
         <f>P27/P25</f>
-        <v>0.74826135290078044</v>
+        <v>0.75757634586680622</v>
       </c>
       <c r="R36" s="3"/>
       <c r="V36" s="7"/>
@@ -28960,13 +28976,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ36">
+      <c r="AQ36" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AR36">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR36" t="e">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.25">
@@ -29016,13 +29032,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ37">
+      <c r="AQ37" t="e">
         <f t="shared" ref="AQ37:AQ68" si="8">IF(AO37&lt;=($Q$11*100),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR37">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR37" t="e">
         <f t="shared" ref="AR37:AR68" si="9">IF(AO37&lt;=($Q$13*100),1,0)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.25">
@@ -29042,12 +29058,12 @@
         <v>0</v>
       </c>
       <c r="AA38" s="34">
-        <v>86.85</v>
+        <v>62.11</v>
       </c>
       <c r="AB38" s="39"/>
       <c r="AC38" s="13">
         <f t="shared" si="4"/>
-        <v>86.85</v>
+        <v>62.11</v>
       </c>
       <c r="AD38" s="22"/>
       <c r="AJ38">
@@ -29074,13 +29090,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ38">
+      <c r="AQ38" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR38">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR38" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.25">
@@ -29097,12 +29113,12 @@
         <v>0</v>
       </c>
       <c r="AA39" s="34">
-        <v>40.130000000000003</v>
+        <v>31.04</v>
       </c>
       <c r="AB39" s="40"/>
       <c r="AC39" s="13">
         <f t="shared" si="4"/>
-        <v>40.130000000000003</v>
+        <v>31.04</v>
       </c>
       <c r="AD39" s="22"/>
       <c r="AJ39">
@@ -29129,13 +29145,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ39">
+      <c r="AQ39" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR39">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR39" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.25">
@@ -29182,13 +29198,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ40">
+      <c r="AQ40" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR40">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR40" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.25">
@@ -29234,13 +29250,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ41">
+      <c r="AQ41" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR41">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR41" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.25">
@@ -29286,13 +29302,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ42">
+      <c r="AQ42" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR42">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR42" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.25">
@@ -29337,13 +29353,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ43">
+      <c r="AQ43" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR43">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR43" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.25">
@@ -29388,13 +29404,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ44">
+      <c r="AQ44" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR44">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR44" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.25">
@@ -29439,13 +29455,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ45">
+      <c r="AQ45" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR45">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR45" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.25">
@@ -29490,13 +29506,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ46">
+      <c r="AQ46" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR46">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR46" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.25">
@@ -29538,13 +29554,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ47">
+      <c r="AQ47" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR47">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR47" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.25">
@@ -29587,13 +29603,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ48">
+      <c r="AQ48" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR48">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR48" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="49" spans="22:44" x14ac:dyDescent="0.25">
@@ -29636,13 +29652,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ49">
+      <c r="AQ49" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR49" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="50" spans="22:44" x14ac:dyDescent="0.25">
@@ -29685,13 +29701,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ50">
+      <c r="AQ50" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR50">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR50" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="51" spans="22:44" x14ac:dyDescent="0.25">
@@ -29734,13 +29750,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ51">
+      <c r="AQ51" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR51">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR51" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="22:44" x14ac:dyDescent="0.25">
@@ -29783,13 +29799,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ52">
+      <c r="AQ52" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR52">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR52" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="53" spans="22:44" x14ac:dyDescent="0.25">
@@ -29832,13 +29848,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ53">
+      <c r="AQ53" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR53">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR53" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="54" spans="22:44" x14ac:dyDescent="0.25">
@@ -29881,13 +29897,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ54">
+      <c r="AQ54" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR54">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR54" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="55" spans="22:44" x14ac:dyDescent="0.25">
@@ -29930,13 +29946,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ55">
+      <c r="AQ55" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR55">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR55" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="56" spans="22:44" x14ac:dyDescent="0.25">
@@ -29979,13 +29995,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ56">
+      <c r="AQ56" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR56">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR56" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="57" spans="22:44" x14ac:dyDescent="0.25">
@@ -30028,13 +30044,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ57">
+      <c r="AQ57" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR57">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR57" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="58" spans="22:44" x14ac:dyDescent="0.25">
@@ -30077,13 +30093,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ58">
+      <c r="AQ58" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR58">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR58" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="59" spans="22:44" x14ac:dyDescent="0.25">
@@ -30126,13 +30142,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ59">
+      <c r="AQ59" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR59">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR59" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="60" spans="22:44" x14ac:dyDescent="0.25">
@@ -30169,13 +30185,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ60">
+      <c r="AQ60" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR60">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR60" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="61" spans="22:44" x14ac:dyDescent="0.25">
@@ -30203,13 +30219,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ61">
+      <c r="AQ61" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR61">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR61" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="62" spans="22:44" x14ac:dyDescent="0.25">
@@ -30237,13 +30253,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ62">
+      <c r="AQ62" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR62">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR62" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="63" spans="22:44" x14ac:dyDescent="0.25">
@@ -30271,13 +30287,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ63">
+      <c r="AQ63" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR63">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR63" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="64" spans="22:44" x14ac:dyDescent="0.25">
@@ -30305,13 +30321,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ64">
+      <c r="AQ64" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR64">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR64" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="65" spans="36:44" x14ac:dyDescent="0.25">
@@ -30339,13 +30355,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ65">
+      <c r="AQ65" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR65">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR65" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="66" spans="36:44" x14ac:dyDescent="0.25">
@@ -30373,13 +30389,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ66">
+      <c r="AQ66" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR66">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR66" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="67" spans="36:44" x14ac:dyDescent="0.25">
@@ -30407,13 +30423,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ67">
+      <c r="AQ67" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR67">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR67" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="68" spans="36:44" x14ac:dyDescent="0.25">
@@ -30441,13 +30457,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ68">
+      <c r="AQ68" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR68">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR68" t="e">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="69" spans="36:44" x14ac:dyDescent="0.25">
@@ -30475,13 +30491,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ69">
+      <c r="AQ69" t="e">
         <f t="shared" ref="AQ69:AQ104" si="10">IF(AO69&lt;=($Q$11*100),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR69">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR69" t="e">
         <f t="shared" ref="AR69:AR104" si="11">IF(AO69&lt;=($Q$13*100),1,0)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="70" spans="36:44" x14ac:dyDescent="0.25">
@@ -30509,13 +30525,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ70">
+      <c r="AQ70" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR70">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR70" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="71" spans="36:44" x14ac:dyDescent="0.25">
@@ -30543,13 +30559,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ71">
+      <c r="AQ71" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR71">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR71" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="72" spans="36:44" x14ac:dyDescent="0.25">
@@ -30577,13 +30593,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ72">
+      <c r="AQ72" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR72">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR72" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="73" spans="36:44" x14ac:dyDescent="0.25">
@@ -30611,13 +30627,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ73">
+      <c r="AQ73" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR73">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR73" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="74" spans="36:44" x14ac:dyDescent="0.25">
@@ -30645,13 +30661,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ74">
+      <c r="AQ74" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR74" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="75" spans="36:44" x14ac:dyDescent="0.25">
@@ -30679,13 +30695,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ75">
+      <c r="AQ75" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR75">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR75" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="76" spans="36:44" x14ac:dyDescent="0.25">
@@ -30713,13 +30729,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ76">
+      <c r="AQ76" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR76">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR76" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="77" spans="36:44" x14ac:dyDescent="0.25">
@@ -30747,13 +30763,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ77">
+      <c r="AQ77" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR77">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR77" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="78" spans="36:44" x14ac:dyDescent="0.25">
@@ -30781,13 +30797,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ78">
+      <c r="AQ78" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR78">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR78" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="79" spans="36:44" x14ac:dyDescent="0.25">
@@ -30805,7 +30821,7 @@
       </c>
       <c r="AM79">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO79">
         <f t="shared" si="15"/>
@@ -30815,13 +30831,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ79">
+      <c r="AQ79" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR79">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR79" t="e">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="80" spans="36:44" x14ac:dyDescent="0.25">
@@ -30849,13 +30865,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ80">
+      <c r="AQ80" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR80">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR80" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="81" spans="36:44" x14ac:dyDescent="0.25">
@@ -30883,13 +30899,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ81">
+      <c r="AQ81" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR81">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR81" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="82" spans="36:44" x14ac:dyDescent="0.25">
@@ -30917,13 +30933,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ82">
+      <c r="AQ82" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR82">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR82" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="83" spans="36:44" x14ac:dyDescent="0.25">
@@ -30951,13 +30967,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ83">
+      <c r="AQ83" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR83">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR83" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="84" spans="36:44" x14ac:dyDescent="0.25">
@@ -30985,13 +31001,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ84">
+      <c r="AQ84" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR84">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR84" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="85" spans="36:44" x14ac:dyDescent="0.25">
@@ -31019,13 +31035,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ85">
+      <c r="AQ85" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR85">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR85" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="86" spans="36:44" x14ac:dyDescent="0.25">
@@ -31053,13 +31069,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ86">
+      <c r="AQ86" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR86">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR86" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="87" spans="36:44" x14ac:dyDescent="0.25">
@@ -31087,13 +31103,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ87">
+      <c r="AQ87" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR87">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR87" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="88" spans="36:44" x14ac:dyDescent="0.25">
@@ -31121,13 +31137,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ88">
+      <c r="AQ88" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR88">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR88" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="89" spans="36:44" x14ac:dyDescent="0.25">
@@ -31155,13 +31171,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ89">
+      <c r="AQ89" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR89">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR89" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="90" spans="36:44" x14ac:dyDescent="0.25">
@@ -31189,13 +31205,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ90">
+      <c r="AQ90" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR90">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR90" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="91" spans="36:44" x14ac:dyDescent="0.25">
@@ -31223,13 +31239,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ91">
+      <c r="AQ91" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR91">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR91" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="92" spans="36:44" x14ac:dyDescent="0.25">
@@ -31257,13 +31273,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ92">
+      <c r="AQ92" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR92">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR92" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="93" spans="36:44" x14ac:dyDescent="0.25">
@@ -31291,13 +31307,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ93">
+      <c r="AQ93" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR93">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR93" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="94" spans="36:44" x14ac:dyDescent="0.25">
@@ -31325,13 +31341,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ94">
+      <c r="AQ94" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR94">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR94" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="95" spans="36:44" x14ac:dyDescent="0.25">
@@ -31359,13 +31375,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ95">
+      <c r="AQ95" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR95">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR95" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="96" spans="36:44" x14ac:dyDescent="0.25">
@@ -31393,13 +31409,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ96">
+      <c r="AQ96" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR96">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR96" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="97" spans="36:44" x14ac:dyDescent="0.25">
@@ -31427,13 +31443,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ97">
+      <c r="AQ97" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR97">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR97" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="98" spans="36:44" x14ac:dyDescent="0.25">
@@ -31461,13 +31477,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ98">
+      <c r="AQ98" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR98">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR98" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="99" spans="36:44" x14ac:dyDescent="0.25">
@@ -31495,13 +31511,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ99">
+      <c r="AQ99" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR99">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR99" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="100" spans="36:44" x14ac:dyDescent="0.25">
@@ -31529,13 +31545,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ100">
+      <c r="AQ100" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR100">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR100" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="101" spans="36:44" x14ac:dyDescent="0.25">
@@ -31563,13 +31579,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ101">
+      <c r="AQ101" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR101">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR101" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="102" spans="36:44" x14ac:dyDescent="0.25">
@@ -31597,13 +31613,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ102">
+      <c r="AQ102" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR102">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR102" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="103" spans="36:44" x14ac:dyDescent="0.25">
@@ -31631,13 +31647,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ103">
+      <c r="AQ103" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR103">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR103" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="104" spans="36:44" x14ac:dyDescent="0.25">
@@ -31665,13 +31681,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ104">
+      <c r="AQ104" t="e">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR104">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR104" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="105" spans="36:44" x14ac:dyDescent="0.25">
@@ -31684,11 +31700,11 @@
       </c>
       <c r="AL105" s="13">
         <f>200-Q30*100</f>
-        <v>174.82613529007804</v>
+        <v>175.75763458668064</v>
       </c>
       <c r="AM105">
         <f>200-Q32*100</f>
-        <v>125.17386470992196</v>
+        <v>124.24236541331938</v>
       </c>
       <c r="AO105">
         <f t="shared" si="15"/>
@@ -31697,13 +31713,13 @@
       <c r="AP105">
         <v>100</v>
       </c>
-      <c r="AQ105" s="13">
+      <c r="AQ105" s="13" t="e">
         <f>200-Q11*100</f>
-        <v>175.45132063535101</v>
-      </c>
-      <c r="AR105">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AR105" t="e">
         <f>200-Q13*100</f>
-        <v>124.548679364649</v>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -31833,9 +31849,15 @@
       <c r="C2" s="14">
         <v>0</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+      <c r="D2" s="14">
+        <v>0</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0</v>
+      </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
@@ -31870,9 +31892,15 @@
       <c r="C3" s="14">
         <v>0</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="14">
+        <v>0</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0</v>
+      </c>
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
@@ -31909,9 +31937,15 @@
       <c r="C4" s="14">
         <v>0</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="14">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14">
+        <v>0</v>
+      </c>
+      <c r="F4" s="14">
+        <v>0</v>
+      </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
@@ -31946,9 +31980,15 @@
       <c r="C5" s="14">
         <v>0</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14">
+        <v>0</v>
+      </c>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
@@ -31983,9 +32023,15 @@
       <c r="C6" s="14">
         <v>0</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="D6" s="14">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14">
+        <v>0</v>
+      </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
@@ -32020,9 +32066,15 @@
       <c r="C7" s="14">
         <v>0</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
@@ -32057,6 +32109,15 @@
       <c r="C8" s="13">
         <v>50</v>
       </c>
+      <c r="D8" s="13">
+        <v>50</v>
+      </c>
+      <c r="E8" s="13">
+        <v>50</v>
+      </c>
+      <c r="F8" s="13">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
@@ -32068,6 +32129,15 @@
       <c r="C9" s="13">
         <v>0</v>
       </c>
+      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
@@ -32079,6 +32149,15 @@
       <c r="C10" s="13">
         <v>0</v>
       </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
@@ -32090,6 +32169,15 @@
       <c r="C11" s="13">
         <v>80</v>
       </c>
+      <c r="D11" s="13">
+        <v>80</v>
+      </c>
+      <c r="E11" s="13">
+        <v>80</v>
+      </c>
+      <c r="F11" s="13">
+        <v>80</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
@@ -32101,6 +32189,15 @@
       <c r="C12" s="13">
         <v>0</v>
       </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
@@ -32112,6 +32209,15 @@
       <c r="C13" s="13">
         <v>0</v>
       </c>
+      <c r="D13" s="13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
@@ -32123,6 +32229,15 @@
       <c r="C14" s="13">
         <v>0</v>
       </c>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
@@ -32134,6 +32249,15 @@
       <c r="C15" s="13">
         <v>10</v>
       </c>
+      <c r="D15" s="13">
+        <v>10</v>
+      </c>
+      <c r="E15" s="13">
+        <v>10</v>
+      </c>
+      <c r="F15" s="13">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -32145,6 +32269,15 @@
       <c r="C16" s="13">
         <v>0</v>
       </c>
+      <c r="D16" s="13">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
@@ -32156,9 +32289,15 @@
       <c r="C17" s="32">
         <v>108.6</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
+      <c r="D17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="E17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="F17" s="32">
+        <v>108.6</v>
+      </c>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
@@ -32193,6 +32332,15 @@
       <c r="C18" s="13">
         <v>0</v>
       </c>
+      <c r="D18" s="13">
+        <v>0</v>
+      </c>
+      <c r="E18" s="13">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
@@ -32204,6 +32352,15 @@
       <c r="C19" s="13">
         <v>34</v>
       </c>
+      <c r="D19" s="13">
+        <v>34</v>
+      </c>
+      <c r="E19" s="13">
+        <v>34</v>
+      </c>
+      <c r="F19" s="13">
+        <v>34</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
@@ -32215,6 +32372,15 @@
       <c r="C20" s="13">
         <v>0</v>
       </c>
+      <c r="D20" s="13">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
@@ -32226,6 +32392,15 @@
       <c r="C21" s="13">
         <v>0</v>
       </c>
+      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
@@ -32237,6 +32412,15 @@
       <c r="C22" s="13">
         <v>0</v>
       </c>
+      <c r="D22" s="13">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
@@ -32248,6 +32432,15 @@
       <c r="C23" s="13">
         <v>0</v>
       </c>
+      <c r="D23" s="13">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
@@ -32259,9 +32452,15 @@
       <c r="C24" s="32">
         <v>42.5</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
+      <c r="D24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="E24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="F24" s="32">
+        <v>42.5</v>
+      </c>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
       <c r="I24" s="32"/>
@@ -32296,6 +32495,15 @@
       <c r="C25" s="13">
         <v>0</v>
       </c>
+      <c r="D25" s="13">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
@@ -32307,9 +32515,15 @@
       <c r="C26" s="32">
         <v>90.8</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
+      <c r="D26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="E26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="F26" s="32">
+        <v>90.8</v>
+      </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
@@ -32344,6 +32558,15 @@
       <c r="C27" s="13">
         <v>0</v>
       </c>
+      <c r="D27" s="13">
+        <v>0</v>
+      </c>
+      <c r="E27" s="13">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
@@ -32355,6 +32578,15 @@
       <c r="C28" s="13">
         <v>0</v>
       </c>
+      <c r="D28" s="13">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
@@ -32366,9 +32598,15 @@
       <c r="C29" s="31">
         <v>10</v>
       </c>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
+      <c r="D29" s="31">
+        <v>10</v>
+      </c>
+      <c r="E29" s="31">
+        <v>10</v>
+      </c>
+      <c r="F29" s="31">
+        <v>10</v>
+      </c>
       <c r="G29" s="31"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
@@ -32403,7 +32641,9 @@
       <c r="C30" s="33">
         <v>36</v>
       </c>
-      <c r="D30" s="33"/>
+      <c r="D30" s="33">
+        <v>34</v>
+      </c>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
       <c r="G30" s="33"/>
@@ -32440,6 +32680,15 @@
       <c r="C31" s="13">
         <v>35</v>
       </c>
+      <c r="D31" s="13">
+        <v>30</v>
+      </c>
+      <c r="E31" s="13">
+        <v>43</v>
+      </c>
+      <c r="F31" s="13">
+        <v>43</v>
+      </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
@@ -32451,8 +32700,17 @@
       <c r="C32" s="13">
         <v>0</v>
       </c>
+      <c r="D32" s="13">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13">
+        <v>0</v>
+      </c>
+      <c r="F32" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>44</v>
       </c>
@@ -32462,8 +32720,17 @@
       <c r="C33" s="13">
         <v>30</v>
       </c>
+      <c r="D33" s="13">
+        <v>30</v>
+      </c>
+      <c r="E33" s="13">
+        <v>30</v>
+      </c>
+      <c r="F33" s="13">
+        <v>30</v>
+      </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
         <v>45</v>
       </c>
@@ -32473,8 +32740,17 @@
       <c r="C34" s="13">
         <v>0</v>
       </c>
+      <c r="D34" s="13">
+        <v>0</v>
+      </c>
+      <c r="E34" s="13">
+        <v>0</v>
+      </c>
+      <c r="F34" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>46</v>
       </c>
@@ -32484,8 +32760,17 @@
       <c r="C35" s="13">
         <v>0</v>
       </c>
+      <c r="D35" s="13">
+        <v>0</v>
+      </c>
+      <c r="E35" s="13">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
@@ -32495,8 +32780,17 @@
       <c r="C36" s="13">
         <v>0</v>
       </c>
+      <c r="D36" s="13">
+        <v>0</v>
+      </c>
+      <c r="E36" s="13">
+        <v>0</v>
+      </c>
+      <c r="F36" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>48</v>
       </c>
@@ -32506,8 +32800,17 @@
       <c r="C37" s="13">
         <v>2</v>
       </c>
+      <c r="D37" s="13">
+        <v>2</v>
+      </c>
+      <c r="E37" s="13">
+        <v>2</v>
+      </c>
+      <c r="F37" s="13">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>49</v>
       </c>
@@ -32517,8 +32820,17 @@
       <c r="C38" s="13">
         <v>32</v>
       </c>
+      <c r="D38" s="13">
+        <v>32</v>
+      </c>
+      <c r="E38" s="13">
+        <v>32</v>
+      </c>
+      <c r="F38" s="13">
+        <v>32</v>
+      </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>50</v>
       </c>
@@ -32528,8 +32840,17 @@
       <c r="C39" s="13">
         <v>0</v>
       </c>
+      <c r="D39" s="13">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
         <v>51</v>
       </c>
@@ -32539,8 +32860,17 @@
       <c r="C40" s="13">
         <v>0</v>
       </c>
+      <c r="D40" s="13">
+        <v>0</v>
+      </c>
+      <c r="E40" s="13">
+        <v>0</v>
+      </c>
+      <c r="F40" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>52</v>
       </c>
@@ -32550,8 +32880,17 @@
       <c r="C41" s="13">
         <v>0</v>
       </c>
+      <c r="D41" s="13">
+        <v>0</v>
+      </c>
+      <c r="E41" s="13">
+        <v>0</v>
+      </c>
+      <c r="F41" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
         <v>53</v>
       </c>
@@ -32561,13 +32900,22 @@
       <c r="C42" s="13">
         <v>0</v>
       </c>
+      <c r="D42" s="13">
+        <v>0</v>
+      </c>
+      <c r="E42" s="13">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>55</v>
       </c>
@@ -32577,8 +32925,17 @@
       <c r="C44" s="13">
         <v>0</v>
       </c>
+      <c r="D44" s="13">
+        <v>0</v>
+      </c>
+      <c r="E44" s="13">
+        <v>0</v>
+      </c>
+      <c r="F44" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>56</v>
       </c>
@@ -32588,8 +32945,17 @@
       <c r="C45" s="13">
         <v>0</v>
       </c>
+      <c r="D45" s="13">
+        <v>0</v>
+      </c>
+      <c r="E45" s="13">
+        <v>0</v>
+      </c>
+      <c r="F45" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>57</v>
       </c>
@@ -32599,8 +32965,17 @@
       <c r="C46" s="13">
         <v>0</v>
       </c>
+      <c r="D46" s="13">
+        <v>0</v>
+      </c>
+      <c r="E46" s="13">
+        <v>0</v>
+      </c>
+      <c r="F46" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>58</v>
       </c>
@@ -32610,8 +32985,17 @@
       <c r="C47" s="13">
         <v>0</v>
       </c>
+      <c r="D47" s="13">
+        <v>0</v>
+      </c>
+      <c r="E47" s="13">
+        <v>0</v>
+      </c>
+      <c r="F47" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
         <v>59</v>
       </c>
@@ -32619,6 +33003,15 @@
         <v>0</v>
       </c>
       <c r="C48" s="13">
+        <v>0</v>
+      </c>
+      <c r="D48" s="13">
+        <v>0</v>
+      </c>
+      <c r="E48" s="13">
+        <v>0</v>
+      </c>
+      <c r="F48" s="13">
         <v>0</v>
       </c>
     </row>
@@ -32632,6 +33025,15 @@
       <c r="C49" s="13">
         <v>0</v>
       </c>
+      <c r="D49" s="13">
+        <v>0</v>
+      </c>
+      <c r="E49" s="13">
+        <v>0</v>
+      </c>
+      <c r="F49" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
@@ -32643,6 +33045,15 @@
       <c r="C50" s="13">
         <v>41</v>
       </c>
+      <c r="D50" s="13">
+        <v>41</v>
+      </c>
+      <c r="E50" s="13">
+        <v>41</v>
+      </c>
+      <c r="F50" s="13">
+        <v>41</v>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
@@ -32654,6 +33065,15 @@
       <c r="C51" s="13">
         <v>0</v>
       </c>
+      <c r="D51" s="13">
+        <v>0</v>
+      </c>
+      <c r="E51" s="13">
+        <v>0</v>
+      </c>
+      <c r="F51" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
@@ -32665,6 +33085,15 @@
       <c r="C52" s="13">
         <v>0</v>
       </c>
+      <c r="D52" s="13">
+        <v>0</v>
+      </c>
+      <c r="E52" s="13">
+        <v>0</v>
+      </c>
+      <c r="F52" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
@@ -32676,6 +33105,15 @@
       <c r="C53" s="13">
         <v>0</v>
       </c>
+      <c r="D53" s="13">
+        <v>0</v>
+      </c>
+      <c r="E53" s="13">
+        <v>0</v>
+      </c>
+      <c r="F53" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
@@ -32687,6 +33125,15 @@
       <c r="C54" s="13">
         <v>0</v>
       </c>
+      <c r="D54" s="13">
+        <v>0</v>
+      </c>
+      <c r="E54" s="13">
+        <v>0</v>
+      </c>
+      <c r="F54" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
@@ -32698,6 +33145,15 @@
       <c r="C55" s="13">
         <v>59</v>
       </c>
+      <c r="D55" s="13">
+        <v>59</v>
+      </c>
+      <c r="E55" s="13">
+        <v>59</v>
+      </c>
+      <c r="F55" s="13">
+        <v>59</v>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
@@ -32713,15 +33169,15 @@
       </c>
       <c r="D57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>653.90000000000009</v>
       </c>
       <c r="E57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>632.90000000000009</v>
       </c>
       <c r="F57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>632.90000000000009</v>
       </c>
       <c r="G57" s="13">
         <f t="shared" si="0"/>
@@ -32834,7 +33290,7 @@
       </c>
       <c r="B59" s="13">
         <f>SUM(A57:AF57)</f>
-        <v>1327</v>
+        <v>3246.7000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -32958,9 +33414,15 @@
       <c r="C2" s="14">
         <v>66</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+      <c r="D2" s="14">
+        <v>66</v>
+      </c>
+      <c r="E2" s="14">
+        <v>66</v>
+      </c>
+      <c r="F2" s="14">
+        <v>66</v>
+      </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
@@ -32998,9 +33460,15 @@
       <c r="C3" s="14">
         <v>0</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="14">
+        <v>0</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0</v>
+      </c>
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
@@ -33060,9 +33528,15 @@
       <c r="C4" s="14">
         <v>30</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="14">
+        <v>30</v>
+      </c>
+      <c r="E4" s="14">
+        <v>30</v>
+      </c>
+      <c r="F4" s="14">
+        <v>30</v>
+      </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
@@ -33100,9 +33574,15 @@
       <c r="C5" s="14">
         <v>68</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="14">
+        <v>68</v>
+      </c>
+      <c r="E5" s="14">
+        <v>68</v>
+      </c>
+      <c r="F5" s="14">
+        <v>68</v>
+      </c>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
@@ -33140,9 +33620,15 @@
       <c r="C6" s="14">
         <v>61</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="D6" s="14">
+        <v>61</v>
+      </c>
+      <c r="E6" s="14">
+        <v>61</v>
+      </c>
+      <c r="F6" s="14">
+        <v>61</v>
+      </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
@@ -33180,9 +33666,15 @@
       <c r="C7" s="14">
         <v>0</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
@@ -33220,6 +33712,15 @@
       <c r="C8">
         <v>38</v>
       </c>
+      <c r="D8">
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>38</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -33231,9 +33732,15 @@
       <c r="C9" s="14">
         <v>46</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="D9" s="14">
+        <v>46</v>
+      </c>
+      <c r="E9" s="14">
+        <v>46</v>
+      </c>
+      <c r="F9" s="14">
+        <v>46</v>
+      </c>
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
@@ -33271,9 +33778,15 @@
       <c r="C10" s="14">
         <v>147</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="D10" s="14">
+        <v>147</v>
+      </c>
+      <c r="E10" s="14">
+        <v>147</v>
+      </c>
+      <c r="F10" s="14">
+        <v>147</v>
+      </c>
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
@@ -33311,9 +33824,15 @@
       <c r="C11" s="14">
         <v>30</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
+      <c r="D11" s="14">
+        <v>30</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>30</v>
+      </c>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
@@ -33351,9 +33870,15 @@
       <c r="C12" s="14">
         <v>102</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="D12" s="14">
+        <v>102</v>
+      </c>
+      <c r="E12" s="14">
+        <v>102</v>
+      </c>
+      <c r="F12" s="14">
+        <v>102</v>
+      </c>
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
@@ -33391,9 +33916,15 @@
       <c r="C13" s="14">
         <v>54</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="D13" s="14">
+        <v>54</v>
+      </c>
+      <c r="E13" s="14">
+        <v>54</v>
+      </c>
+      <c r="F13" s="14">
+        <v>54</v>
+      </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
@@ -33431,9 +33962,15 @@
       <c r="C14" s="14">
         <v>172</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="D14" s="14">
+        <v>172</v>
+      </c>
+      <c r="E14" s="14">
+        <v>172</v>
+      </c>
+      <c r="F14" s="14">
+        <v>172</v>
+      </c>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
@@ -33471,9 +34008,15 @@
       <c r="C15" s="14">
         <v>50</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
+      <c r="D15" s="14">
+        <v>50</v>
+      </c>
+      <c r="E15" s="14">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>50</v>
+      </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
@@ -33511,6 +34054,15 @@
       <c r="C16">
         <v>58</v>
       </c>
+      <c r="D16">
+        <v>58</v>
+      </c>
+      <c r="E16">
+        <v>58</v>
+      </c>
+      <c r="F16">
+        <v>58</v>
+      </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -33522,6 +34074,15 @@
       <c r="C17">
         <v>104</v>
       </c>
+      <c r="D17">
+        <v>104</v>
+      </c>
+      <c r="E17">
+        <v>104</v>
+      </c>
+      <c r="F17">
+        <v>104</v>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -33533,9 +34094,15 @@
       <c r="C18" s="14">
         <v>0</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="D18" s="14">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
@@ -33573,9 +34140,15 @@
       <c r="C19" s="14">
         <v>51</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="D19" s="14">
+        <v>51</v>
+      </c>
+      <c r="E19" s="14">
+        <v>51</v>
+      </c>
+      <c r="F19" s="14">
+        <v>51</v>
+      </c>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
@@ -33613,9 +34186,15 @@
       <c r="C20" s="14">
         <v>45</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+      <c r="D20" s="14">
+        <v>45</v>
+      </c>
+      <c r="E20" s="14">
+        <v>45</v>
+      </c>
+      <c r="F20" s="14">
+        <v>45</v>
+      </c>
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -33653,9 +34232,15 @@
       <c r="C21" s="14">
         <v>55</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
+      <c r="D21" s="14">
+        <v>55</v>
+      </c>
+      <c r="E21" s="14">
+        <v>55</v>
+      </c>
+      <c r="F21" s="14">
+        <v>55</v>
+      </c>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -33693,6 +34278,15 @@
       <c r="C22">
         <v>95</v>
       </c>
+      <c r="D22">
+        <v>95</v>
+      </c>
+      <c r="E22">
+        <v>95</v>
+      </c>
+      <c r="F22">
+        <v>95</v>
+      </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -33704,9 +34298,15 @@
       <c r="C23" s="14">
         <v>0</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="D23" s="14">
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
@@ -33744,6 +34344,15 @@
       <c r="C24">
         <v>56</v>
       </c>
+      <c r="D24">
+        <v>56</v>
+      </c>
+      <c r="E24">
+        <v>56</v>
+      </c>
+      <c r="F24">
+        <v>56</v>
+      </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -33755,9 +34364,15 @@
       <c r="C25" s="14">
         <v>50</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+      <c r="D25" s="14">
+        <v>50</v>
+      </c>
+      <c r="E25" s="14">
+        <v>50</v>
+      </c>
+      <c r="F25" s="14">
+        <v>50</v>
+      </c>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
@@ -33795,9 +34410,15 @@
       <c r="C26" s="34">
         <v>63.05</v>
       </c>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
+      <c r="D26" s="34">
+        <v>59.12</v>
+      </c>
+      <c r="E26" s="34">
+        <v>64.41</v>
+      </c>
+      <c r="F26" s="34">
+        <v>64.41</v>
+      </c>
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
       <c r="I26" s="34"/>
@@ -33835,9 +34456,15 @@
       <c r="C27" s="34">
         <v>114</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
+      <c r="D27" s="34">
+        <v>114</v>
+      </c>
+      <c r="E27" s="34">
+        <v>125.65</v>
+      </c>
+      <c r="F27" s="34">
+        <v>125.65</v>
+      </c>
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
       <c r="I27" s="34"/>
@@ -33875,9 +34502,15 @@
       <c r="C28" s="14">
         <v>0</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="D28" s="14">
+        <v>0</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
@@ -33915,9 +34548,15 @@
       <c r="C29" s="34">
         <v>48.91</v>
       </c>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
+      <c r="D29" s="34">
+        <v>58.51</v>
+      </c>
+      <c r="E29" s="34">
+        <v>58.01</v>
+      </c>
+      <c r="F29" s="34">
+        <v>58.01</v>
+      </c>
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
       <c r="I29" s="34"/>
@@ -33955,9 +34594,15 @@
       <c r="C30" s="14">
         <v>29</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
+      <c r="D30" s="14">
+        <v>29</v>
+      </c>
+      <c r="E30" s="14">
+        <v>29</v>
+      </c>
+      <c r="F30" s="14">
+        <v>29</v>
+      </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
@@ -33995,9 +34640,15 @@
       <c r="C31" s="14">
         <v>92</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
+      <c r="D31" s="14">
+        <v>139</v>
+      </c>
+      <c r="E31" s="14">
+        <v>139</v>
+      </c>
+      <c r="F31" s="14">
+        <v>139</v>
+      </c>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
@@ -34035,9 +34686,15 @@
       <c r="C32" s="14">
         <v>0</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+      <c r="D32" s="14">
+        <v>0</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
@@ -34075,9 +34732,15 @@
       <c r="C33" s="14">
         <v>0</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="D33" s="14">
+        <v>0</v>
+      </c>
+      <c r="E33" s="14">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
@@ -34115,9 +34778,15 @@
       <c r="C34" s="34">
         <v>89.19</v>
       </c>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
+      <c r="D34" s="34">
+        <v>86.85</v>
+      </c>
+      <c r="E34" s="34">
+        <v>93.9</v>
+      </c>
+      <c r="F34" s="34">
+        <v>93.9</v>
+      </c>
       <c r="G34" s="34"/>
       <c r="H34" s="34"/>
       <c r="I34" s="34"/>
@@ -34155,9 +34824,15 @@
       <c r="C35" s="34">
         <v>35.54</v>
       </c>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
+      <c r="D35" s="34">
+        <v>40.130000000000003</v>
+      </c>
+      <c r="E35" s="34">
+        <v>36.89</v>
+      </c>
+      <c r="F35" s="34">
+        <v>36.89</v>
+      </c>
       <c r="G35" s="34"/>
       <c r="H35" s="34"/>
       <c r="I35" s="34"/>
@@ -34195,9 +34870,15 @@
       <c r="C36" s="14">
         <v>0</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
+      <c r="D36" s="14">
+        <v>0</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
@@ -34235,9 +34916,15 @@
       <c r="C37" s="14">
         <v>0</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
@@ -34275,6 +34962,15 @@
       <c r="C38">
         <v>60</v>
       </c>
+      <c r="D38">
+        <v>60</v>
+      </c>
+      <c r="E38">
+        <v>60</v>
+      </c>
+      <c r="F38">
+        <v>60</v>
+      </c>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -34286,9 +34982,15 @@
       <c r="C39" s="14">
         <v>0</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
+      <c r="D39" s="14">
+        <v>0</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
@@ -34326,9 +35028,15 @@
       <c r="C40" s="14">
         <v>0</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
+      <c r="D40" s="14">
+        <v>0</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
@@ -34366,9 +35074,15 @@
       <c r="C41" s="14">
         <v>40</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+      <c r="D41" s="14">
+        <v>40</v>
+      </c>
+      <c r="E41" s="14">
+        <v>40</v>
+      </c>
+      <c r="F41" s="14">
+        <v>40</v>
+      </c>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
@@ -34406,9 +35120,15 @@
       <c r="C42" s="14">
         <v>0</v>
       </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
+      <c r="D42" s="14">
+        <v>0</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
@@ -34446,9 +35166,15 @@
       <c r="C43" s="14">
         <v>70</v>
       </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+      <c r="D43" s="14">
+        <v>70</v>
+      </c>
+      <c r="E43" s="14">
+        <v>70</v>
+      </c>
+      <c r="F43" s="14">
+        <v>70</v>
+      </c>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
@@ -34486,9 +35212,15 @@
       <c r="C44" s="14">
         <v>0</v>
       </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
+      <c r="D44" s="14">
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
@@ -34526,9 +35258,15 @@
       <c r="C45" s="14">
         <v>0</v>
       </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
+      <c r="D45" s="14">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
@@ -34566,9 +35304,15 @@
       <c r="C46" s="14">
         <v>80</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
+      <c r="D46" s="14">
+        <v>80</v>
+      </c>
+      <c r="E46" s="14">
+        <v>80</v>
+      </c>
+      <c r="F46" s="14">
+        <v>80</v>
+      </c>
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
       <c r="I46" s="14"/>
@@ -34606,9 +35350,15 @@
       <c r="C47" s="14">
         <v>0</v>
       </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
@@ -34646,9 +35396,15 @@
       <c r="C48" s="14">
         <v>170</v>
       </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
+      <c r="D48" s="14">
+        <v>170</v>
+      </c>
+      <c r="E48" s="14">
+        <v>170</v>
+      </c>
+      <c r="F48" s="14">
+        <v>170</v>
+      </c>
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
@@ -34686,9 +35442,15 @@
       <c r="C49" s="14">
         <v>30</v>
       </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
+      <c r="D49" s="14">
+        <v>30</v>
+      </c>
+      <c r="E49" s="14">
+        <v>30</v>
+      </c>
+      <c r="F49" s="14">
+        <v>30</v>
+      </c>
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
@@ -34726,6 +35488,15 @@
       <c r="C50">
         <v>225</v>
       </c>
+      <c r="D50">
+        <v>225</v>
+      </c>
+      <c r="E50">
+        <v>225</v>
+      </c>
+      <c r="F50">
+        <v>225</v>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
@@ -34737,9 +35508,15 @@
       <c r="C51" s="14">
         <v>53</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
+      <c r="D51" s="14">
+        <v>53</v>
+      </c>
+      <c r="E51" s="14">
+        <v>53</v>
+      </c>
+      <c r="F51" s="14">
+        <v>53</v>
+      </c>
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="14"/>
@@ -34777,9 +35554,15 @@
       <c r="C52" s="14">
         <v>0</v>
       </c>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="14"/>
@@ -34817,9 +35600,15 @@
       <c r="C53" s="14">
         <v>0</v>
       </c>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
@@ -34857,9 +35646,15 @@
       <c r="C54" s="14">
         <v>0</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
@@ -34897,6 +35692,15 @@
       <c r="C55">
         <v>61</v>
       </c>
+      <c r="D55">
+        <v>61</v>
+      </c>
+      <c r="E55">
+        <v>61</v>
+      </c>
+      <c r="F55">
+        <v>61</v>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
@@ -34912,15 +35716,15 @@
       </c>
       <c r="D57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2693.6099999999997</v>
       </c>
       <c r="E57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2713.8600000000006</v>
       </c>
       <c r="F57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2713.8600000000006</v>
       </c>
       <c r="G57" s="13">
         <f t="shared" si="0"/>
@@ -35033,7 +35837,7 @@
       </c>
       <c r="B59">
         <f>SUM(A57:AF57)</f>
-        <v>5271.34</v>
+        <v>13392.670000000002</v>
       </c>
     </row>
   </sheetData>

--- a/Project Zero Dashboard 1 - Copy.xlsx
+++ b/Project Zero Dashboard 1 - Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMT NUC 3\Desktop\Solar Dashboard Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0631805-E830-4FE0-970E-7C3A1944A491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1971D6-B6C7-4B50-AB04-D0705338E43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{850AF22D-85D1-4C73-981E-24580D680358}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="97">
   <si>
     <t>Average Production</t>
   </si>
@@ -329,15 +329,6 @@
   </si>
   <si>
     <t>Purchase (MWh)</t>
-  </si>
-  <si>
-    <t>DELAY : 5</t>
-  </si>
-  <si>
-    <t>9.8</t>
-  </si>
-  <si>
-    <t>x12</t>
   </si>
 </sst>
 </file>
@@ -5728,70 +5719,70 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -6028,7 +6019,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.00">
-                  <c:v>0</c:v>
+                  <c:v>177.01835827173846</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10801,235 +10792,235 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>0</c:v>
@@ -11101,7 +11092,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0</c:v>
+                  <c:v>122.98164172826152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15942,7 +15933,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -16173,7 +16164,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.00">
-                  <c:v>175.75763458668064</c:v>
+                  <c:v>176.31609484875167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21175,7 +21166,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>0</c:v>
@@ -21250,7 +21241,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>124.24236541331938</c:v>
+                  <c:v>123.68390515124833</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25505,7 +25496,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>#VALUE!</a:t>
+            <a:t>23%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -25633,7 +25624,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>#VALUE!</a:t>
+            <a:t>77%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -25934,7 +25925,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>#VALUE!</a:t>
+            <a:t>611,90</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="3600">
             <a:solidFill>
@@ -26009,7 +26000,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>3246,70</a:t>
+            <a:t>5694,30</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -26288,7 +26279,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>#VALUE!</a:t>
+            <a:t>2050,66</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -26363,7 +26354,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>10145,97</a:t>
+            <a:t>18348,61</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="6600">
             <a:solidFill>
@@ -26854,9 +26845,9 @@
         <v>0</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="19" t="e">
+      <c r="P4" s="19">
         <f>AVERAGE(Y6:Y68)</f>
-        <v>#VALUE!</v>
+        <v>11.545283018867925</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>77</v>
@@ -26963,13 +26954,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ5" t="e">
+      <c r="AQ5">
         <f t="shared" ref="AQ5:AQ36" si="0">IF(AO5&lt;=($Q$11*100),1,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR5" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR5">
         <f t="shared" ref="AR5:AR36" si="1">IF(AO5&lt;=($Q$13*100),1,0)</f>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -26983,9 +26974,9 @@
         <v>67</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="P6" s="20" t="e">
+      <c r="P6" s="20">
         <f>IF(P4&gt;P5,0,P5-P4)</f>
-        <v>#VALUE!</v>
+        <v>37.761383647798738</v>
       </c>
       <c r="Q6" s="18" t="s">
         <v>77</v>
@@ -27043,13 +27034,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ6" t="e">
+      <c r="AQ6">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR6" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR6">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.25">
@@ -27058,9 +27049,9 @@
       <c r="N7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="P7" s="21" t="e">
+      <c r="P7" s="21">
         <f>SUM(Y6:Y59)</f>
-        <v>#VALUE!</v>
+        <v>611.90000000000009</v>
       </c>
       <c r="Q7" s="18" t="s">
         <v>77</v>
@@ -27118,13 +27109,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ7" t="e">
+      <c r="AQ7">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR7" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR7">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.25">
@@ -27193,13 +27184,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ8" t="e">
+      <c r="AQ8">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR8" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR8">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.25">
@@ -27209,9 +27200,9 @@
         <v>68</v>
       </c>
       <c r="O9" s="4"/>
-      <c r="P9" s="20" t="e">
+      <c r="P9" s="20">
         <f>IF(P7&gt;P8,0,P8-P7)</f>
-        <v>#VALUE!</v>
+        <v>2050.66</v>
       </c>
       <c r="Q9" s="18" t="s">
         <v>77</v>
@@ -27269,13 +27260,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ9" t="e">
+      <c r="AQ9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR9" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR9">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -27336,13 +27327,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ10" t="e">
+      <c r="AQ10">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR10" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR10">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.25">
@@ -27353,9 +27344,9 @@
       </c>
       <c r="O11" s="20"/>
       <c r="P11" s="20"/>
-      <c r="Q11" s="23" t="e">
+      <c r="Q11" s="23">
         <f>Q15</f>
-        <v>#VALUE!</v>
+        <v>0.22981641728261526</v>
       </c>
       <c r="V11" s="7"/>
       <c r="W11" t="s">
@@ -27410,13 +27401,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ11" t="e">
+      <c r="AQ11">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR11" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR11">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.25">
@@ -27433,12 +27424,12 @@
       <c r="W12" t="s">
         <v>19</v>
       </c>
-      <c r="X12" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y12" s="13" t="e">
+      <c r="X12">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="13">
         <f>X12+Z12</f>
-        <v>#VALUE!</v>
+        <v>50</v>
       </c>
       <c r="Z12">
         <v>40</v>
@@ -27446,9 +27437,9 @@
       <c r="AA12">
         <v>38</v>
       </c>
-      <c r="AC12" s="13" t="e">
+      <c r="AC12" s="13">
         <f>IF(Y12&gt;AA12,0,AA12-Y12)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="22"/>
       <c r="AE12" s="7" t="s">
@@ -27485,13 +27476,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ12" t="e">
+      <c r="AQ12">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR12" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR12">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.25">
@@ -27502,9 +27493,9 @@
       </c>
       <c r="O13" s="24"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="23" t="e">
+      <c r="Q13" s="23">
         <f>Q17</f>
-        <v>#VALUE!</v>
+        <v>0.77018358271738474</v>
       </c>
       <c r="V13" s="7"/>
       <c r="W13" t="s">
@@ -27555,13 +27546,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ13" t="e">
+      <c r="AQ13">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR13" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR13">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.25">
@@ -27620,13 +27611,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ14" t="e">
+      <c r="AQ14">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR14" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR14">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.25">
@@ -27637,9 +27628,9 @@
       </c>
       <c r="O15" s="24"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="25" t="e">
+      <c r="Q15" s="25">
         <f>P7/P8</f>
-        <v>#VALUE!</v>
+        <v>0.22981641728261526</v>
       </c>
       <c r="V15" s="7"/>
       <c r="W15" t="s">
@@ -27690,13 +27681,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ15" t="e">
+      <c r="AQ15">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR15" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR15">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.25">
@@ -27755,13 +27746,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ16" t="e">
+      <c r="AQ16">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR16" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR16">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.25">
@@ -27778,9 +27769,9 @@
       </c>
       <c r="O17" s="24"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="25" t="e">
+      <c r="Q17" s="25">
         <f>P9/P8</f>
-        <v>#VALUE!</v>
+        <v>0.77018358271738474</v>
       </c>
       <c r="V17" s="7"/>
       <c r="W17" t="s">
@@ -27831,13 +27822,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ17" t="e">
+      <c r="AQ17">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR17" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR17">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.25">
@@ -27895,13 +27886,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ18" t="e">
+      <c r="AQ18">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR18" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR18">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.25">
@@ -27958,13 +27949,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ19" t="e">
+      <c r="AQ19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR19" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR19">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.25">
@@ -28016,13 +28007,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ20" t="e">
+      <c r="AQ20">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR20" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR20">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:44" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -28083,13 +28074,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ21" t="e">
+      <c r="AQ21">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR21" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR21">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.25">
@@ -28138,13 +28129,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ22" t="e">
+      <c r="AQ22">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR22" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR22">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.25">
@@ -28155,7 +28146,7 @@
       </c>
       <c r="P23" s="21">
         <f>'Production By Date'!B59</f>
-        <v>3246.7000000000003</v>
+        <v>5694.2999999999993</v>
       </c>
       <c r="Q23" s="22" t="s">
         <v>77</v>
@@ -28199,13 +28190,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ23" t="e">
+      <c r="AQ23">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR23" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR23">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.25">
@@ -28216,7 +28207,7 @@
       <c r="O24" s="4"/>
       <c r="P24" s="20">
         <f>P23/1000</f>
-        <v>3.2467000000000001</v>
+        <v>5.6942999999999993</v>
       </c>
       <c r="Q24" s="18" t="s">
         <v>79</v>
@@ -28260,13 +28251,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ24" t="e">
+      <c r="AQ24">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR24" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR24">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.25">
@@ -28278,7 +28269,7 @@
       </c>
       <c r="P25" s="5">
         <f>'Consumption By Date'!B59</f>
-        <v>13392.670000000002</v>
+        <v>24042.910000000003</v>
       </c>
       <c r="Q25" s="22" t="s">
         <v>77</v>
@@ -28322,13 +28313,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ25" t="e">
+      <c r="AQ25">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR25" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR25">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.25">
@@ -28338,7 +28329,7 @@
       <c r="N26" s="7"/>
       <c r="P26" s="20">
         <f>P25/1000</f>
-        <v>13.392670000000003</v>
+        <v>24.042910000000003</v>
       </c>
       <c r="Q26" s="22" t="s">
         <v>79</v>
@@ -28382,13 +28373,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ26" t="e">
+      <c r="AQ26">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR26" t="e">
+        <v>1</v>
+      </c>
+      <c r="AR26">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.25">
@@ -28401,7 +28392,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="20">
         <f>IF(P23&gt;P25,0,P25-P23)</f>
-        <v>10145.970000000001</v>
+        <v>18348.610000000004</v>
       </c>
       <c r="Q27" s="22" t="s">
         <v>77</v>
@@ -28445,13 +28436,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ27" t="e">
+      <c r="AQ27">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR27" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR27">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.25">
@@ -28461,7 +28452,7 @@
       <c r="N28" s="7"/>
       <c r="P28" s="20">
         <f>P27/1000</f>
-        <v>10.145970000000002</v>
+        <v>18.348610000000004</v>
       </c>
       <c r="Q28" s="22" t="s">
         <v>79</v>
@@ -28491,7 +28482,7 @@
       </c>
       <c r="AL28">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM28">
         <f t="shared" si="3"/>
@@ -28505,13 +28496,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ28" t="e">
+      <c r="AQ28">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR28" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR28">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.25">
@@ -28559,13 +28550,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ29" t="e">
+      <c r="AQ29">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR29" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR29">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.25">
@@ -28579,7 +28570,7 @@
       <c r="P30" s="20"/>
       <c r="Q30" s="23">
         <f>Q34</f>
-        <v>0.24242365413319375</v>
+        <v>0.23683905151248325</v>
       </c>
       <c r="V30" s="7"/>
       <c r="W30" t="s">
@@ -28620,13 +28611,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ30" t="e">
+      <c r="AQ30">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR30" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR30">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.25">
@@ -28677,13 +28668,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ31" t="e">
+      <c r="AQ31">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR31" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR31">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.25">
@@ -28697,7 +28688,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="23">
         <f>Q36</f>
-        <v>0.75757634586680622</v>
+        <v>0.76316094848751681</v>
       </c>
       <c r="V32" s="7"/>
       <c r="W32" t="s">
@@ -28738,13 +28729,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ32" t="e">
+      <c r="AQ32">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR32" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR32">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.25">
@@ -28795,13 +28786,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ33" t="e">
+      <c r="AQ33">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR33" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR33">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:44" ht="26.25" x14ac:dyDescent="0.45">
@@ -28815,22 +28806,22 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="25">
         <f>P23/P25</f>
-        <v>0.24242365413319375</v>
+        <v>0.23683905151248325</v>
       </c>
       <c r="R34" s="3"/>
       <c r="V34" s="7"/>
       <c r="W34" t="s">
         <v>41</v>
       </c>
-      <c r="Y34" s="44" t="s">
-        <v>98</v>
+      <c r="Y34" s="44">
+        <v>10</v>
       </c>
       <c r="AA34" s="14">
         <v>29</v>
       </c>
       <c r="AC34" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AD34" s="22"/>
       <c r="AJ34">
@@ -28857,13 +28848,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ34" t="e">
+      <c r="AQ34">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR34" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR34">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.25">
@@ -28879,15 +28870,15 @@
       <c r="W35" t="s">
         <v>42</v>
       </c>
-      <c r="Y35" s="13" t="s">
-        <v>99</v>
+      <c r="Y35" s="13">
+        <v>12</v>
       </c>
       <c r="AA35" s="14">
         <v>139</v>
       </c>
       <c r="AC35" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="AD35" s="22"/>
       <c r="AJ35">
@@ -28914,13 +28905,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ35" t="e">
+      <c r="AQ35">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR35" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR35">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.25">
@@ -28934,7 +28925,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="25">
         <f>P27/P25</f>
-        <v>0.75757634586680622</v>
+        <v>0.76316094848751681</v>
       </c>
       <c r="R36" s="3"/>
       <c r="V36" s="7"/>
@@ -28976,13 +28967,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ36" t="e">
+      <c r="AQ36">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR36" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR36">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.25">
@@ -29032,13 +29023,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ37" t="e">
+      <c r="AQ37">
         <f t="shared" ref="AQ37:AQ68" si="8">IF(AO37&lt;=($Q$11*100),1,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR37" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR37">
         <f t="shared" ref="AR37:AR68" si="9">IF(AO37&lt;=($Q$13*100),1,0)</f>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.25">
@@ -29090,13 +29081,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ38" t="e">
+      <c r="AQ38">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR38" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR38">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.25">
@@ -29145,13 +29136,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ39" t="e">
+      <c r="AQ39">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR39" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR39">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.25">
@@ -29198,13 +29189,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ40" t="e">
+      <c r="AQ40">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR40" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR40">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.25">
@@ -29250,13 +29241,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ41" t="e">
+      <c r="AQ41">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR41" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR41">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.25">
@@ -29302,13 +29293,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ42" t="e">
+      <c r="AQ42">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR42" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR42">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.25">
@@ -29353,13 +29344,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ43" t="e">
+      <c r="AQ43">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR43" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR43">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.25">
@@ -29404,13 +29395,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ44" t="e">
+      <c r="AQ44">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR44" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR44">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.25">
@@ -29455,13 +29446,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ45" t="e">
+      <c r="AQ45">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR45" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR45">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.25">
@@ -29506,13 +29497,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ46" t="e">
+      <c r="AQ46">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR46" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR46">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.25">
@@ -29554,13 +29545,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ47" t="e">
+      <c r="AQ47">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR47" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR47">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.25">
@@ -29603,13 +29594,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ48" t="e">
+      <c r="AQ48">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR48" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR48">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="22:44" x14ac:dyDescent="0.25">
@@ -29652,13 +29643,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ49" t="e">
+      <c r="AQ49">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR49" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR49">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="22:44" x14ac:dyDescent="0.25">
@@ -29701,13 +29692,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ50" t="e">
+      <c r="AQ50">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR50" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR50">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="22:44" x14ac:dyDescent="0.25">
@@ -29750,13 +29741,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ51" t="e">
+      <c r="AQ51">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR51" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR51">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="22:44" x14ac:dyDescent="0.25">
@@ -29799,13 +29790,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ52" t="e">
+      <c r="AQ52">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR52" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR52">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="22:44" x14ac:dyDescent="0.25">
@@ -29848,13 +29839,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ53" t="e">
+      <c r="AQ53">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR53" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR53">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="22:44" x14ac:dyDescent="0.25">
@@ -29897,13 +29888,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ54" t="e">
+      <c r="AQ54">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR54" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR54">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="22:44" x14ac:dyDescent="0.25">
@@ -29946,13 +29937,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ55" t="e">
+      <c r="AQ55">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR55" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR55">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="22:44" x14ac:dyDescent="0.25">
@@ -29995,13 +29986,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ56" t="e">
+      <c r="AQ56">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR56" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR56">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="22:44" x14ac:dyDescent="0.25">
@@ -30044,13 +30035,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ57" t="e">
+      <c r="AQ57">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR57" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR57">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="22:44" x14ac:dyDescent="0.25">
@@ -30093,13 +30084,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ58" t="e">
+      <c r="AQ58">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR58" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR58">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="22:44" x14ac:dyDescent="0.25">
@@ -30142,13 +30133,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ59" t="e">
+      <c r="AQ59">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR59" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR59">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="22:44" x14ac:dyDescent="0.25">
@@ -30185,13 +30176,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ60" t="e">
+      <c r="AQ60">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR60" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR60">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="22:44" x14ac:dyDescent="0.25">
@@ -30219,13 +30210,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ61" t="e">
+      <c r="AQ61">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR61" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR61">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="22:44" x14ac:dyDescent="0.25">
@@ -30253,13 +30244,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ62" t="e">
+      <c r="AQ62">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR62" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR62">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="22:44" x14ac:dyDescent="0.25">
@@ -30287,13 +30278,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ63" t="e">
+      <c r="AQ63">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR63" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR63">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="22:44" x14ac:dyDescent="0.25">
@@ -30321,13 +30312,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ64" t="e">
+      <c r="AQ64">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR64" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR64">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="36:44" x14ac:dyDescent="0.25">
@@ -30355,13 +30346,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ65" t="e">
+      <c r="AQ65">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR65" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR65">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="36:44" x14ac:dyDescent="0.25">
@@ -30389,13 +30380,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ66" t="e">
+      <c r="AQ66">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR66" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR66">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="36:44" x14ac:dyDescent="0.25">
@@ -30423,13 +30414,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ67" t="e">
+      <c r="AQ67">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR67" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR67">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="36:44" x14ac:dyDescent="0.25">
@@ -30457,13 +30448,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ68" t="e">
+      <c r="AQ68">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR68" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR68">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="36:44" x14ac:dyDescent="0.25">
@@ -30491,13 +30482,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ69" t="e">
+      <c r="AQ69">
         <f t="shared" ref="AQ69:AQ104" si="10">IF(AO69&lt;=($Q$11*100),1,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR69" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR69">
         <f t="shared" ref="AR69:AR104" si="11">IF(AO69&lt;=($Q$13*100),1,0)</f>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="36:44" x14ac:dyDescent="0.25">
@@ -30525,13 +30516,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ70" t="e">
+      <c r="AQ70">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR70" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR70">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="36:44" x14ac:dyDescent="0.25">
@@ -30559,13 +30550,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ71" t="e">
+      <c r="AQ71">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR71" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR71">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="36:44" x14ac:dyDescent="0.25">
@@ -30593,13 +30584,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ72" t="e">
+      <c r="AQ72">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR72" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR72">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="36:44" x14ac:dyDescent="0.25">
@@ -30627,13 +30618,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ73" t="e">
+      <c r="AQ73">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR73" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR73">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="36:44" x14ac:dyDescent="0.25">
@@ -30661,13 +30652,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ74" t="e">
+      <c r="AQ74">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR74" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR74">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="36:44" x14ac:dyDescent="0.25">
@@ -30695,13 +30686,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ75" t="e">
+      <c r="AQ75">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR75" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR75">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="36:44" x14ac:dyDescent="0.25">
@@ -30729,13 +30720,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ76" t="e">
+      <c r="AQ76">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR76" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR76">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="36:44" x14ac:dyDescent="0.25">
@@ -30763,13 +30754,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ77" t="e">
+      <c r="AQ77">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR77" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR77">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="36:44" x14ac:dyDescent="0.25">
@@ -30797,13 +30788,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ78" t="e">
+      <c r="AQ78">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR78" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR78">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="36:44" x14ac:dyDescent="0.25">
@@ -30831,13 +30822,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ79" t="e">
+      <c r="AQ79">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR79" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR79">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="36:44" x14ac:dyDescent="0.25">
@@ -30855,7 +30846,7 @@
       </c>
       <c r="AM80">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO80">
         <f t="shared" si="15"/>
@@ -30865,13 +30856,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ80" t="e">
+      <c r="AQ80">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR80" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR80">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="36:44" x14ac:dyDescent="0.25">
@@ -30899,13 +30890,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ81" t="e">
+      <c r="AQ81">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR81" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR81">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="36:44" x14ac:dyDescent="0.25">
@@ -30933,13 +30924,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ82" t="e">
+      <c r="AQ82">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR82" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR82">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="36:44" x14ac:dyDescent="0.25">
@@ -30967,13 +30958,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ83" t="e">
+      <c r="AQ83">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR83" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR83">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="36:44" x14ac:dyDescent="0.25">
@@ -31001,13 +30992,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ84" t="e">
+      <c r="AQ84">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR84" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR84">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="36:44" x14ac:dyDescent="0.25">
@@ -31035,13 +31026,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ85" t="e">
+      <c r="AQ85">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR85" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR85">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="36:44" x14ac:dyDescent="0.25">
@@ -31069,13 +31060,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ86" t="e">
+      <c r="AQ86">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR86" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR86">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="36:44" x14ac:dyDescent="0.25">
@@ -31103,13 +31094,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ87" t="e">
+      <c r="AQ87">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR87" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR87">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="36:44" x14ac:dyDescent="0.25">
@@ -31137,13 +31128,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ88" t="e">
+      <c r="AQ88">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR88" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR88">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="36:44" x14ac:dyDescent="0.25">
@@ -31171,13 +31162,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ89" t="e">
+      <c r="AQ89">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR89" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR89">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="36:44" x14ac:dyDescent="0.25">
@@ -31205,13 +31196,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ90" t="e">
+      <c r="AQ90">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR90" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR90">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="36:44" x14ac:dyDescent="0.25">
@@ -31239,13 +31230,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ91" t="e">
+      <c r="AQ91">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR91" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR91">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="36:44" x14ac:dyDescent="0.25">
@@ -31273,13 +31264,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ92" t="e">
+      <c r="AQ92">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR92" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR92">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="36:44" x14ac:dyDescent="0.25">
@@ -31307,13 +31298,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ93" t="e">
+      <c r="AQ93">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR93" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR93">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="36:44" x14ac:dyDescent="0.25">
@@ -31341,13 +31332,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ94" t="e">
+      <c r="AQ94">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR94" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR94">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="36:44" x14ac:dyDescent="0.25">
@@ -31375,13 +31366,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ95" t="e">
+      <c r="AQ95">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR95" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR95">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="36:44" x14ac:dyDescent="0.25">
@@ -31409,13 +31400,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ96" t="e">
+      <c r="AQ96">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR96" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR96">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="36:44" x14ac:dyDescent="0.25">
@@ -31443,13 +31434,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ97" t="e">
+      <c r="AQ97">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR97" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR97">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="36:44" x14ac:dyDescent="0.25">
@@ -31477,13 +31468,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ98" t="e">
+      <c r="AQ98">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR98" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR98">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="36:44" x14ac:dyDescent="0.25">
@@ -31511,13 +31502,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ99" t="e">
+      <c r="AQ99">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR99" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR99">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="36:44" x14ac:dyDescent="0.25">
@@ -31545,13 +31536,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ100" t="e">
+      <c r="AQ100">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR100" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR100">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="36:44" x14ac:dyDescent="0.25">
@@ -31579,13 +31570,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ101" t="e">
+      <c r="AQ101">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR101" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR101">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="36:44" x14ac:dyDescent="0.25">
@@ -31613,13 +31604,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ102" t="e">
+      <c r="AQ102">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR102" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR102">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="36:44" x14ac:dyDescent="0.25">
@@ -31647,13 +31638,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ103" t="e">
+      <c r="AQ103">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR103" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR103">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="36:44" x14ac:dyDescent="0.25">
@@ -31681,13 +31672,13 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="AQ104" t="e">
+      <c r="AQ104">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR104" t="e">
+        <v>0</v>
+      </c>
+      <c r="AR104">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="36:44" x14ac:dyDescent="0.25">
@@ -31700,11 +31691,11 @@
       </c>
       <c r="AL105" s="13">
         <f>200-Q30*100</f>
-        <v>175.75763458668064</v>
+        <v>176.31609484875167</v>
       </c>
       <c r="AM105">
         <f>200-Q32*100</f>
-        <v>124.24236541331938</v>
+        <v>123.68390515124833</v>
       </c>
       <c r="AO105">
         <f t="shared" si="15"/>
@@ -31713,13 +31704,13 @@
       <c r="AP105">
         <v>100</v>
       </c>
-      <c r="AQ105" s="13" t="e">
+      <c r="AQ105" s="13">
         <f>200-Q11*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AR105" t="e">
+        <v>177.01835827173846</v>
+      </c>
+      <c r="AR105">
         <f>200-Q13*100</f>
-        <v>#VALUE!</v>
+        <v>122.98164172826152</v>
       </c>
     </row>
   </sheetData>
@@ -31858,10 +31849,18 @@
       <c r="F2" s="14">
         <v>0</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="G2" s="14">
+        <v>0</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0</v>
+      </c>
+      <c r="I2" s="14">
+        <v>0</v>
+      </c>
+      <c r="J2" s="14">
+        <v>0</v>
+      </c>
       <c r="K2" s="14"/>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
@@ -31901,10 +31900,18 @@
       <c r="F3" s="14">
         <v>0</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14">
+        <v>0</v>
+      </c>
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
@@ -31946,10 +31953,18 @@
       <c r="F4" s="14">
         <v>0</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
+      <c r="G4" s="14">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14">
+        <v>0</v>
+      </c>
       <c r="K4" s="14"/>
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
@@ -31989,10 +32004,18 @@
       <c r="F5" s="14">
         <v>0</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="G5" s="14">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
+        <v>0</v>
+      </c>
       <c r="K5" s="14"/>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
@@ -32032,10 +32055,18 @@
       <c r="F6" s="14">
         <v>0</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="G6" s="14">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14">
+        <v>0</v>
+      </c>
       <c r="K6" s="14"/>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
@@ -32075,10 +32106,18 @@
       <c r="F7" s="14">
         <v>0</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14">
+        <v>0</v>
+      </c>
       <c r="K7" s="14"/>
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
@@ -32118,6 +32157,18 @@
       <c r="F8" s="13">
         <v>50</v>
       </c>
+      <c r="G8" s="13">
+        <v>50</v>
+      </c>
+      <c r="H8" s="13">
+        <v>50</v>
+      </c>
+      <c r="I8" s="13">
+        <v>50</v>
+      </c>
+      <c r="J8" s="13">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
@@ -32138,6 +32189,18 @@
       <c r="F9" s="13">
         <v>0</v>
       </c>
+      <c r="G9" s="13">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
@@ -32158,6 +32221,18 @@
       <c r="F10" s="13">
         <v>0</v>
       </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
@@ -32178,6 +32253,18 @@
       <c r="F11" s="13">
         <v>80</v>
       </c>
+      <c r="G11" s="13">
+        <v>80</v>
+      </c>
+      <c r="H11" s="13">
+        <v>80</v>
+      </c>
+      <c r="I11" s="13">
+        <v>80</v>
+      </c>
+      <c r="J11" s="13">
+        <v>80</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
@@ -32198,6 +32285,18 @@
       <c r="F12" s="13">
         <v>0</v>
       </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
@@ -32218,6 +32317,18 @@
       <c r="F13" s="13">
         <v>0</v>
       </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
@@ -32238,6 +32349,18 @@
       <c r="F14" s="13">
         <v>0</v>
       </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
@@ -32258,6 +32381,18 @@
       <c r="F15" s="13">
         <v>10</v>
       </c>
+      <c r="G15" s="13">
+        <v>10</v>
+      </c>
+      <c r="H15" s="13">
+        <v>10</v>
+      </c>
+      <c r="I15" s="13">
+        <v>10</v>
+      </c>
+      <c r="J15" s="13">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -32278,6 +32413,18 @@
       <c r="F16" s="13">
         <v>0</v>
       </c>
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
@@ -32298,10 +32445,18 @@
       <c r="F17" s="32">
         <v>108.6</v>
       </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
+      <c r="G17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="H17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="I17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="J17" s="32">
+        <v>108.6</v>
+      </c>
       <c r="K17" s="32"/>
       <c r="L17" s="32"/>
       <c r="M17" s="32"/>
@@ -32341,6 +32496,18 @@
       <c r="F18" s="13">
         <v>0</v>
       </c>
+      <c r="G18" s="13">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13">
+        <v>0</v>
+      </c>
+      <c r="J18" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
@@ -32361,6 +32528,18 @@
       <c r="F19" s="13">
         <v>34</v>
       </c>
+      <c r="G19" s="13">
+        <v>34</v>
+      </c>
+      <c r="H19" s="13">
+        <v>34</v>
+      </c>
+      <c r="I19" s="13">
+        <v>34</v>
+      </c>
+      <c r="J19" s="13">
+        <v>34</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
@@ -32381,6 +32560,18 @@
       <c r="F20" s="13">
         <v>0</v>
       </c>
+      <c r="G20" s="13">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
@@ -32401,6 +32592,18 @@
       <c r="F21" s="13">
         <v>0</v>
       </c>
+      <c r="G21" s="13">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
@@ -32421,6 +32624,18 @@
       <c r="F22" s="13">
         <v>0</v>
       </c>
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0</v>
+      </c>
+      <c r="J22" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
@@ -32441,6 +32656,18 @@
       <c r="F23" s="13">
         <v>0</v>
       </c>
+      <c r="G23" s="13">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0</v>
+      </c>
+      <c r="J23" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
@@ -32461,10 +32688,18 @@
       <c r="F24" s="32">
         <v>42.5</v>
       </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
+      <c r="G24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="H24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="I24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="J24" s="32">
+        <v>42.5</v>
+      </c>
       <c r="K24" s="32"/>
       <c r="L24" s="32"/>
       <c r="M24" s="32"/>
@@ -32504,6 +32739,18 @@
       <c r="F25" s="13">
         <v>0</v>
       </c>
+      <c r="G25" s="13">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
@@ -32524,10 +32771,18 @@
       <c r="F26" s="32">
         <v>90.8</v>
       </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
+      <c r="G26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="H26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="I26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="J26" s="32">
+        <v>90.8</v>
+      </c>
       <c r="K26" s="32"/>
       <c r="L26" s="32"/>
       <c r="M26" s="32"/>
@@ -32567,6 +32822,18 @@
       <c r="F27" s="13">
         <v>0</v>
       </c>
+      <c r="G27" s="13">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
@@ -32587,6 +32854,18 @@
       <c r="F28" s="13">
         <v>0</v>
       </c>
+      <c r="G28" s="13">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
@@ -32607,10 +32886,18 @@
       <c r="F29" s="31">
         <v>10</v>
       </c>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
+      <c r="G29" s="31">
+        <v>10</v>
+      </c>
+      <c r="H29" s="31">
+        <v>10</v>
+      </c>
+      <c r="I29" s="31">
+        <v>10</v>
+      </c>
+      <c r="J29" s="31">
+        <v>10</v>
+      </c>
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
       <c r="M29" s="31"/>
@@ -32646,10 +32933,18 @@
       </c>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
+      <c r="G30" s="33">
+        <v>10</v>
+      </c>
+      <c r="H30" s="33">
+        <v>10</v>
+      </c>
+      <c r="I30" s="33">
+        <v>10</v>
+      </c>
+      <c r="J30" s="33">
+        <v>10</v>
+      </c>
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="33"/>
@@ -32689,6 +32984,18 @@
       <c r="F31" s="13">
         <v>43</v>
       </c>
+      <c r="G31" s="13">
+        <v>12</v>
+      </c>
+      <c r="H31" s="13">
+        <v>12</v>
+      </c>
+      <c r="I31" s="13">
+        <v>12</v>
+      </c>
+      <c r="J31" s="13">
+        <v>12</v>
+      </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
@@ -32709,8 +33016,20 @@
       <c r="F32" s="13">
         <v>0</v>
       </c>
+      <c r="G32" s="13">
+        <v>0</v>
+      </c>
+      <c r="H32" s="13">
+        <v>0</v>
+      </c>
+      <c r="I32" s="13">
+        <v>0</v>
+      </c>
+      <c r="J32" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>44</v>
       </c>
@@ -32729,8 +33048,20 @@
       <c r="F33" s="13">
         <v>30</v>
       </c>
+      <c r="G33" s="13">
+        <v>30</v>
+      </c>
+      <c r="H33" s="13">
+        <v>30</v>
+      </c>
+      <c r="I33" s="13">
+        <v>30</v>
+      </c>
+      <c r="J33" s="13">
+        <v>30</v>
+      </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
         <v>45</v>
       </c>
@@ -32749,8 +33080,20 @@
       <c r="F34" s="13">
         <v>0</v>
       </c>
+      <c r="G34" s="13">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13">
+        <v>0</v>
+      </c>
+      <c r="I34" s="13">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>46</v>
       </c>
@@ -32769,8 +33112,20 @@
       <c r="F35" s="13">
         <v>0</v>
       </c>
+      <c r="G35" s="13">
+        <v>0</v>
+      </c>
+      <c r="H35" s="13">
+        <v>0</v>
+      </c>
+      <c r="I35" s="13">
+        <v>0</v>
+      </c>
+      <c r="J35" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
@@ -32789,8 +33144,20 @@
       <c r="F36" s="13">
         <v>0</v>
       </c>
+      <c r="G36" s="13">
+        <v>0</v>
+      </c>
+      <c r="H36" s="13">
+        <v>0</v>
+      </c>
+      <c r="I36" s="13">
+        <v>0</v>
+      </c>
+      <c r="J36" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>48</v>
       </c>
@@ -32809,8 +33176,20 @@
       <c r="F37" s="13">
         <v>2</v>
       </c>
+      <c r="G37" s="13">
+        <v>2</v>
+      </c>
+      <c r="H37" s="13">
+        <v>2</v>
+      </c>
+      <c r="I37" s="13">
+        <v>2</v>
+      </c>
+      <c r="J37" s="13">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>49</v>
       </c>
@@ -32829,8 +33208,20 @@
       <c r="F38" s="13">
         <v>32</v>
       </c>
+      <c r="G38" s="13">
+        <v>32</v>
+      </c>
+      <c r="H38" s="13">
+        <v>32</v>
+      </c>
+      <c r="I38" s="13">
+        <v>32</v>
+      </c>
+      <c r="J38" s="13">
+        <v>32</v>
+      </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>50</v>
       </c>
@@ -32849,8 +33240,20 @@
       <c r="F39" s="13">
         <v>0</v>
       </c>
+      <c r="G39" s="13">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13">
+        <v>0</v>
+      </c>
+      <c r="I39" s="13">
+        <v>0</v>
+      </c>
+      <c r="J39" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
         <v>51</v>
       </c>
@@ -32869,8 +33272,20 @@
       <c r="F40" s="13">
         <v>0</v>
       </c>
+      <c r="G40" s="13">
+        <v>0</v>
+      </c>
+      <c r="H40" s="13">
+        <v>0</v>
+      </c>
+      <c r="I40" s="13">
+        <v>0</v>
+      </c>
+      <c r="J40" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>52</v>
       </c>
@@ -32889,8 +33304,20 @@
       <c r="F41" s="13">
         <v>0</v>
       </c>
+      <c r="G41" s="13">
+        <v>0</v>
+      </c>
+      <c r="H41" s="13">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13">
+        <v>0</v>
+      </c>
+      <c r="J41" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
         <v>53</v>
       </c>
@@ -32909,13 +33336,25 @@
       <c r="F42" s="13">
         <v>0</v>
       </c>
+      <c r="G42" s="13">
+        <v>0</v>
+      </c>
+      <c r="H42" s="13">
+        <v>0</v>
+      </c>
+      <c r="I42" s="13">
+        <v>0</v>
+      </c>
+      <c r="J42" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>55</v>
       </c>
@@ -32934,8 +33373,20 @@
       <c r="F44" s="13">
         <v>0</v>
       </c>
+      <c r="G44" s="13">
+        <v>0</v>
+      </c>
+      <c r="H44" s="13">
+        <v>0</v>
+      </c>
+      <c r="I44" s="13">
+        <v>0</v>
+      </c>
+      <c r="J44" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>56</v>
       </c>
@@ -32954,8 +33405,20 @@
       <c r="F45" s="13">
         <v>0</v>
       </c>
+      <c r="G45" s="13">
+        <v>0</v>
+      </c>
+      <c r="H45" s="13">
+        <v>0</v>
+      </c>
+      <c r="I45" s="13">
+        <v>0</v>
+      </c>
+      <c r="J45" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>57</v>
       </c>
@@ -32974,8 +33437,20 @@
       <c r="F46" s="13">
         <v>0</v>
       </c>
+      <c r="G46" s="13">
+        <v>0</v>
+      </c>
+      <c r="H46" s="13">
+        <v>0</v>
+      </c>
+      <c r="I46" s="13">
+        <v>0</v>
+      </c>
+      <c r="J46" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>58</v>
       </c>
@@ -32994,8 +33469,20 @@
       <c r="F47" s="13">
         <v>0</v>
       </c>
+      <c r="G47" s="13">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13">
+        <v>0</v>
+      </c>
+      <c r="J47" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
         <v>59</v>
       </c>
@@ -33012,6 +33499,18 @@
         <v>0</v>
       </c>
       <c r="F48" s="13">
+        <v>0</v>
+      </c>
+      <c r="G48" s="13">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13">
+        <v>0</v>
+      </c>
+      <c r="I48" s="13">
+        <v>0</v>
+      </c>
+      <c r="J48" s="13">
         <v>0</v>
       </c>
     </row>
@@ -33034,6 +33533,18 @@
       <c r="F49" s="13">
         <v>0</v>
       </c>
+      <c r="G49" s="13">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13">
+        <v>0</v>
+      </c>
+      <c r="I49" s="13">
+        <v>0</v>
+      </c>
+      <c r="J49" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
@@ -33054,6 +33565,18 @@
       <c r="F50" s="13">
         <v>41</v>
       </c>
+      <c r="G50" s="13">
+        <v>41</v>
+      </c>
+      <c r="H50" s="13">
+        <v>41</v>
+      </c>
+      <c r="I50" s="13">
+        <v>41</v>
+      </c>
+      <c r="J50" s="13">
+        <v>41</v>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
@@ -33074,6 +33597,18 @@
       <c r="F51" s="13">
         <v>0</v>
       </c>
+      <c r="G51" s="13">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13">
+        <v>0</v>
+      </c>
+      <c r="I51" s="13">
+        <v>0</v>
+      </c>
+      <c r="J51" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
@@ -33094,6 +33629,18 @@
       <c r="F52" s="13">
         <v>0</v>
       </c>
+      <c r="G52" s="13">
+        <v>0</v>
+      </c>
+      <c r="H52" s="13">
+        <v>0</v>
+      </c>
+      <c r="I52" s="13">
+        <v>0</v>
+      </c>
+      <c r="J52" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
@@ -33114,6 +33661,18 @@
       <c r="F53" s="13">
         <v>0</v>
       </c>
+      <c r="G53" s="13">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13">
+        <v>0</v>
+      </c>
+      <c r="J53" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
@@ -33134,6 +33693,18 @@
       <c r="F54" s="13">
         <v>0</v>
       </c>
+      <c r="G54" s="13">
+        <v>0</v>
+      </c>
+      <c r="H54" s="13">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13">
+        <v>0</v>
+      </c>
+      <c r="J54" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
@@ -33154,6 +33725,18 @@
       <c r="F55" s="13">
         <v>59</v>
       </c>
+      <c r="G55" s="13">
+        <v>59</v>
+      </c>
+      <c r="H55" s="13">
+        <v>59</v>
+      </c>
+      <c r="I55" s="13">
+        <v>59</v>
+      </c>
+      <c r="J55" s="13">
+        <v>59</v>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
@@ -33181,19 +33764,19 @@
       </c>
       <c r="G57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>611.90000000000009</v>
       </c>
       <c r="H57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>611.90000000000009</v>
       </c>
       <c r="I57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>611.90000000000009</v>
       </c>
       <c r="J57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>611.90000000000009</v>
       </c>
       <c r="K57" s="13">
         <f t="shared" si="0"/>
@@ -33290,7 +33873,7 @@
       </c>
       <c r="B59" s="13">
         <f>SUM(A57:AF57)</f>
-        <v>3246.7000000000003</v>
+        <v>5694.2999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -33423,10 +34006,18 @@
       <c r="F2" s="14">
         <v>66</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="G2" s="14">
+        <v>66</v>
+      </c>
+      <c r="H2" s="14">
+        <v>66</v>
+      </c>
+      <c r="I2" s="14">
+        <v>66</v>
+      </c>
+      <c r="J2" s="14">
+        <v>66</v>
+      </c>
       <c r="K2" s="14"/>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
@@ -33469,10 +34060,18 @@
       <c r="F3" s="14">
         <v>0</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14">
+        <v>0</v>
+      </c>
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
@@ -33537,10 +34136,18 @@
       <c r="F4" s="14">
         <v>30</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
+      <c r="G4" s="14">
+        <v>30</v>
+      </c>
+      <c r="H4" s="14">
+        <v>30</v>
+      </c>
+      <c r="I4" s="14">
+        <v>30</v>
+      </c>
+      <c r="J4" s="14">
+        <v>30</v>
+      </c>
       <c r="K4" s="14"/>
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
@@ -33583,10 +34190,18 @@
       <c r="F5" s="14">
         <v>68</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="G5" s="14">
+        <v>68</v>
+      </c>
+      <c r="H5" s="14">
+        <v>68</v>
+      </c>
+      <c r="I5" s="14">
+        <v>68</v>
+      </c>
+      <c r="J5" s="14">
+        <v>68</v>
+      </c>
       <c r="K5" s="14"/>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
@@ -33629,10 +34244,18 @@
       <c r="F6" s="14">
         <v>61</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="G6" s="14">
+        <v>61</v>
+      </c>
+      <c r="H6" s="14">
+        <v>61</v>
+      </c>
+      <c r="I6" s="14">
+        <v>61</v>
+      </c>
+      <c r="J6" s="14">
+        <v>61</v>
+      </c>
       <c r="K6" s="14"/>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
@@ -33675,10 +34298,18 @@
       <c r="F7" s="14">
         <v>0</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14">
+        <v>0</v>
+      </c>
       <c r="K7" s="14"/>
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
@@ -33721,6 +34352,18 @@
       <c r="F8">
         <v>38</v>
       </c>
+      <c r="G8">
+        <v>38</v>
+      </c>
+      <c r="H8">
+        <v>38</v>
+      </c>
+      <c r="I8">
+        <v>38</v>
+      </c>
+      <c r="J8">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -33741,10 +34384,18 @@
       <c r="F9" s="14">
         <v>46</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
+      <c r="G9" s="14">
+        <v>46</v>
+      </c>
+      <c r="H9" s="14">
+        <v>46</v>
+      </c>
+      <c r="I9" s="14">
+        <v>46</v>
+      </c>
+      <c r="J9" s="14">
+        <v>46</v>
+      </c>
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
@@ -33787,10 +34438,18 @@
       <c r="F10" s="14">
         <v>147</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
+      <c r="G10" s="14">
+        <v>147</v>
+      </c>
+      <c r="H10" s="14">
+        <v>147</v>
+      </c>
+      <c r="I10" s="14">
+        <v>147</v>
+      </c>
+      <c r="J10" s="14">
+        <v>147</v>
+      </c>
       <c r="K10" s="14"/>
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
@@ -33833,10 +34492,18 @@
       <c r="F11" s="14">
         <v>30</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
+      <c r="G11" s="14">
+        <v>30</v>
+      </c>
+      <c r="H11" s="14">
+        <v>30</v>
+      </c>
+      <c r="I11" s="14">
+        <v>30</v>
+      </c>
+      <c r="J11" s="14">
+        <v>30</v>
+      </c>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
@@ -33879,10 +34546,18 @@
       <c r="F12" s="14">
         <v>102</v>
       </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
+      <c r="G12" s="14">
+        <v>102</v>
+      </c>
+      <c r="H12" s="14">
+        <v>102</v>
+      </c>
+      <c r="I12" s="14">
+        <v>102</v>
+      </c>
+      <c r="J12" s="14">
+        <v>102</v>
+      </c>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
@@ -33925,10 +34600,18 @@
       <c r="F13" s="14">
         <v>54</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
+      <c r="G13" s="14">
+        <v>54</v>
+      </c>
+      <c r="H13" s="14">
+        <v>54</v>
+      </c>
+      <c r="I13" s="14">
+        <v>54</v>
+      </c>
+      <c r="J13" s="14">
+        <v>54</v>
+      </c>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
@@ -33971,10 +34654,18 @@
       <c r="F14" s="14">
         <v>172</v>
       </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
+      <c r="G14" s="14">
+        <v>172</v>
+      </c>
+      <c r="H14" s="14">
+        <v>172</v>
+      </c>
+      <c r="I14" s="14">
+        <v>172</v>
+      </c>
+      <c r="J14" s="14">
+        <v>172</v>
+      </c>
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
@@ -34017,10 +34708,18 @@
       <c r="F15" s="14">
         <v>50</v>
       </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
+      <c r="G15" s="14">
+        <v>50</v>
+      </c>
+      <c r="H15" s="14">
+        <v>50</v>
+      </c>
+      <c r="I15" s="14">
+        <v>50</v>
+      </c>
+      <c r="J15" s="14">
+        <v>50</v>
+      </c>
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="14"/>
@@ -34063,6 +34762,18 @@
       <c r="F16">
         <v>58</v>
       </c>
+      <c r="G16">
+        <v>58</v>
+      </c>
+      <c r="H16">
+        <v>58</v>
+      </c>
+      <c r="I16">
+        <v>58</v>
+      </c>
+      <c r="J16">
+        <v>58</v>
+      </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -34083,6 +34794,18 @@
       <c r="F17">
         <v>104</v>
       </c>
+      <c r="G17">
+        <v>104</v>
+      </c>
+      <c r="H17">
+        <v>104</v>
+      </c>
+      <c r="I17">
+        <v>104</v>
+      </c>
+      <c r="J17">
+        <v>104</v>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -34103,10 +34826,18 @@
       <c r="F18" s="14">
         <v>0</v>
       </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0</v>
+      </c>
+      <c r="I18" s="14">
+        <v>0</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0</v>
+      </c>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="14"/>
@@ -34149,10 +34880,18 @@
       <c r="F19" s="14">
         <v>51</v>
       </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
+      <c r="G19" s="14">
+        <v>51</v>
+      </c>
+      <c r="H19" s="14">
+        <v>51</v>
+      </c>
+      <c r="I19" s="14">
+        <v>51</v>
+      </c>
+      <c r="J19" s="14">
+        <v>51</v>
+      </c>
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="14"/>
@@ -34195,10 +34934,18 @@
       <c r="F20" s="14">
         <v>45</v>
       </c>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
+      <c r="G20" s="14">
+        <v>45</v>
+      </c>
+      <c r="H20" s="14">
+        <v>45</v>
+      </c>
+      <c r="I20" s="14">
+        <v>45</v>
+      </c>
+      <c r="J20" s="14">
+        <v>45</v>
+      </c>
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
@@ -34241,10 +34988,18 @@
       <c r="F21" s="14">
         <v>55</v>
       </c>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
+      <c r="G21" s="14">
+        <v>55</v>
+      </c>
+      <c r="H21" s="14">
+        <v>55</v>
+      </c>
+      <c r="I21" s="14">
+        <v>55</v>
+      </c>
+      <c r="J21" s="14">
+        <v>55</v>
+      </c>
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
@@ -34287,6 +35042,18 @@
       <c r="F22">
         <v>95</v>
       </c>
+      <c r="G22">
+        <v>95</v>
+      </c>
+      <c r="H22">
+        <v>95</v>
+      </c>
+      <c r="I22">
+        <v>95</v>
+      </c>
+      <c r="J22">
+        <v>95</v>
+      </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -34307,10 +35074,18 @@
       <c r="F23" s="14">
         <v>0</v>
       </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14">
+        <v>0</v>
+      </c>
+      <c r="J23" s="14">
+        <v>0</v>
+      </c>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
@@ -34353,6 +35128,18 @@
       <c r="F24">
         <v>56</v>
       </c>
+      <c r="G24">
+        <v>56</v>
+      </c>
+      <c r="H24">
+        <v>56</v>
+      </c>
+      <c r="I24">
+        <v>56</v>
+      </c>
+      <c r="J24">
+        <v>56</v>
+      </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -34373,10 +35160,18 @@
       <c r="F25" s="14">
         <v>50</v>
       </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
+      <c r="G25" s="14">
+        <v>50</v>
+      </c>
+      <c r="H25" s="14">
+        <v>50</v>
+      </c>
+      <c r="I25" s="14">
+        <v>50</v>
+      </c>
+      <c r="J25" s="14">
+        <v>50</v>
+      </c>
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
       <c r="M25" s="14"/>
@@ -34419,10 +35214,18 @@
       <c r="F26" s="34">
         <v>64.41</v>
       </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
+      <c r="G26" s="34">
+        <v>56.92</v>
+      </c>
+      <c r="H26" s="34">
+        <v>56.92</v>
+      </c>
+      <c r="I26" s="34">
+        <v>56.92</v>
+      </c>
+      <c r="J26" s="34">
+        <v>56.92</v>
+      </c>
       <c r="K26" s="34"/>
       <c r="L26" s="34"/>
       <c r="M26" s="34"/>
@@ -34465,10 +35268,18 @@
       <c r="F27" s="34">
         <v>125.65</v>
       </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
+      <c r="G27" s="34">
+        <v>126.05</v>
+      </c>
+      <c r="H27" s="34">
+        <v>126.05</v>
+      </c>
+      <c r="I27" s="34">
+        <v>126.05</v>
+      </c>
+      <c r="J27" s="34">
+        <v>126.05</v>
+      </c>
       <c r="K27" s="34"/>
       <c r="L27" s="34"/>
       <c r="M27" s="34"/>
@@ -34511,10 +35322,18 @@
       <c r="F28" s="14">
         <v>0</v>
       </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="14">
+        <v>0</v>
+      </c>
+      <c r="J28" s="14">
+        <v>0</v>
+      </c>
       <c r="K28" s="14"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
@@ -34557,10 +35376,18 @@
       <c r="F29" s="34">
         <v>58.01</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
+      <c r="G29" s="34">
+        <v>51.44</v>
+      </c>
+      <c r="H29" s="34">
+        <v>51.44</v>
+      </c>
+      <c r="I29" s="34">
+        <v>51.44</v>
+      </c>
+      <c r="J29" s="34">
+        <v>51.44</v>
+      </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34"/>
       <c r="M29" s="34"/>
@@ -34603,10 +35430,18 @@
       <c r="F30" s="14">
         <v>29</v>
       </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
+      <c r="G30" s="14">
+        <v>29</v>
+      </c>
+      <c r="H30" s="14">
+        <v>29</v>
+      </c>
+      <c r="I30" s="14">
+        <v>29</v>
+      </c>
+      <c r="J30" s="14">
+        <v>29</v>
+      </c>
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
@@ -34649,10 +35484,18 @@
       <c r="F31" s="14">
         <v>139</v>
       </c>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
+      <c r="G31" s="14">
+        <v>139</v>
+      </c>
+      <c r="H31" s="14">
+        <v>139</v>
+      </c>
+      <c r="I31" s="14">
+        <v>139</v>
+      </c>
+      <c r="J31" s="14">
+        <v>139</v>
+      </c>
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
@@ -34695,10 +35538,18 @@
       <c r="F32" s="14">
         <v>0</v>
       </c>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="14">
+        <v>0</v>
+      </c>
+      <c r="J32" s="14">
+        <v>0</v>
+      </c>
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
@@ -34741,10 +35592,18 @@
       <c r="F33" s="14">
         <v>0</v>
       </c>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>0</v>
+      </c>
+      <c r="I33" s="14">
+        <v>0</v>
+      </c>
+      <c r="J33" s="14">
+        <v>0</v>
+      </c>
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
@@ -34787,10 +35646,18 @@
       <c r="F34" s="34">
         <v>93.9</v>
       </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
+      <c r="G34" s="34">
+        <v>62.11</v>
+      </c>
+      <c r="H34" s="34">
+        <v>62.11</v>
+      </c>
+      <c r="I34" s="34">
+        <v>62.11</v>
+      </c>
+      <c r="J34" s="34">
+        <v>62.11</v>
+      </c>
       <c r="K34" s="34"/>
       <c r="L34" s="34"/>
       <c r="M34" s="34"/>
@@ -34833,10 +35700,18 @@
       <c r="F35" s="34">
         <v>36.89</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
+      <c r="G35" s="34">
+        <v>31.04</v>
+      </c>
+      <c r="H35" s="34">
+        <v>31.04</v>
+      </c>
+      <c r="I35" s="34">
+        <v>31.04</v>
+      </c>
+      <c r="J35" s="34">
+        <v>31.04</v>
+      </c>
       <c r="K35" s="34"/>
       <c r="L35" s="34"/>
       <c r="M35" s="34"/>
@@ -34879,10 +35754,18 @@
       <c r="F36" s="14">
         <v>0</v>
       </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>0</v>
+      </c>
+      <c r="I36" s="14">
+        <v>0</v>
+      </c>
+      <c r="J36" s="14">
+        <v>0</v>
+      </c>
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
@@ -34925,10 +35808,18 @@
       <c r="F37" s="14">
         <v>0</v>
       </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>0</v>
+      </c>
+      <c r="I37" s="14">
+        <v>0</v>
+      </c>
+      <c r="J37" s="14">
+        <v>0</v>
+      </c>
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="14"/>
@@ -34971,6 +35862,18 @@
       <c r="F38">
         <v>60</v>
       </c>
+      <c r="G38">
+        <v>60</v>
+      </c>
+      <c r="H38">
+        <v>60</v>
+      </c>
+      <c r="I38">
+        <v>60</v>
+      </c>
+      <c r="J38">
+        <v>60</v>
+      </c>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -34991,10 +35894,18 @@
       <c r="F39" s="14">
         <v>0</v>
       </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>0</v>
+      </c>
+      <c r="I39" s="14">
+        <v>0</v>
+      </c>
+      <c r="J39" s="14">
+        <v>0</v>
+      </c>
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
       <c r="M39" s="14"/>
@@ -35037,10 +35948,18 @@
       <c r="F40" s="14">
         <v>0</v>
       </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>0</v>
+      </c>
+      <c r="I40" s="14">
+        <v>0</v>
+      </c>
+      <c r="J40" s="14">
+        <v>0</v>
+      </c>
       <c r="K40" s="14"/>
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
@@ -35083,10 +36002,18 @@
       <c r="F41" s="14">
         <v>40</v>
       </c>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
+      <c r="G41" s="14">
+        <v>40</v>
+      </c>
+      <c r="H41" s="14">
+        <v>40</v>
+      </c>
+      <c r="I41" s="14">
+        <v>40</v>
+      </c>
+      <c r="J41" s="14">
+        <v>40</v>
+      </c>
       <c r="K41" s="14"/>
       <c r="L41" s="14"/>
       <c r="M41" s="14"/>
@@ -35129,10 +36056,18 @@
       <c r="F42" s="14">
         <v>0</v>
       </c>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>0</v>
+      </c>
+      <c r="I42" s="14">
+        <v>0</v>
+      </c>
+      <c r="J42" s="14">
+        <v>0</v>
+      </c>
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
       <c r="M42" s="14"/>
@@ -35175,10 +36110,18 @@
       <c r="F43" s="14">
         <v>70</v>
       </c>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
+      <c r="G43" s="14">
+        <v>70</v>
+      </c>
+      <c r="H43" s="14">
+        <v>70</v>
+      </c>
+      <c r="I43" s="14">
+        <v>70</v>
+      </c>
+      <c r="J43" s="14">
+        <v>70</v>
+      </c>
       <c r="K43" s="14"/>
       <c r="L43" s="14"/>
       <c r="M43" s="14"/>
@@ -35221,10 +36164,18 @@
       <c r="F44" s="14">
         <v>0</v>
       </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>0</v>
+      </c>
+      <c r="I44" s="14">
+        <v>0</v>
+      </c>
+      <c r="J44" s="14">
+        <v>0</v>
+      </c>
       <c r="K44" s="14"/>
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>
@@ -35267,10 +36218,18 @@
       <c r="F45" s="14">
         <v>0</v>
       </c>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>0</v>
+      </c>
+      <c r="I45" s="14">
+        <v>0</v>
+      </c>
+      <c r="J45" s="14">
+        <v>0</v>
+      </c>
       <c r="K45" s="14"/>
       <c r="L45" s="14"/>
       <c r="M45" s="14"/>
@@ -35313,10 +36272,18 @@
       <c r="F46" s="14">
         <v>80</v>
       </c>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
+      <c r="G46" s="14">
+        <v>80</v>
+      </c>
+      <c r="H46" s="14">
+        <v>80</v>
+      </c>
+      <c r="I46" s="14">
+        <v>80</v>
+      </c>
+      <c r="J46" s="14">
+        <v>80</v>
+      </c>
       <c r="K46" s="14"/>
       <c r="L46" s="14"/>
       <c r="M46" s="14"/>
@@ -35359,10 +36326,18 @@
       <c r="F47" s="14">
         <v>0</v>
       </c>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>0</v>
+      </c>
+      <c r="I47" s="14">
+        <v>0</v>
+      </c>
+      <c r="J47" s="14">
+        <v>0</v>
+      </c>
       <c r="K47" s="14"/>
       <c r="L47" s="14"/>
       <c r="M47" s="14"/>
@@ -35405,10 +36380,18 @@
       <c r="F48" s="14">
         <v>170</v>
       </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
+      <c r="G48" s="14">
+        <v>170</v>
+      </c>
+      <c r="H48" s="14">
+        <v>170</v>
+      </c>
+      <c r="I48" s="14">
+        <v>170</v>
+      </c>
+      <c r="J48" s="14">
+        <v>170</v>
+      </c>
       <c r="K48" s="14"/>
       <c r="L48" s="14"/>
       <c r="M48" s="14"/>
@@ -35451,10 +36434,18 @@
       <c r="F49" s="14">
         <v>30</v>
       </c>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
+      <c r="G49" s="14">
+        <v>30</v>
+      </c>
+      <c r="H49" s="14">
+        <v>30</v>
+      </c>
+      <c r="I49" s="14">
+        <v>30</v>
+      </c>
+      <c r="J49" s="14">
+        <v>30</v>
+      </c>
       <c r="K49" s="14"/>
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
@@ -35497,6 +36488,18 @@
       <c r="F50">
         <v>225</v>
       </c>
+      <c r="G50">
+        <v>225</v>
+      </c>
+      <c r="H50">
+        <v>225</v>
+      </c>
+      <c r="I50">
+        <v>225</v>
+      </c>
+      <c r="J50">
+        <v>225</v>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
@@ -35517,10 +36520,18 @@
       <c r="F51" s="14">
         <v>53</v>
       </c>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
+      <c r="G51" s="14">
+        <v>53</v>
+      </c>
+      <c r="H51" s="14">
+        <v>53</v>
+      </c>
+      <c r="I51" s="14">
+        <v>53</v>
+      </c>
+      <c r="J51" s="14">
+        <v>53</v>
+      </c>
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
@@ -35563,10 +36574,18 @@
       <c r="F52" s="14">
         <v>0</v>
       </c>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>0</v>
+      </c>
+      <c r="I52" s="14">
+        <v>0</v>
+      </c>
+      <c r="J52" s="14">
+        <v>0</v>
+      </c>
       <c r="K52" s="14"/>
       <c r="L52" s="14"/>
       <c r="M52" s="14"/>
@@ -35609,10 +36628,18 @@
       <c r="F53" s="14">
         <v>0</v>
       </c>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>0</v>
+      </c>
+      <c r="I53" s="14">
+        <v>0</v>
+      </c>
+      <c r="J53" s="14">
+        <v>0</v>
+      </c>
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
       <c r="M53" s="14"/>
@@ -35655,10 +36682,18 @@
       <c r="F54" s="14">
         <v>0</v>
       </c>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>0</v>
+      </c>
+      <c r="I54" s="14">
+        <v>0</v>
+      </c>
+      <c r="J54" s="14">
+        <v>0</v>
+      </c>
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
       <c r="M54" s="14"/>
@@ -35701,6 +36736,18 @@
       <c r="F55">
         <v>61</v>
       </c>
+      <c r="G55">
+        <v>61</v>
+      </c>
+      <c r="H55">
+        <v>61</v>
+      </c>
+      <c r="I55">
+        <v>61</v>
+      </c>
+      <c r="J55">
+        <v>61</v>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
@@ -35728,19 +36775,19 @@
       </c>
       <c r="G57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2662.56</v>
       </c>
       <c r="H57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2662.56</v>
       </c>
       <c r="I57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2662.56</v>
       </c>
       <c r="J57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2662.56</v>
       </c>
       <c r="K57" s="13">
         <f t="shared" si="0"/>
@@ -35837,7 +36884,7 @@
       </c>
       <c r="B59">
         <f>SUM(A57:AF57)</f>
-        <v>13392.670000000002</v>
+        <v>24042.910000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Project Zero Dashboard 1 - Copy.xlsx
+++ b/Project Zero Dashboard 1 - Copy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMT NUC 3\Desktop\Solar Dashboard Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1971D6-B6C7-4B50-AB04-D0705338E43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5762C344-1B5F-4D3D-9ADE-E3E96BDF0184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{850AF22D-85D1-4C73-981E-24580D680358}"/>
   </bookViews>
@@ -5785,10 +5785,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -6019,7 +6019,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.00">
-                  <c:v>177.01835827173846</c:v>
+                  <c:v>175.29993464028152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11017,10 +11017,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>0</c:v>
@@ -11092,7 +11092,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>122.98164172826152</c:v>
+                  <c:v>124.70006535971847</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15933,7 +15933,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -16164,7 +16164,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.00">
-                  <c:v>176.31609484875167</c:v>
+                  <c:v>175.90630270193802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21166,7 +21166,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>0</c:v>
@@ -21241,7 +21241,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>123.68390515124833</c:v>
+                  <c:v>124.09369729806198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25496,7 +25496,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>23%</a:t>
+            <a:t>25%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -25624,7 +25624,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>77%</a:t>
+            <a:t>75%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -25925,7 +25925,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>611,90</a:t>
+            <a:t>668,90</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="3600">
             <a:solidFill>
@@ -26000,7 +26000,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>5694,30</a:t>
+            <a:t>9707,70</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -26279,7 +26279,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>2050,66</a:t>
+            <a:t>2039,19</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="4800">
             <a:solidFill>
@@ -26354,7 +26354,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr/>
-            <a:t>18348,61</a:t>
+            <a:t>30583,75</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="6600">
             <a:solidFill>
@@ -26847,7 +26847,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="19">
         <f>AVERAGE(Y6:Y68)</f>
-        <v>11.545283018867925</v>
+        <v>12.620754716981134</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>77</v>
@@ -26900,7 +26900,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="20">
         <f>AVERAGE(AA6:AA68)</f>
-        <v>49.306666666666665</v>
+        <v>50.149814814814818</v>
       </c>
       <c r="Q5" s="18" t="s">
         <v>77</v>
@@ -26976,7 +26976,7 @@
       <c r="O6" s="4"/>
       <c r="P6" s="20">
         <f>IF(P4&gt;P5,0,P5-P4)</f>
-        <v>37.761383647798738</v>
+        <v>37.529060097833685</v>
       </c>
       <c r="Q6" s="18" t="s">
         <v>77</v>
@@ -27051,7 +27051,7 @@
       </c>
       <c r="P7" s="21">
         <f>SUM(Y6:Y59)</f>
-        <v>611.90000000000009</v>
+        <v>668.90000000000009</v>
       </c>
       <c r="Q7" s="18" t="s">
         <v>77</v>
@@ -27126,7 +27126,7 @@
       </c>
       <c r="P8" s="5">
         <f>SUM(AA6:AA68)</f>
-        <v>2662.56</v>
+        <v>2708.09</v>
       </c>
       <c r="Q8" s="18" t="s">
         <v>77</v>
@@ -27202,7 +27202,7 @@
       <c r="O9" s="4"/>
       <c r="P9" s="20">
         <f>IF(P7&gt;P8,0,P8-P7)</f>
-        <v>2050.66</v>
+        <v>2039.19</v>
       </c>
       <c r="Q9" s="18" t="s">
         <v>77</v>
@@ -27346,7 +27346,7 @@
       <c r="P11" s="20"/>
       <c r="Q11" s="23">
         <f>Q15</f>
-        <v>0.22981641728261526</v>
+        <v>0.24700065359718476</v>
       </c>
       <c r="V11" s="7"/>
       <c r="W11" t="s">
@@ -27495,7 +27495,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="23">
         <f>Q17</f>
-        <v>0.77018358271738474</v>
+        <v>0.75299934640281529</v>
       </c>
       <c r="V13" s="7"/>
       <c r="W13" t="s">
@@ -27630,7 +27630,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="25">
         <f>P7/P8</f>
-        <v>0.22981641728261526</v>
+        <v>0.24700065359718476</v>
       </c>
       <c r="V15" s="7"/>
       <c r="W15" t="s">
@@ -27771,7 +27771,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="25">
         <f>P9/P8</f>
-        <v>0.77018358271738474</v>
+        <v>0.75299934640281529</v>
       </c>
       <c r="V17" s="7"/>
       <c r="W17" t="s">
@@ -28146,7 +28146,7 @@
       </c>
       <c r="P23" s="21">
         <f>'Production By Date'!B59</f>
-        <v>5694.2999999999993</v>
+        <v>9707.6999999999971</v>
       </c>
       <c r="Q23" s="22" t="s">
         <v>77</v>
@@ -28207,7 +28207,7 @@
       <c r="O24" s="4"/>
       <c r="P24" s="20">
         <f>P23/1000</f>
-        <v>5.6942999999999993</v>
+        <v>9.7076999999999973</v>
       </c>
       <c r="Q24" s="18" t="s">
         <v>79</v>
@@ -28269,7 +28269,7 @@
       </c>
       <c r="P25" s="5">
         <f>'Consumption By Date'!B59</f>
-        <v>24042.910000000003</v>
+        <v>40291.449999999997</v>
       </c>
       <c r="Q25" s="22" t="s">
         <v>77</v>
@@ -28329,7 +28329,7 @@
       <c r="N26" s="7"/>
       <c r="P26" s="20">
         <f>P25/1000</f>
-        <v>24.042910000000003</v>
+        <v>40.291449999999998</v>
       </c>
       <c r="Q26" s="22" t="s">
         <v>79</v>
@@ -28392,7 +28392,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="20">
         <f>IF(P23&gt;P25,0,P25-P23)</f>
-        <v>18348.610000000004</v>
+        <v>30583.75</v>
       </c>
       <c r="Q27" s="22" t="s">
         <v>77</v>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="AQ27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <f t="shared" si="1"/>
@@ -28452,7 +28452,7 @@
       <c r="N28" s="7"/>
       <c r="P28" s="20">
         <f>P27/1000</f>
-        <v>18.348610000000004</v>
+        <v>30.583749999999998</v>
       </c>
       <c r="Q28" s="22" t="s">
         <v>79</v>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="AL28">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28">
         <f t="shared" si="3"/>
@@ -28498,7 +28498,7 @@
       </c>
       <c r="AQ28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <f t="shared" si="1"/>
@@ -28570,7 +28570,7 @@
       <c r="P30" s="20"/>
       <c r="Q30" s="23">
         <f>Q34</f>
-        <v>0.23683905151248325</v>
+        <v>0.24093697298061989</v>
       </c>
       <c r="V30" s="7"/>
       <c r="W30" t="s">
@@ -28580,7 +28580,7 @@
         <v>90.8</v>
       </c>
       <c r="AA30" s="34">
-        <v>56.92</v>
+        <v>70.08</v>
       </c>
       <c r="AC30" s="13">
         <f t="shared" si="4"/>
@@ -28637,11 +28637,11 @@
         <v>0</v>
       </c>
       <c r="AA31" s="34">
-        <v>126.05</v>
+        <v>125.01</v>
       </c>
       <c r="AC31" s="13">
         <f t="shared" si="4"/>
-        <v>126.05</v>
+        <v>125.01</v>
       </c>
       <c r="AD31" s="22"/>
       <c r="AJ31">
@@ -28688,7 +28688,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="23">
         <f>Q36</f>
-        <v>0.76316094848751681</v>
+        <v>0.75906302701938011</v>
       </c>
       <c r="V32" s="7"/>
       <c r="W32" t="s">
@@ -28755,11 +28755,11 @@
         <v>10</v>
       </c>
       <c r="AA33" s="34">
-        <v>51.44</v>
+        <v>58.32</v>
       </c>
       <c r="AC33" s="13">
         <f t="shared" si="4"/>
-        <v>41.44</v>
+        <v>48.32</v>
       </c>
       <c r="AD33" s="22"/>
       <c r="AJ33">
@@ -28806,7 +28806,7 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="25">
         <f>P23/P25</f>
-        <v>0.23683905151248325</v>
+        <v>0.24093697298061989</v>
       </c>
       <c r="R34" s="3"/>
       <c r="V34" s="7"/>
@@ -28814,14 +28814,14 @@
         <v>41</v>
       </c>
       <c r="Y34" s="44">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AA34" s="14">
         <v>29</v>
       </c>
       <c r="AC34" s="13">
         <f t="shared" si="4"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AD34" s="22"/>
       <c r="AJ34">
@@ -28871,14 +28871,14 @@
         <v>42</v>
       </c>
       <c r="Y35" s="13">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AA35" s="14">
         <v>139</v>
       </c>
       <c r="AC35" s="13">
         <f t="shared" si="4"/>
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="AD35" s="22"/>
       <c r="AJ35">
@@ -28925,7 +28925,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="25">
         <f>P27/P25</f>
-        <v>0.76316094848751681</v>
+        <v>0.75906302701938011</v>
       </c>
       <c r="R36" s="3"/>
       <c r="V36" s="7"/>
@@ -29049,12 +29049,12 @@
         <v>0</v>
       </c>
       <c r="AA38" s="34">
-        <v>62.11</v>
+        <v>85.3</v>
       </c>
       <c r="AB38" s="39"/>
       <c r="AC38" s="13">
         <f t="shared" si="4"/>
-        <v>62.11</v>
+        <v>85.3</v>
       </c>
       <c r="AD38" s="22"/>
       <c r="AJ38">
@@ -29104,12 +29104,12 @@
         <v>0</v>
       </c>
       <c r="AA39" s="34">
-        <v>31.04</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="AB39" s="40"/>
       <c r="AC39" s="13">
         <f t="shared" si="4"/>
-        <v>31.04</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="AD39" s="22"/>
       <c r="AJ39">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="AM80">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO80">
         <f t="shared" si="15"/>
@@ -30862,7 +30862,7 @@
       </c>
       <c r="AR80">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="36:44" x14ac:dyDescent="0.25">
@@ -30896,7 +30896,7 @@
       </c>
       <c r="AR81">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="36:44" x14ac:dyDescent="0.25">
@@ -31691,11 +31691,11 @@
       </c>
       <c r="AL105" s="13">
         <f>200-Q30*100</f>
-        <v>176.31609484875167</v>
+        <v>175.90630270193802</v>
       </c>
       <c r="AM105">
         <f>200-Q32*100</f>
-        <v>123.68390515124833</v>
+        <v>124.09369729806198</v>
       </c>
       <c r="AO105">
         <f t="shared" si="15"/>
@@ -31706,11 +31706,11 @@
       </c>
       <c r="AQ105" s="13">
         <f>200-Q11*100</f>
-        <v>177.01835827173846</v>
+        <v>175.29993464028152</v>
       </c>
       <c r="AR105">
         <f>200-Q13*100</f>
-        <v>122.98164172826152</v>
+        <v>124.70006535971847</v>
       </c>
     </row>
   </sheetData>
@@ -31861,12 +31861,24 @@
       <c r="J2" s="14">
         <v>0</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
+      <c r="K2" s="14">
+        <v>0</v>
+      </c>
+      <c r="L2" s="14">
+        <v>0</v>
+      </c>
+      <c r="M2" s="14">
+        <v>0</v>
+      </c>
+      <c r="N2" s="14">
+        <v>0</v>
+      </c>
+      <c r="O2" s="14">
+        <v>0</v>
+      </c>
+      <c r="P2" s="14">
+        <v>0</v>
+      </c>
       <c r="Q2" s="14"/>
       <c r="R2" s="14"/>
       <c r="S2" s="14"/>
@@ -31912,12 +31924,24 @@
       <c r="J3" s="14">
         <v>0</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
+      <c r="K3" s="14">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14">
+        <v>0</v>
+      </c>
+      <c r="M3" s="14">
+        <v>0</v>
+      </c>
+      <c r="N3" s="14">
+        <v>0</v>
+      </c>
+      <c r="O3" s="14">
+        <v>0</v>
+      </c>
+      <c r="P3" s="14">
+        <v>0</v>
+      </c>
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="S3" s="14"/>
@@ -31965,12 +31989,24 @@
       <c r="J4" s="14">
         <v>0</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
+      <c r="K4" s="14">
+        <v>0</v>
+      </c>
+      <c r="L4" s="14">
+        <v>0</v>
+      </c>
+      <c r="M4" s="14">
+        <v>0</v>
+      </c>
+      <c r="N4" s="14">
+        <v>0</v>
+      </c>
+      <c r="O4" s="14">
+        <v>0</v>
+      </c>
+      <c r="P4" s="14">
+        <v>0</v>
+      </c>
       <c r="Q4" s="14"/>
       <c r="R4" s="14"/>
       <c r="S4" s="14"/>
@@ -32016,12 +32052,24 @@
       <c r="J5" s="14">
         <v>0</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
+      <c r="K5" s="14">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14">
+        <v>0</v>
+      </c>
+      <c r="O5" s="14">
+        <v>0</v>
+      </c>
+      <c r="P5" s="14">
+        <v>0</v>
+      </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="14"/>
       <c r="S5" s="14"/>
@@ -32067,12 +32115,24 @@
       <c r="J6" s="14">
         <v>0</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
+      <c r="K6" s="14">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
+        <v>0</v>
+      </c>
+      <c r="M6" s="14">
+        <v>0</v>
+      </c>
+      <c r="N6" s="14">
+        <v>0</v>
+      </c>
+      <c r="O6" s="14">
+        <v>0</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0</v>
+      </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
       <c r="S6" s="14"/>
@@ -32118,12 +32178,24 @@
       <c r="J7" s="14">
         <v>0</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
+      <c r="K7" s="14">
+        <v>0</v>
+      </c>
+      <c r="L7" s="14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14">
+        <v>0</v>
+      </c>
+      <c r="O7" s="14">
+        <v>0</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0</v>
+      </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
       <c r="S7" s="14"/>
@@ -32169,6 +32241,24 @@
       <c r="J8" s="13">
         <v>50</v>
       </c>
+      <c r="K8" s="13">
+        <v>50</v>
+      </c>
+      <c r="L8" s="13">
+        <v>50</v>
+      </c>
+      <c r="M8" s="13">
+        <v>50</v>
+      </c>
+      <c r="N8" s="13">
+        <v>50</v>
+      </c>
+      <c r="O8" s="13">
+        <v>50</v>
+      </c>
+      <c r="P8" s="13">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
@@ -32201,6 +32291,24 @@
       <c r="J9" s="13">
         <v>0</v>
       </c>
+      <c r="K9" s="13">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="13">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13">
+        <v>0</v>
+      </c>
+      <c r="O9" s="13">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
@@ -32233,6 +32341,24 @@
       <c r="J10" s="13">
         <v>0</v>
       </c>
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13">
+        <v>0</v>
+      </c>
+      <c r="N10" s="13">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
@@ -32265,6 +32391,24 @@
       <c r="J11" s="13">
         <v>80</v>
       </c>
+      <c r="K11" s="13">
+        <v>80</v>
+      </c>
+      <c r="L11" s="13">
+        <v>80</v>
+      </c>
+      <c r="M11" s="13">
+        <v>80</v>
+      </c>
+      <c r="N11" s="13">
+        <v>80</v>
+      </c>
+      <c r="O11" s="13">
+        <v>80</v>
+      </c>
+      <c r="P11" s="13">
+        <v>80</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
@@ -32297,6 +32441,24 @@
       <c r="J12" s="13">
         <v>0</v>
       </c>
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
@@ -32329,6 +32491,24 @@
       <c r="J13" s="13">
         <v>0</v>
       </c>
+      <c r="K13" s="13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
@@ -32361,6 +32541,24 @@
       <c r="J14" s="13">
         <v>0</v>
       </c>
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13">
+        <v>0</v>
+      </c>
+      <c r="N14" s="13">
+        <v>0</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
@@ -32393,6 +32591,24 @@
       <c r="J15" s="13">
         <v>10</v>
       </c>
+      <c r="K15" s="13">
+        <v>10</v>
+      </c>
+      <c r="L15" s="13">
+        <v>10</v>
+      </c>
+      <c r="M15" s="13">
+        <v>10</v>
+      </c>
+      <c r="N15" s="13">
+        <v>10</v>
+      </c>
+      <c r="O15" s="13">
+        <v>10</v>
+      </c>
+      <c r="P15" s="13">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -32425,6 +32641,24 @@
       <c r="J16" s="13">
         <v>0</v>
       </c>
+      <c r="K16" s="13">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13">
+        <v>0</v>
+      </c>
+      <c r="N16" s="13">
+        <v>0</v>
+      </c>
+      <c r="O16" s="13">
+        <v>0</v>
+      </c>
+      <c r="P16" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
@@ -32457,12 +32691,24 @@
       <c r="J17" s="32">
         <v>108.6</v>
       </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
+      <c r="K17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="L17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="M17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="N17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="O17" s="32">
+        <v>108.6</v>
+      </c>
+      <c r="P17" s="32">
+        <v>108.6</v>
+      </c>
       <c r="Q17" s="32"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
@@ -32508,6 +32754,24 @@
       <c r="J18" s="13">
         <v>0</v>
       </c>
+      <c r="K18" s="13">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13">
+        <v>0</v>
+      </c>
+      <c r="M18" s="13">
+        <v>0</v>
+      </c>
+      <c r="N18" s="13">
+        <v>0</v>
+      </c>
+      <c r="O18" s="13">
+        <v>0</v>
+      </c>
+      <c r="P18" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
@@ -32540,6 +32804,24 @@
       <c r="J19" s="13">
         <v>34</v>
       </c>
+      <c r="K19" s="13">
+        <v>34</v>
+      </c>
+      <c r="L19" s="13">
+        <v>34</v>
+      </c>
+      <c r="M19" s="13">
+        <v>34</v>
+      </c>
+      <c r="N19" s="13">
+        <v>34</v>
+      </c>
+      <c r="O19" s="13">
+        <v>34</v>
+      </c>
+      <c r="P19" s="13">
+        <v>34</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
@@ -32572,6 +32854,24 @@
       <c r="J20" s="13">
         <v>0</v>
       </c>
+      <c r="K20" s="13">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13">
+        <v>0</v>
+      </c>
+      <c r="N20" s="13">
+        <v>0</v>
+      </c>
+      <c r="O20" s="13">
+        <v>0</v>
+      </c>
+      <c r="P20" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
@@ -32604,6 +32904,24 @@
       <c r="J21" s="13">
         <v>0</v>
       </c>
+      <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="13">
+        <v>0</v>
+      </c>
+      <c r="N21" s="13">
+        <v>0</v>
+      </c>
+      <c r="O21" s="13">
+        <v>0</v>
+      </c>
+      <c r="P21" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
@@ -32636,6 +32954,24 @@
       <c r="J22" s="13">
         <v>0</v>
       </c>
+      <c r="K22" s="13">
+        <v>0</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13">
+        <v>0</v>
+      </c>
+      <c r="N22" s="13">
+        <v>0</v>
+      </c>
+      <c r="O22" s="13">
+        <v>0</v>
+      </c>
+      <c r="P22" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
@@ -32668,6 +33004,24 @@
       <c r="J23" s="13">
         <v>0</v>
       </c>
+      <c r="K23" s="13">
+        <v>0</v>
+      </c>
+      <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="13">
+        <v>0</v>
+      </c>
+      <c r="N23" s="13">
+        <v>0</v>
+      </c>
+      <c r="O23" s="13">
+        <v>0</v>
+      </c>
+      <c r="P23" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
@@ -32700,12 +33054,24 @@
       <c r="J24" s="32">
         <v>42.5</v>
       </c>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
+      <c r="K24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="L24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="M24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="N24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="O24" s="32">
+        <v>42.5</v>
+      </c>
+      <c r="P24" s="32">
+        <v>42.5</v>
+      </c>
       <c r="Q24" s="32"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
@@ -32751,6 +33117,24 @@
       <c r="J25" s="13">
         <v>0</v>
       </c>
+      <c r="K25" s="13">
+        <v>0</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="M25" s="13">
+        <v>0</v>
+      </c>
+      <c r="N25" s="13">
+        <v>0</v>
+      </c>
+      <c r="O25" s="13">
+        <v>0</v>
+      </c>
+      <c r="P25" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
@@ -32783,12 +33167,24 @@
       <c r="J26" s="32">
         <v>90.8</v>
       </c>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
-      <c r="P26" s="32"/>
+      <c r="K26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="L26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="M26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="N26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="O26" s="32">
+        <v>90.8</v>
+      </c>
+      <c r="P26" s="32">
+        <v>90.8</v>
+      </c>
       <c r="Q26" s="32"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
@@ -32834,6 +33230,24 @@
       <c r="J27" s="13">
         <v>0</v>
       </c>
+      <c r="K27" s="13">
+        <v>0</v>
+      </c>
+      <c r="L27" s="13">
+        <v>0</v>
+      </c>
+      <c r="M27" s="13">
+        <v>0</v>
+      </c>
+      <c r="N27" s="13">
+        <v>0</v>
+      </c>
+      <c r="O27" s="13">
+        <v>0</v>
+      </c>
+      <c r="P27" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
@@ -32866,6 +33280,24 @@
       <c r="J28" s="13">
         <v>0</v>
       </c>
+      <c r="K28" s="13">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13">
+        <v>0</v>
+      </c>
+      <c r="N28" s="13">
+        <v>0</v>
+      </c>
+      <c r="O28" s="13">
+        <v>0</v>
+      </c>
+      <c r="P28" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
@@ -32898,12 +33330,24 @@
       <c r="J29" s="31">
         <v>10</v>
       </c>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
+      <c r="K29" s="31">
+        <v>10</v>
+      </c>
+      <c r="L29" s="31">
+        <v>10</v>
+      </c>
+      <c r="M29" s="31">
+        <v>10</v>
+      </c>
+      <c r="N29" s="31">
+        <v>10</v>
+      </c>
+      <c r="O29" s="31">
+        <v>10</v>
+      </c>
+      <c r="P29" s="31">
+        <v>10</v>
+      </c>
       <c r="Q29" s="31"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
@@ -32945,12 +33389,24 @@
       <c r="J30" s="33">
         <v>10</v>
       </c>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
+      <c r="K30" s="33">
+        <v>44</v>
+      </c>
+      <c r="L30" s="33">
+        <v>44</v>
+      </c>
+      <c r="M30" s="33">
+        <v>44</v>
+      </c>
+      <c r="N30" s="33">
+        <v>44</v>
+      </c>
+      <c r="O30" s="33">
+        <v>44</v>
+      </c>
+      <c r="P30" s="33">
+        <v>44</v>
+      </c>
       <c r="Q30" s="33"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
@@ -32996,6 +33452,24 @@
       <c r="J31" s="13">
         <v>12</v>
       </c>
+      <c r="K31" s="13">
+        <v>35</v>
+      </c>
+      <c r="L31" s="13">
+        <v>35</v>
+      </c>
+      <c r="M31" s="13">
+        <v>35</v>
+      </c>
+      <c r="N31" s="13">
+        <v>35</v>
+      </c>
+      <c r="O31" s="13">
+        <v>35</v>
+      </c>
+      <c r="P31" s="13">
+        <v>35</v>
+      </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
@@ -33028,8 +33502,26 @@
       <c r="J32" s="13">
         <v>0</v>
       </c>
+      <c r="K32" s="13">
+        <v>0</v>
+      </c>
+      <c r="L32" s="13">
+        <v>0</v>
+      </c>
+      <c r="M32" s="13">
+        <v>0</v>
+      </c>
+      <c r="N32" s="13">
+        <v>0</v>
+      </c>
+      <c r="O32" s="13">
+        <v>0</v>
+      </c>
+      <c r="P32" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>44</v>
       </c>
@@ -33060,8 +33552,26 @@
       <c r="J33" s="13">
         <v>30</v>
       </c>
+      <c r="K33" s="13">
+        <v>30</v>
+      </c>
+      <c r="L33" s="13">
+        <v>30</v>
+      </c>
+      <c r="M33" s="13">
+        <v>30</v>
+      </c>
+      <c r="N33" s="13">
+        <v>30</v>
+      </c>
+      <c r="O33" s="13">
+        <v>30</v>
+      </c>
+      <c r="P33" s="13">
+        <v>30</v>
+      </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
         <v>45</v>
       </c>
@@ -33092,8 +33602,26 @@
       <c r="J34" s="13">
         <v>0</v>
       </c>
+      <c r="K34" s="13">
+        <v>0</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="13">
+        <v>0</v>
+      </c>
+      <c r="N34" s="13">
+        <v>0</v>
+      </c>
+      <c r="O34" s="13">
+        <v>0</v>
+      </c>
+      <c r="P34" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>46</v>
       </c>
@@ -33124,8 +33652,26 @@
       <c r="J35" s="13">
         <v>0</v>
       </c>
+      <c r="K35" s="13">
+        <v>0</v>
+      </c>
+      <c r="L35" s="13">
+        <v>0</v>
+      </c>
+      <c r="M35" s="13">
+        <v>0</v>
+      </c>
+      <c r="N35" s="13">
+        <v>0</v>
+      </c>
+      <c r="O35" s="13">
+        <v>0</v>
+      </c>
+      <c r="P35" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
@@ -33156,8 +33702,26 @@
       <c r="J36" s="13">
         <v>0</v>
       </c>
+      <c r="K36" s="13">
+        <v>0</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="13">
+        <v>0</v>
+      </c>
+      <c r="N36" s="13">
+        <v>0</v>
+      </c>
+      <c r="O36" s="13">
+        <v>0</v>
+      </c>
+      <c r="P36" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>48</v>
       </c>
@@ -33188,8 +33752,26 @@
       <c r="J37" s="13">
         <v>2</v>
       </c>
+      <c r="K37" s="13">
+        <v>2</v>
+      </c>
+      <c r="L37" s="13">
+        <v>2</v>
+      </c>
+      <c r="M37" s="13">
+        <v>2</v>
+      </c>
+      <c r="N37" s="13">
+        <v>2</v>
+      </c>
+      <c r="O37" s="13">
+        <v>2</v>
+      </c>
+      <c r="P37" s="13">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>49</v>
       </c>
@@ -33220,8 +33802,26 @@
       <c r="J38" s="13">
         <v>32</v>
       </c>
+      <c r="K38" s="13">
+        <v>32</v>
+      </c>
+      <c r="L38" s="13">
+        <v>32</v>
+      </c>
+      <c r="M38" s="13">
+        <v>32</v>
+      </c>
+      <c r="N38" s="13">
+        <v>32</v>
+      </c>
+      <c r="O38" s="13">
+        <v>32</v>
+      </c>
+      <c r="P38" s="13">
+        <v>32</v>
+      </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>50</v>
       </c>
@@ -33252,8 +33852,26 @@
       <c r="J39" s="13">
         <v>0</v>
       </c>
+      <c r="K39" s="13">
+        <v>0</v>
+      </c>
+      <c r="L39" s="13">
+        <v>0</v>
+      </c>
+      <c r="M39" s="13">
+        <v>0</v>
+      </c>
+      <c r="N39" s="13">
+        <v>0</v>
+      </c>
+      <c r="O39" s="13">
+        <v>0</v>
+      </c>
+      <c r="P39" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
         <v>51</v>
       </c>
@@ -33284,8 +33902,26 @@
       <c r="J40" s="13">
         <v>0</v>
       </c>
+      <c r="K40" s="13">
+        <v>0</v>
+      </c>
+      <c r="L40" s="13">
+        <v>0</v>
+      </c>
+      <c r="M40" s="13">
+        <v>0</v>
+      </c>
+      <c r="N40" s="13">
+        <v>0</v>
+      </c>
+      <c r="O40" s="13">
+        <v>0</v>
+      </c>
+      <c r="P40" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>52</v>
       </c>
@@ -33316,8 +33952,26 @@
       <c r="J41" s="13">
         <v>0</v>
       </c>
+      <c r="K41" s="13">
+        <v>0</v>
+      </c>
+      <c r="L41" s="13">
+        <v>0</v>
+      </c>
+      <c r="M41" s="13">
+        <v>0</v>
+      </c>
+      <c r="N41" s="13">
+        <v>0</v>
+      </c>
+      <c r="O41" s="13">
+        <v>0</v>
+      </c>
+      <c r="P41" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
         <v>53</v>
       </c>
@@ -33348,13 +34002,31 @@
       <c r="J42" s="13">
         <v>0</v>
       </c>
+      <c r="K42" s="13">
+        <v>0</v>
+      </c>
+      <c r="L42" s="13">
+        <v>0</v>
+      </c>
+      <c r="M42" s="13">
+        <v>0</v>
+      </c>
+      <c r="N42" s="13">
+        <v>0</v>
+      </c>
+      <c r="O42" s="13">
+        <v>0</v>
+      </c>
+      <c r="P42" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>55</v>
       </c>
@@ -33385,8 +34057,26 @@
       <c r="J44" s="13">
         <v>0</v>
       </c>
+      <c r="K44" s="13">
+        <v>0</v>
+      </c>
+      <c r="L44" s="13">
+        <v>0</v>
+      </c>
+      <c r="M44" s="13">
+        <v>0</v>
+      </c>
+      <c r="N44" s="13">
+        <v>0</v>
+      </c>
+      <c r="O44" s="13">
+        <v>0</v>
+      </c>
+      <c r="P44" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>56</v>
       </c>
@@ -33417,8 +34107,26 @@
       <c r="J45" s="13">
         <v>0</v>
       </c>
+      <c r="K45" s="13">
+        <v>0</v>
+      </c>
+      <c r="L45" s="13">
+        <v>0</v>
+      </c>
+      <c r="M45" s="13">
+        <v>0</v>
+      </c>
+      <c r="N45" s="13">
+        <v>0</v>
+      </c>
+      <c r="O45" s="13">
+        <v>0</v>
+      </c>
+      <c r="P45" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>57</v>
       </c>
@@ -33449,8 +34157,26 @@
       <c r="J46" s="13">
         <v>0</v>
       </c>
+      <c r="K46" s="13">
+        <v>0</v>
+      </c>
+      <c r="L46" s="13">
+        <v>0</v>
+      </c>
+      <c r="M46" s="13">
+        <v>0</v>
+      </c>
+      <c r="N46" s="13">
+        <v>0</v>
+      </c>
+      <c r="O46" s="13">
+        <v>0</v>
+      </c>
+      <c r="P46" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>58</v>
       </c>
@@ -33481,8 +34207,26 @@
       <c r="J47" s="13">
         <v>0</v>
       </c>
+      <c r="K47" s="13">
+        <v>0</v>
+      </c>
+      <c r="L47" s="13">
+        <v>0</v>
+      </c>
+      <c r="M47" s="13">
+        <v>0</v>
+      </c>
+      <c r="N47" s="13">
+        <v>0</v>
+      </c>
+      <c r="O47" s="13">
+        <v>0</v>
+      </c>
+      <c r="P47" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
         <v>59</v>
       </c>
@@ -33511,6 +34255,24 @@
         <v>0</v>
       </c>
       <c r="J48" s="13">
+        <v>0</v>
+      </c>
+      <c r="K48" s="13">
+        <v>0</v>
+      </c>
+      <c r="L48" s="13">
+        <v>0</v>
+      </c>
+      <c r="M48" s="13">
+        <v>0</v>
+      </c>
+      <c r="N48" s="13">
+        <v>0</v>
+      </c>
+      <c r="O48" s="13">
+        <v>0</v>
+      </c>
+      <c r="P48" s="13">
         <v>0</v>
       </c>
     </row>
@@ -33545,6 +34307,24 @@
       <c r="J49" s="13">
         <v>0</v>
       </c>
+      <c r="K49" s="13">
+        <v>0</v>
+      </c>
+      <c r="L49" s="13">
+        <v>0</v>
+      </c>
+      <c r="M49" s="13">
+        <v>0</v>
+      </c>
+      <c r="N49" s="13">
+        <v>0</v>
+      </c>
+      <c r="O49" s="13">
+        <v>0</v>
+      </c>
+      <c r="P49" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
@@ -33577,6 +34357,24 @@
       <c r="J50" s="13">
         <v>41</v>
       </c>
+      <c r="K50" s="13">
+        <v>41</v>
+      </c>
+      <c r="L50" s="13">
+        <v>41</v>
+      </c>
+      <c r="M50" s="13">
+        <v>41</v>
+      </c>
+      <c r="N50" s="13">
+        <v>41</v>
+      </c>
+      <c r="O50" s="13">
+        <v>41</v>
+      </c>
+      <c r="P50" s="13">
+        <v>41</v>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
@@ -33609,6 +34407,24 @@
       <c r="J51" s="13">
         <v>0</v>
       </c>
+      <c r="K51" s="13">
+        <v>0</v>
+      </c>
+      <c r="L51" s="13">
+        <v>0</v>
+      </c>
+      <c r="M51" s="13">
+        <v>0</v>
+      </c>
+      <c r="N51" s="13">
+        <v>0</v>
+      </c>
+      <c r="O51" s="13">
+        <v>0</v>
+      </c>
+      <c r="P51" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
@@ -33641,6 +34457,24 @@
       <c r="J52" s="13">
         <v>0</v>
       </c>
+      <c r="K52" s="13">
+        <v>0</v>
+      </c>
+      <c r="L52" s="13">
+        <v>0</v>
+      </c>
+      <c r="M52" s="13">
+        <v>0</v>
+      </c>
+      <c r="N52" s="13">
+        <v>0</v>
+      </c>
+      <c r="O52" s="13">
+        <v>0</v>
+      </c>
+      <c r="P52" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
@@ -33673,6 +34507,24 @@
       <c r="J53" s="13">
         <v>0</v>
       </c>
+      <c r="K53" s="13">
+        <v>0</v>
+      </c>
+      <c r="L53" s="13">
+        <v>0</v>
+      </c>
+      <c r="M53" s="13">
+        <v>0</v>
+      </c>
+      <c r="N53" s="13">
+        <v>0</v>
+      </c>
+      <c r="O53" s="13">
+        <v>0</v>
+      </c>
+      <c r="P53" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
@@ -33705,6 +34557,24 @@
       <c r="J54" s="13">
         <v>0</v>
       </c>
+      <c r="K54" s="13">
+        <v>0</v>
+      </c>
+      <c r="L54" s="13">
+        <v>0</v>
+      </c>
+      <c r="M54" s="13">
+        <v>0</v>
+      </c>
+      <c r="N54" s="13">
+        <v>0</v>
+      </c>
+      <c r="O54" s="13">
+        <v>0</v>
+      </c>
+      <c r="P54" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
@@ -33737,6 +34607,24 @@
       <c r="J55" s="13">
         <v>59</v>
       </c>
+      <c r="K55" s="13">
+        <v>59</v>
+      </c>
+      <c r="L55" s="13">
+        <v>59</v>
+      </c>
+      <c r="M55" s="13">
+        <v>59</v>
+      </c>
+      <c r="N55" s="13">
+        <v>59</v>
+      </c>
+      <c r="O55" s="13">
+        <v>59</v>
+      </c>
+      <c r="P55" s="13">
+        <v>59</v>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
@@ -33780,27 +34668,27 @@
       </c>
       <c r="K57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>668.90000000000009</v>
       </c>
       <c r="L57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>668.90000000000009</v>
       </c>
       <c r="M57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>668.90000000000009</v>
       </c>
       <c r="N57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>668.90000000000009</v>
       </c>
       <c r="O57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>668.90000000000009</v>
       </c>
       <c r="P57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>668.90000000000009</v>
       </c>
       <c r="Q57" s="13">
         <f t="shared" si="0"/>
@@ -33873,7 +34761,7 @@
       </c>
       <c r="B59" s="13">
         <f>SUM(A57:AF57)</f>
-        <v>5694.2999999999993</v>
+        <v>9707.6999999999971</v>
       </c>
     </row>
   </sheetData>
@@ -34018,12 +34906,24 @@
       <c r="J2" s="14">
         <v>66</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
+      <c r="K2" s="14">
+        <v>66</v>
+      </c>
+      <c r="L2" s="14">
+        <v>66</v>
+      </c>
+      <c r="M2" s="14">
+        <v>66</v>
+      </c>
+      <c r="N2" s="14">
+        <v>66</v>
+      </c>
+      <c r="O2" s="14">
+        <v>66</v>
+      </c>
+      <c r="P2" s="14">
+        <v>66</v>
+      </c>
       <c r="Q2" s="14"/>
       <c r="R2" s="14"/>
       <c r="S2" s="14"/>
@@ -34072,12 +34972,24 @@
       <c r="J3" s="14">
         <v>0</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
+      <c r="K3" s="14">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14">
+        <v>0</v>
+      </c>
+      <c r="M3" s="14">
+        <v>0</v>
+      </c>
+      <c r="N3" s="14">
+        <v>0</v>
+      </c>
+      <c r="O3" s="14">
+        <v>0</v>
+      </c>
+      <c r="P3" s="14">
+        <v>0</v>
+      </c>
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="S3" s="14"/>
@@ -34148,12 +35060,24 @@
       <c r="J4" s="14">
         <v>30</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
+      <c r="K4" s="14">
+        <v>30</v>
+      </c>
+      <c r="L4" s="14">
+        <v>30</v>
+      </c>
+      <c r="M4" s="14">
+        <v>30</v>
+      </c>
+      <c r="N4" s="14">
+        <v>30</v>
+      </c>
+      <c r="O4" s="14">
+        <v>30</v>
+      </c>
+      <c r="P4" s="14">
+        <v>30</v>
+      </c>
       <c r="Q4" s="14"/>
       <c r="R4" s="14"/>
       <c r="S4" s="14"/>
@@ -34202,12 +35126,24 @@
       <c r="J5" s="14">
         <v>68</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
+      <c r="K5" s="14">
+        <v>68</v>
+      </c>
+      <c r="L5" s="14">
+        <v>68</v>
+      </c>
+      <c r="M5" s="14">
+        <v>68</v>
+      </c>
+      <c r="N5" s="14">
+        <v>68</v>
+      </c>
+      <c r="O5" s="14">
+        <v>68</v>
+      </c>
+      <c r="P5" s="14">
+        <v>68</v>
+      </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="14"/>
       <c r="S5" s="14"/>
@@ -34256,12 +35192,24 @@
       <c r="J6" s="14">
         <v>61</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
+      <c r="K6" s="14">
+        <v>61</v>
+      </c>
+      <c r="L6" s="14">
+        <v>61</v>
+      </c>
+      <c r="M6" s="14">
+        <v>61</v>
+      </c>
+      <c r="N6" s="14">
+        <v>61</v>
+      </c>
+      <c r="O6" s="14">
+        <v>61</v>
+      </c>
+      <c r="P6" s="14">
+        <v>61</v>
+      </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
       <c r="S6" s="14"/>
@@ -34310,12 +35258,24 @@
       <c r="J7" s="14">
         <v>0</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
+      <c r="K7" s="14">
+        <v>0</v>
+      </c>
+      <c r="L7" s="14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14">
+        <v>0</v>
+      </c>
+      <c r="O7" s="14">
+        <v>0</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0</v>
+      </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
       <c r="S7" s="14"/>
@@ -34364,6 +35324,24 @@
       <c r="J8">
         <v>38</v>
       </c>
+      <c r="K8">
+        <v>38</v>
+      </c>
+      <c r="L8">
+        <v>38</v>
+      </c>
+      <c r="M8">
+        <v>38</v>
+      </c>
+      <c r="N8">
+        <v>38</v>
+      </c>
+      <c r="O8">
+        <v>38</v>
+      </c>
+      <c r="P8">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -34396,12 +35374,24 @@
       <c r="J9" s="14">
         <v>46</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
+      <c r="K9" s="14">
+        <v>46</v>
+      </c>
+      <c r="L9" s="14">
+        <v>46</v>
+      </c>
+      <c r="M9" s="14">
+        <v>46</v>
+      </c>
+      <c r="N9" s="14">
+        <v>46</v>
+      </c>
+      <c r="O9" s="14">
+        <v>46</v>
+      </c>
+      <c r="P9" s="14">
+        <v>46</v>
+      </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="14"/>
       <c r="S9" s="14"/>
@@ -34450,12 +35440,24 @@
       <c r="J10" s="14">
         <v>147</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
+      <c r="K10" s="14">
+        <v>147</v>
+      </c>
+      <c r="L10" s="14">
+        <v>147</v>
+      </c>
+      <c r="M10" s="14">
+        <v>147</v>
+      </c>
+      <c r="N10" s="14">
+        <v>147</v>
+      </c>
+      <c r="O10" s="14">
+        <v>147</v>
+      </c>
+      <c r="P10" s="14">
+        <v>147</v>
+      </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="14"/>
       <c r="S10" s="14"/>
@@ -34504,12 +35506,24 @@
       <c r="J11" s="14">
         <v>30</v>
       </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
+      <c r="K11" s="14">
+        <v>30</v>
+      </c>
+      <c r="L11" s="14">
+        <v>30</v>
+      </c>
+      <c r="M11" s="14">
+        <v>30</v>
+      </c>
+      <c r="N11" s="14">
+        <v>30</v>
+      </c>
+      <c r="O11" s="14">
+        <v>30</v>
+      </c>
+      <c r="P11" s="14">
+        <v>30</v>
+      </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="14"/>
       <c r="S11" s="14"/>
@@ -34558,12 +35572,24 @@
       <c r="J12" s="14">
         <v>102</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
+      <c r="K12" s="14">
+        <v>102</v>
+      </c>
+      <c r="L12" s="14">
+        <v>102</v>
+      </c>
+      <c r="M12" s="14">
+        <v>102</v>
+      </c>
+      <c r="N12" s="14">
+        <v>102</v>
+      </c>
+      <c r="O12" s="14">
+        <v>102</v>
+      </c>
+      <c r="P12" s="14">
+        <v>102</v>
+      </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="14"/>
       <c r="S12" s="14"/>
@@ -34612,12 +35638,24 @@
       <c r="J13" s="14">
         <v>54</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
+      <c r="K13" s="14">
+        <v>54</v>
+      </c>
+      <c r="L13" s="14">
+        <v>54</v>
+      </c>
+      <c r="M13" s="14">
+        <v>54</v>
+      </c>
+      <c r="N13" s="14">
+        <v>54</v>
+      </c>
+      <c r="O13" s="14">
+        <v>54</v>
+      </c>
+      <c r="P13" s="14">
+        <v>54</v>
+      </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="14"/>
       <c r="S13" s="14"/>
@@ -34666,12 +35704,24 @@
       <c r="J14" s="14">
         <v>172</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
+      <c r="K14" s="14">
+        <v>172</v>
+      </c>
+      <c r="L14" s="14">
+        <v>172</v>
+      </c>
+      <c r="M14" s="14">
+        <v>172</v>
+      </c>
+      <c r="N14" s="14">
+        <v>172</v>
+      </c>
+      <c r="O14" s="14">
+        <v>172</v>
+      </c>
+      <c r="P14" s="14">
+        <v>172</v>
+      </c>
       <c r="Q14" s="14"/>
       <c r="R14" s="14"/>
       <c r="S14" s="14"/>
@@ -34720,12 +35770,24 @@
       <c r="J15" s="14">
         <v>50</v>
       </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
+      <c r="K15" s="14">
+        <v>50</v>
+      </c>
+      <c r="L15" s="14">
+        <v>50</v>
+      </c>
+      <c r="M15" s="14">
+        <v>50</v>
+      </c>
+      <c r="N15" s="14">
+        <v>50</v>
+      </c>
+      <c r="O15" s="14">
+        <v>50</v>
+      </c>
+      <c r="P15" s="14">
+        <v>50</v>
+      </c>
       <c r="Q15" s="14"/>
       <c r="R15" s="14"/>
       <c r="S15" s="14"/>
@@ -34774,6 +35836,24 @@
       <c r="J16">
         <v>58</v>
       </c>
+      <c r="K16">
+        <v>58</v>
+      </c>
+      <c r="L16">
+        <v>58</v>
+      </c>
+      <c r="M16">
+        <v>58</v>
+      </c>
+      <c r="N16">
+        <v>58</v>
+      </c>
+      <c r="O16">
+        <v>58</v>
+      </c>
+      <c r="P16">
+        <v>58</v>
+      </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -34806,6 +35886,24 @@
       <c r="J17">
         <v>104</v>
       </c>
+      <c r="K17">
+        <v>104</v>
+      </c>
+      <c r="L17">
+        <v>104</v>
+      </c>
+      <c r="M17">
+        <v>104</v>
+      </c>
+      <c r="N17">
+        <v>104</v>
+      </c>
+      <c r="O17">
+        <v>104</v>
+      </c>
+      <c r="P17">
+        <v>104</v>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -34838,12 +35936,24 @@
       <c r="J18" s="14">
         <v>0</v>
       </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
+      <c r="K18" s="14">
+        <v>0</v>
+      </c>
+      <c r="L18" s="14">
+        <v>0</v>
+      </c>
+      <c r="M18" s="14">
+        <v>0</v>
+      </c>
+      <c r="N18" s="14">
+        <v>0</v>
+      </c>
+      <c r="O18" s="14">
+        <v>0</v>
+      </c>
+      <c r="P18" s="14">
+        <v>0</v>
+      </c>
       <c r="Q18" s="14"/>
       <c r="R18" s="14"/>
       <c r="S18" s="14"/>
@@ -34892,12 +36002,24 @@
       <c r="J19" s="14">
         <v>51</v>
       </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
+      <c r="K19" s="14">
+        <v>51</v>
+      </c>
+      <c r="L19" s="14">
+        <v>51</v>
+      </c>
+      <c r="M19" s="14">
+        <v>51</v>
+      </c>
+      <c r="N19" s="14">
+        <v>51</v>
+      </c>
+      <c r="O19" s="14">
+        <v>51</v>
+      </c>
+      <c r="P19" s="14">
+        <v>51</v>
+      </c>
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
       <c r="S19" s="14"/>
@@ -34946,12 +36068,24 @@
       <c r="J20" s="14">
         <v>45</v>
       </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
+      <c r="K20" s="14">
+        <v>45</v>
+      </c>
+      <c r="L20" s="14">
+        <v>45</v>
+      </c>
+      <c r="M20" s="14">
+        <v>45</v>
+      </c>
+      <c r="N20" s="14">
+        <v>45</v>
+      </c>
+      <c r="O20" s="14">
+        <v>45</v>
+      </c>
+      <c r="P20" s="14">
+        <v>45</v>
+      </c>
       <c r="Q20" s="14"/>
       <c r="R20" s="14"/>
       <c r="S20" s="14"/>
@@ -35000,12 +36134,24 @@
       <c r="J21" s="14">
         <v>55</v>
       </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
+      <c r="K21" s="14">
+        <v>55</v>
+      </c>
+      <c r="L21" s="14">
+        <v>55</v>
+      </c>
+      <c r="M21" s="14">
+        <v>55</v>
+      </c>
+      <c r="N21" s="14">
+        <v>55</v>
+      </c>
+      <c r="O21" s="14">
+        <v>55</v>
+      </c>
+      <c r="P21" s="14">
+        <v>55</v>
+      </c>
       <c r="Q21" s="14"/>
       <c r="R21" s="14"/>
       <c r="S21" s="14"/>
@@ -35054,6 +36200,24 @@
       <c r="J22">
         <v>95</v>
       </c>
+      <c r="K22">
+        <v>95</v>
+      </c>
+      <c r="L22">
+        <v>95</v>
+      </c>
+      <c r="M22">
+        <v>95</v>
+      </c>
+      <c r="N22">
+        <v>95</v>
+      </c>
+      <c r="O22">
+        <v>95</v>
+      </c>
+      <c r="P22">
+        <v>95</v>
+      </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -35086,12 +36250,24 @@
       <c r="J23" s="14">
         <v>0</v>
       </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
+      <c r="K23" s="14">
+        <v>0</v>
+      </c>
+      <c r="L23" s="14">
+        <v>0</v>
+      </c>
+      <c r="M23" s="14">
+        <v>0</v>
+      </c>
+      <c r="N23" s="14">
+        <v>0</v>
+      </c>
+      <c r="O23" s="14">
+        <v>0</v>
+      </c>
+      <c r="P23" s="14">
+        <v>0</v>
+      </c>
       <c r="Q23" s="14"/>
       <c r="R23" s="14"/>
       <c r="S23" s="14"/>
@@ -35140,6 +36316,24 @@
       <c r="J24">
         <v>56</v>
       </c>
+      <c r="K24">
+        <v>56</v>
+      </c>
+      <c r="L24">
+        <v>56</v>
+      </c>
+      <c r="M24">
+        <v>56</v>
+      </c>
+      <c r="N24">
+        <v>56</v>
+      </c>
+      <c r="O24">
+        <v>56</v>
+      </c>
+      <c r="P24">
+        <v>56</v>
+      </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -35172,12 +36366,24 @@
       <c r="J25" s="14">
         <v>50</v>
       </c>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
+      <c r="K25" s="14">
+        <v>50</v>
+      </c>
+      <c r="L25" s="14">
+        <v>50</v>
+      </c>
+      <c r="M25" s="14">
+        <v>50</v>
+      </c>
+      <c r="N25" s="14">
+        <v>50</v>
+      </c>
+      <c r="O25" s="14">
+        <v>50</v>
+      </c>
+      <c r="P25" s="14">
+        <v>50</v>
+      </c>
       <c r="Q25" s="14"/>
       <c r="R25" s="14"/>
       <c r="S25" s="14"/>
@@ -35226,12 +36432,24 @@
       <c r="J26" s="34">
         <v>56.92</v>
       </c>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
+      <c r="K26" s="34">
+        <v>70.08</v>
+      </c>
+      <c r="L26" s="34">
+        <v>70.08</v>
+      </c>
+      <c r="M26" s="34">
+        <v>70.08</v>
+      </c>
+      <c r="N26" s="34">
+        <v>70.08</v>
+      </c>
+      <c r="O26" s="34">
+        <v>70.08</v>
+      </c>
+      <c r="P26" s="34">
+        <v>70.08</v>
+      </c>
       <c r="Q26" s="34"/>
       <c r="R26" s="34"/>
       <c r="S26" s="34"/>
@@ -35280,12 +36498,24 @@
       <c r="J27" s="34">
         <v>126.05</v>
       </c>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
+      <c r="K27" s="34">
+        <v>125.01</v>
+      </c>
+      <c r="L27" s="34">
+        <v>125.01</v>
+      </c>
+      <c r="M27" s="34">
+        <v>125.01</v>
+      </c>
+      <c r="N27" s="34">
+        <v>125.01</v>
+      </c>
+      <c r="O27" s="34">
+        <v>125.01</v>
+      </c>
+      <c r="P27" s="34">
+        <v>125.01</v>
+      </c>
       <c r="Q27" s="34"/>
       <c r="R27" s="34"/>
       <c r="S27" s="34"/>
@@ -35334,12 +36564,24 @@
       <c r="J28" s="14">
         <v>0</v>
       </c>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
+      <c r="K28" s="14">
+        <v>0</v>
+      </c>
+      <c r="L28" s="14">
+        <v>0</v>
+      </c>
+      <c r="M28" s="14">
+        <v>0</v>
+      </c>
+      <c r="N28" s="14">
+        <v>0</v>
+      </c>
+      <c r="O28" s="14">
+        <v>0</v>
+      </c>
+      <c r="P28" s="14">
+        <v>0</v>
+      </c>
       <c r="Q28" s="14"/>
       <c r="R28" s="14"/>
       <c r="S28" s="14"/>
@@ -35388,12 +36630,24 @@
       <c r="J29" s="34">
         <v>51.44</v>
       </c>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-      <c r="P29" s="34"/>
+      <c r="K29" s="34">
+        <v>58.32</v>
+      </c>
+      <c r="L29" s="34">
+        <v>58.32</v>
+      </c>
+      <c r="M29" s="34">
+        <v>58.32</v>
+      </c>
+      <c r="N29" s="34">
+        <v>58.32</v>
+      </c>
+      <c r="O29" s="34">
+        <v>58.32</v>
+      </c>
+      <c r="P29" s="34">
+        <v>58.32</v>
+      </c>
       <c r="Q29" s="34"/>
       <c r="R29" s="34"/>
       <c r="S29" s="34"/>
@@ -35442,12 +36696,24 @@
       <c r="J30" s="14">
         <v>29</v>
       </c>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
+      <c r="K30" s="14">
+        <v>29</v>
+      </c>
+      <c r="L30" s="14">
+        <v>29</v>
+      </c>
+      <c r="M30" s="14">
+        <v>29</v>
+      </c>
+      <c r="N30" s="14">
+        <v>29</v>
+      </c>
+      <c r="O30" s="14">
+        <v>29</v>
+      </c>
+      <c r="P30" s="14">
+        <v>29</v>
+      </c>
       <c r="Q30" s="14"/>
       <c r="R30" s="14"/>
       <c r="S30" s="14"/>
@@ -35496,12 +36762,24 @@
       <c r="J31" s="14">
         <v>139</v>
       </c>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
+      <c r="K31" s="14">
+        <v>139</v>
+      </c>
+      <c r="L31" s="14">
+        <v>139</v>
+      </c>
+      <c r="M31" s="14">
+        <v>139</v>
+      </c>
+      <c r="N31" s="14">
+        <v>139</v>
+      </c>
+      <c r="O31" s="14">
+        <v>139</v>
+      </c>
+      <c r="P31" s="14">
+        <v>139</v>
+      </c>
       <c r="Q31" s="14"/>
       <c r="R31" s="14"/>
       <c r="S31" s="14"/>
@@ -35550,12 +36828,24 @@
       <c r="J32" s="14">
         <v>0</v>
       </c>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
+      <c r="K32" s="14">
+        <v>0</v>
+      </c>
+      <c r="L32" s="14">
+        <v>0</v>
+      </c>
+      <c r="M32" s="14">
+        <v>0</v>
+      </c>
+      <c r="N32" s="14">
+        <v>0</v>
+      </c>
+      <c r="O32" s="14">
+        <v>0</v>
+      </c>
+      <c r="P32" s="14">
+        <v>0</v>
+      </c>
       <c r="Q32" s="14"/>
       <c r="R32" s="14"/>
       <c r="S32" s="14"/>
@@ -35604,12 +36894,24 @@
       <c r="J33" s="14">
         <v>0</v>
       </c>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
+      <c r="K33" s="14">
+        <v>0</v>
+      </c>
+      <c r="L33" s="14">
+        <v>0</v>
+      </c>
+      <c r="M33" s="14">
+        <v>0</v>
+      </c>
+      <c r="N33" s="14">
+        <v>0</v>
+      </c>
+      <c r="O33" s="14">
+        <v>0</v>
+      </c>
+      <c r="P33" s="14">
+        <v>0</v>
+      </c>
       <c r="Q33" s="14"/>
       <c r="R33" s="14"/>
       <c r="S33" s="14"/>
@@ -35658,12 +36960,24 @@
       <c r="J34" s="34">
         <v>62.11</v>
       </c>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
+      <c r="K34" s="34">
+        <v>85.3</v>
+      </c>
+      <c r="L34" s="34">
+        <v>85.3</v>
+      </c>
+      <c r="M34" s="34">
+        <v>85.3</v>
+      </c>
+      <c r="N34" s="34">
+        <v>85.3</v>
+      </c>
+      <c r="O34" s="34">
+        <v>85.3</v>
+      </c>
+      <c r="P34" s="34">
+        <v>85.3</v>
+      </c>
       <c r="Q34" s="34"/>
       <c r="R34" s="34"/>
       <c r="S34" s="34"/>
@@ -35712,12 +37026,24 @@
       <c r="J35" s="34">
         <v>31.04</v>
       </c>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
+      <c r="K35" s="34">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="L35" s="34">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="M35" s="34">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="N35" s="34">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="O35" s="34">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="P35" s="34">
+        <v>34.380000000000003</v>
+      </c>
       <c r="Q35" s="34"/>
       <c r="R35" s="34"/>
       <c r="S35" s="34"/>
@@ -35766,12 +37092,24 @@
       <c r="J36" s="14">
         <v>0</v>
       </c>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
+      <c r="K36" s="14">
+        <v>0</v>
+      </c>
+      <c r="L36" s="14">
+        <v>0</v>
+      </c>
+      <c r="M36" s="14">
+        <v>0</v>
+      </c>
+      <c r="N36" s="14">
+        <v>0</v>
+      </c>
+      <c r="O36" s="14">
+        <v>0</v>
+      </c>
+      <c r="P36" s="14">
+        <v>0</v>
+      </c>
       <c r="Q36" s="14"/>
       <c r="R36" s="14"/>
       <c r="S36" s="14"/>
@@ -35820,12 +37158,24 @@
       <c r="J37" s="14">
         <v>0</v>
       </c>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
+      <c r="K37" s="14">
+        <v>0</v>
+      </c>
+      <c r="L37" s="14">
+        <v>0</v>
+      </c>
+      <c r="M37" s="14">
+        <v>0</v>
+      </c>
+      <c r="N37" s="14">
+        <v>0</v>
+      </c>
+      <c r="O37" s="14">
+        <v>0</v>
+      </c>
+      <c r="P37" s="14">
+        <v>0</v>
+      </c>
       <c r="Q37" s="14"/>
       <c r="R37" s="14"/>
       <c r="S37" s="14"/>
@@ -35874,6 +37224,24 @@
       <c r="J38">
         <v>60</v>
       </c>
+      <c r="K38">
+        <v>60</v>
+      </c>
+      <c r="L38">
+        <v>60</v>
+      </c>
+      <c r="M38">
+        <v>60</v>
+      </c>
+      <c r="N38">
+        <v>60</v>
+      </c>
+      <c r="O38">
+        <v>60</v>
+      </c>
+      <c r="P38">
+        <v>60</v>
+      </c>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -35906,12 +37274,24 @@
       <c r="J39" s="14">
         <v>0</v>
       </c>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="14"/>
-      <c r="P39" s="14"/>
+      <c r="K39" s="14">
+        <v>0</v>
+      </c>
+      <c r="L39" s="14">
+        <v>0</v>
+      </c>
+      <c r="M39" s="14">
+        <v>0</v>
+      </c>
+      <c r="N39" s="14">
+        <v>0</v>
+      </c>
+      <c r="O39" s="14">
+        <v>0</v>
+      </c>
+      <c r="P39" s="14">
+        <v>0</v>
+      </c>
       <c r="Q39" s="14"/>
       <c r="R39" s="14"/>
       <c r="S39" s="14"/>
@@ -35960,12 +37340,24 @@
       <c r="J40" s="14">
         <v>0</v>
       </c>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14"/>
+      <c r="K40" s="14">
+        <v>0</v>
+      </c>
+      <c r="L40" s="14">
+        <v>0</v>
+      </c>
+      <c r="M40" s="14">
+        <v>0</v>
+      </c>
+      <c r="N40" s="14">
+        <v>0</v>
+      </c>
+      <c r="O40" s="14">
+        <v>0</v>
+      </c>
+      <c r="P40" s="14">
+        <v>0</v>
+      </c>
       <c r="Q40" s="14"/>
       <c r="R40" s="14"/>
       <c r="S40" s="14"/>
@@ -36014,12 +37406,24 @@
       <c r="J41" s="14">
         <v>40</v>
       </c>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
+      <c r="K41" s="14">
+        <v>40</v>
+      </c>
+      <c r="L41" s="14">
+        <v>40</v>
+      </c>
+      <c r="M41" s="14">
+        <v>40</v>
+      </c>
+      <c r="N41" s="14">
+        <v>40</v>
+      </c>
+      <c r="O41" s="14">
+        <v>40</v>
+      </c>
+      <c r="P41" s="14">
+        <v>40</v>
+      </c>
       <c r="Q41" s="14"/>
       <c r="R41" s="14"/>
       <c r="S41" s="14"/>
@@ -36068,12 +37472,24 @@
       <c r="J42" s="14">
         <v>0</v>
       </c>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="14"/>
+      <c r="K42" s="14">
+        <v>0</v>
+      </c>
+      <c r="L42" s="14">
+        <v>0</v>
+      </c>
+      <c r="M42" s="14">
+        <v>0</v>
+      </c>
+      <c r="N42" s="14">
+        <v>0</v>
+      </c>
+      <c r="O42" s="14">
+        <v>0</v>
+      </c>
+      <c r="P42" s="14">
+        <v>0</v>
+      </c>
       <c r="Q42" s="14"/>
       <c r="R42" s="14"/>
       <c r="S42" s="14"/>
@@ -36122,12 +37538,24 @@
       <c r="J43" s="14">
         <v>70</v>
       </c>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="14"/>
-      <c r="O43" s="14"/>
-      <c r="P43" s="14"/>
+      <c r="K43" s="14">
+        <v>70</v>
+      </c>
+      <c r="L43" s="14">
+        <v>70</v>
+      </c>
+      <c r="M43" s="14">
+        <v>70</v>
+      </c>
+      <c r="N43" s="14">
+        <v>70</v>
+      </c>
+      <c r="O43" s="14">
+        <v>70</v>
+      </c>
+      <c r="P43" s="14">
+        <v>70</v>
+      </c>
       <c r="Q43" s="14"/>
       <c r="R43" s="14"/>
       <c r="S43" s="14"/>
@@ -36176,12 +37604,24 @@
       <c r="J44" s="14">
         <v>0</v>
       </c>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="14"/>
+      <c r="K44" s="14">
+        <v>0</v>
+      </c>
+      <c r="L44" s="14">
+        <v>0</v>
+      </c>
+      <c r="M44" s="14">
+        <v>0</v>
+      </c>
+      <c r="N44" s="14">
+        <v>0</v>
+      </c>
+      <c r="O44" s="14">
+        <v>0</v>
+      </c>
+      <c r="P44" s="14">
+        <v>0</v>
+      </c>
       <c r="Q44" s="14"/>
       <c r="R44" s="14"/>
       <c r="S44" s="14"/>
@@ -36230,12 +37670,24 @@
       <c r="J45" s="14">
         <v>0</v>
       </c>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="14"/>
+      <c r="K45" s="14">
+        <v>0</v>
+      </c>
+      <c r="L45" s="14">
+        <v>0</v>
+      </c>
+      <c r="M45" s="14">
+        <v>0</v>
+      </c>
+      <c r="N45" s="14">
+        <v>0</v>
+      </c>
+      <c r="O45" s="14">
+        <v>0</v>
+      </c>
+      <c r="P45" s="14">
+        <v>0</v>
+      </c>
       <c r="Q45" s="14"/>
       <c r="R45" s="14"/>
       <c r="S45" s="14"/>
@@ -36284,12 +37736,24 @@
       <c r="J46" s="14">
         <v>80</v>
       </c>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="14"/>
+      <c r="K46" s="14">
+        <v>80</v>
+      </c>
+      <c r="L46" s="14">
+        <v>80</v>
+      </c>
+      <c r="M46" s="14">
+        <v>80</v>
+      </c>
+      <c r="N46" s="14">
+        <v>80</v>
+      </c>
+      <c r="O46" s="14">
+        <v>80</v>
+      </c>
+      <c r="P46" s="14">
+        <v>80</v>
+      </c>
       <c r="Q46" s="14"/>
       <c r="R46" s="14"/>
       <c r="S46" s="14"/>
@@ -36338,12 +37802,24 @@
       <c r="J47" s="14">
         <v>0</v>
       </c>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="14"/>
+      <c r="K47" s="14">
+        <v>0</v>
+      </c>
+      <c r="L47" s="14">
+        <v>0</v>
+      </c>
+      <c r="M47" s="14">
+        <v>0</v>
+      </c>
+      <c r="N47" s="14">
+        <v>0</v>
+      </c>
+      <c r="O47" s="14">
+        <v>0</v>
+      </c>
+      <c r="P47" s="14">
+        <v>0</v>
+      </c>
       <c r="Q47" s="14"/>
       <c r="R47" s="14"/>
       <c r="S47" s="14"/>
@@ -36392,12 +37868,24 @@
       <c r="J48" s="14">
         <v>170</v>
       </c>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14"/>
+      <c r="K48" s="14">
+        <v>170</v>
+      </c>
+      <c r="L48" s="14">
+        <v>170</v>
+      </c>
+      <c r="M48" s="14">
+        <v>170</v>
+      </c>
+      <c r="N48" s="14">
+        <v>170</v>
+      </c>
+      <c r="O48" s="14">
+        <v>170</v>
+      </c>
+      <c r="P48" s="14">
+        <v>170</v>
+      </c>
       <c r="Q48" s="14"/>
       <c r="R48" s="14"/>
       <c r="S48" s="14"/>
@@ -36446,12 +37934,24 @@
       <c r="J49" s="14">
         <v>30</v>
       </c>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="14"/>
+      <c r="K49" s="14">
+        <v>30</v>
+      </c>
+      <c r="L49" s="14">
+        <v>30</v>
+      </c>
+      <c r="M49" s="14">
+        <v>30</v>
+      </c>
+      <c r="N49" s="14">
+        <v>30</v>
+      </c>
+      <c r="O49" s="14">
+        <v>30</v>
+      </c>
+      <c r="P49" s="14">
+        <v>30</v>
+      </c>
       <c r="Q49" s="14"/>
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
@@ -36500,6 +38000,24 @@
       <c r="J50">
         <v>225</v>
       </c>
+      <c r="K50">
+        <v>225</v>
+      </c>
+      <c r="L50">
+        <v>225</v>
+      </c>
+      <c r="M50">
+        <v>225</v>
+      </c>
+      <c r="N50">
+        <v>225</v>
+      </c>
+      <c r="O50">
+        <v>225</v>
+      </c>
+      <c r="P50">
+        <v>225</v>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
@@ -36532,12 +38050,24 @@
       <c r="J51" s="14">
         <v>53</v>
       </c>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="14"/>
+      <c r="K51" s="14">
+        <v>53</v>
+      </c>
+      <c r="L51" s="14">
+        <v>53</v>
+      </c>
+      <c r="M51" s="14">
+        <v>53</v>
+      </c>
+      <c r="N51" s="14">
+        <v>53</v>
+      </c>
+      <c r="O51" s="14">
+        <v>53</v>
+      </c>
+      <c r="P51" s="14">
+        <v>53</v>
+      </c>
       <c r="Q51" s="14"/>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
@@ -36586,12 +38116,24 @@
       <c r="J52" s="14">
         <v>0</v>
       </c>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="14"/>
+      <c r="K52" s="14">
+        <v>0</v>
+      </c>
+      <c r="L52" s="14">
+        <v>0</v>
+      </c>
+      <c r="M52" s="14">
+        <v>0</v>
+      </c>
+      <c r="N52" s="14">
+        <v>0</v>
+      </c>
+      <c r="O52" s="14">
+        <v>0</v>
+      </c>
+      <c r="P52" s="14">
+        <v>0</v>
+      </c>
       <c r="Q52" s="14"/>
       <c r="R52" s="14"/>
       <c r="S52" s="14"/>
@@ -36640,12 +38182,24 @@
       <c r="J53" s="14">
         <v>0</v>
       </c>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="14"/>
+      <c r="K53" s="14">
+        <v>0</v>
+      </c>
+      <c r="L53" s="14">
+        <v>0</v>
+      </c>
+      <c r="M53" s="14">
+        <v>0</v>
+      </c>
+      <c r="N53" s="14">
+        <v>0</v>
+      </c>
+      <c r="O53" s="14">
+        <v>0</v>
+      </c>
+      <c r="P53" s="14">
+        <v>0</v>
+      </c>
       <c r="Q53" s="14"/>
       <c r="R53" s="14"/>
       <c r="S53" s="14"/>
@@ -36694,12 +38248,24 @@
       <c r="J54" s="14">
         <v>0</v>
       </c>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="14"/>
-      <c r="P54" s="14"/>
+      <c r="K54" s="14">
+        <v>0</v>
+      </c>
+      <c r="L54" s="14">
+        <v>0</v>
+      </c>
+      <c r="M54" s="14">
+        <v>0</v>
+      </c>
+      <c r="N54" s="14">
+        <v>0</v>
+      </c>
+      <c r="O54" s="14">
+        <v>0</v>
+      </c>
+      <c r="P54" s="14">
+        <v>0</v>
+      </c>
       <c r="Q54" s="14"/>
       <c r="R54" s="14"/>
       <c r="S54" s="14"/>
@@ -36748,6 +38314,24 @@
       <c r="J55">
         <v>61</v>
       </c>
+      <c r="K55">
+        <v>61</v>
+      </c>
+      <c r="L55">
+        <v>61</v>
+      </c>
+      <c r="M55">
+        <v>61</v>
+      </c>
+      <c r="N55">
+        <v>61</v>
+      </c>
+      <c r="O55">
+        <v>61</v>
+      </c>
+      <c r="P55">
+        <v>61</v>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
@@ -36791,27 +38375,27 @@
       </c>
       <c r="K57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2708.09</v>
       </c>
       <c r="L57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2708.09</v>
       </c>
       <c r="M57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2708.09</v>
       </c>
       <c r="N57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2708.09</v>
       </c>
       <c r="O57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2708.09</v>
       </c>
       <c r="P57" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2708.09</v>
       </c>
       <c r="Q57" s="13">
         <f t="shared" si="0"/>
@@ -36884,7 +38468,7 @@
       </c>
       <c r="B59">
         <f>SUM(A57:AF57)</f>
-        <v>24042.910000000003</v>
+        <v>40291.449999999997</v>
       </c>
     </row>
   </sheetData>
